--- a/outputs/stock_Refinery/_news.xlsx
+++ b/outputs/stock_Refinery/_news.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,37 +468,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-10 16:15:00</t>
+          <t>2026-04-27 13:15:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Delek US Holdings to Host First Quarter 2026 Conference Call on April 29th</t>
+          <t>Delek Gears Up to Report Q1 Earnings: Key Metrics to Watch</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-to-host-first-quarter-2026-conference-20260410.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-gears-up-to-report-q1-earnings-key-metrics-20260427.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>businesswire.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE: DK) (“Delek US”) today announced that the Company intends to issue a press release summarizing first quarter 2026 results before the U.S. stock market opens on Wednesday, April 29, 2026. A conference call to discuss these results is scheduled to begin at 9:00 a.m. CT (10:00 a.m. ET) on Wednesday, April 29, 2026. The live broadcast of this conference call will be available online by going to www.DelekUS.com and clicking on the inv.</t>
+          <t>DK heads into Q1 earnings with revenue pressure, rising costs and refinery downtime, even as optimization efforts may help cushion the impact.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260410266271/en/Delek-US-Holdings-to-Host-First-Quarter-2026-Conference-Call-on-April-29th/</t>
+          <t>https://www.zacks.com/stock/news/2908830/delek-gears-up-to-report-q1-earnings-key-metrics-to-watch?cid=CS-STOCKNEWSAPI-FT-analyst_blog|earnings_preview-2908830</t>
         </is>
       </c>
     </row>
@@ -510,37 +510,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-10 07:51:29</t>
+          <t>2026-04-20 18:00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>247 Wallst</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Here Are Friday’s Top Wall Street Analyst Research Calls: Autodesk, Delek US Holdings, Insmed, Nike, Nutanix, ServiceNow, Shake Shack, Southern Copper, Veeva Systems, and More</t>
+          <t>Delek US Holdings Announces Refining Leadership Transition</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/here-are-fridays-top-wall-street-analyst-research-calls-20260410.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-announces-refining-leadership-transition-20260420.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>247wallst.com</t>
+          <t>businesswire.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Market Stock Futures: The futures are trading mixed as we approach the end of one of the most volatile and wild trading weeks in recent memory. After starting the day lower on Thursday as mixed reports on the success of the ships passing through the Strait of Hormuz rolled in, stocks gained momentum as the... Here Are Friday's Top Wall Street Analyst Research Calls: Autodesk, Delek US Holdings, Insmed, Nike, Nutanix, ServiceNow, Shake Shack, Southern Copper, Veeva Systems, and More</t>
+          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE: DK) today announced the appointment of Amber Russell as Executive Vice President, Refining, effective April 20, 2026. In this role, Ms. Russell will lead the company's refining operations, with a focus on advancing operational excellence, safety performance, and strategic growth across Delek's refining system. Ms. Russell has nearly three decades of global energy industry experience, including senior leadership roles at ExxonMobi.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://247wallst.com/investing/2026/04/10/here-are-fridays-top-wall-street-analyst-research-calls-autodesk-delek-us-holdings-insmed-nike-nutanix-servicenow-shake-shack-southern-copper-veeva-systems-and-more/</t>
+          <t>https://www.businesswire.com/news/home/20260420229701/en/Delek-US-Holdings-Announces-Refining-Leadership-Transition/</t>
         </is>
       </c>
     </row>
@@ -552,37 +552,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-07 05:07:04</t>
+          <t>2026-04-20 17:30:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SG Americas Securities LLC Sells 30,236 Shares of Delek US Holdings, Inc. $DK</t>
+          <t>Delek US Holdings, Inc. Announces Quarterly Dividend</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/sg-americas-securities-llc-sells-30236-shares-of-delek-20260407.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-inc-announces-quarterly-dividend-20260420.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>businesswire.com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SG Americas Securities LLC trimmed its holdings in Delek US Holdings, Inc. (NYSE: DK) by 38.1% in the fourth quarter, according to the company in its most recent Form 13F filing with the Securities and Exchange Commission. The fund owned 49,056 shares of the oil and gas company's stock after selling 30,236 shares</t>
+          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE:DK) (“Delek”) today announced that its Board of Directors has approved a quarterly dividend of $0.255 per share, to be paid on May 8, 2026, to shareholders of record on May 1, 2026. About Delek US Holdings, Inc. Delek US Holdings, Inc. is a diversified downstream energy company with assets in petroleum refining, logistics, and pipelines. The refining assets consist primarily of refineries operated in Tyler and Big Spring, Texas, E.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/04/07/sg-americas-securities-llc-sells-30236-shares-of-delek-us-holdings-inc-dk.html</t>
+          <t>https://www.businesswire.com/news/home/20260420552491/en/Delek-US-Holdings-Inc.-Announces-Quarterly-Dividend/</t>
         </is>
       </c>
     </row>
@@ -594,37 +594,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-06 09:58:00</t>
+          <t>2026-04-10 16:15:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A Delek Director Sold 5,000 Company Shares. Here's What It Means for Investors.</t>
+          <t>Delek US Holdings to Host First Quarter 2026 Conference Call on April 29th</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/a-delek-director-sold-5000-company-shares-heres-what-20260406.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-to-host-first-quarter-2026-conference-20260410.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>businesswire.com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Director William Finnerty sold 5,000 shares for a transaction value of ~$238,000 on March 27, 2026. The sale represented 12.09% of his direct holdings at the time, reducing his direct position from 41,369 to 36,369 shares.</t>
+          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE: DK) (“Delek US”) today announced that the Company intends to issue a press release summarizing first quarter 2026 results before the U.S. stock market opens on Wednesday, April 29, 2026. A conference call to discuss these results is scheduled to begin at 9:00 a.m. CT (10:00 a.m. ET) on Wednesday, April 29, 2026. The live broadcast of this conference call will be available online by going to www.DelekUS.com and clicking on the inv.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.fool.com/coverage/filings/2026/04/06/director-sells-dk-5000-shares-for-238000/</t>
+          <t>https://www.businesswire.com/news/home/20260410266271/en/Delek-US-Holdings-to-Host-First-Quarter-2026-Conference-Call-on-April-29th/</t>
         </is>
       </c>
     </row>
@@ -636,37 +636,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-02 17:01:41</t>
+          <t>2026-04-10 07:51:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>247 Wallst</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Delek US Holdings: Iran War Benefits Justify The Rally (Downgrade)</t>
+          <t>Here Are Friday’s Top Wall Street Analyst Research Calls: Autodesk, Delek US Holdings, Insmed, Nike, Nutanix, ServiceNow, Shake Shack, Southern Copper, Veeva Systems, and More</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-iran-war-benefits-justify-the-rally-20260402.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/here-are-fridays-top-wall-street-analyst-research-calls-20260410.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>247wallst.com</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Delek US Holdings has surged nearly 200% over the past year, driven by regulatory relief and surging crack spreads from geopolitical disruptions. DK benefits from EPA small refinery exemptions and a favorable balance sheet, with $615 million in cash, $889 million in debt, and a valuable DKL stake. I estimate DK's fair value at $53, reflecting both a one-time windfall from the Iran War and normalized free cash flow, implying ~20% upside.</t>
+          <t>Pre-Market Stock Futures: The futures are trading mixed as we approach the end of one of the most volatile and wild trading weeks in recent memory. After starting the day lower on Thursday as mixed reports on the success of the ships passing through the Strait of Hormuz rolled in, stocks gained momentum as the... Here Are Friday's Top Wall Street Analyst Research Calls: Autodesk, Delek US Holdings, Insmed, Nike, Nutanix, ServiceNow, Shake Shack, Southern Copper, Veeva Systems, and More</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4888191-delek-us-holdings-iran-war-benefits-justify-the-rally-downgrade</t>
+          <t>https://247wallst.com/investing/2026/04/10/here-are-fridays-top-wall-street-analyst-research-calls-autodesk-delek-us-holdings-insmed-nike-nutanix-servicenow-shake-shack-southern-copper-veeva-systems-and-more/</t>
         </is>
       </c>
     </row>
@@ -678,37 +678,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-31 12:36:11</t>
+          <t>2026-04-07 05:07:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Delek Shares Surges 204% in a Year: Should Investors Lock In Profits?</t>
+          <t>SG Americas Securities LLC Sells 30,236 Shares of Delek US Holdings, Inc. $DK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-shares-surges-204-in-a-year-should-investors-20260331.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/sg-americas-securities-llc-sells-30236-shares-of-delek-20260407.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Shares of Delek US Holdings, Inc.  DK gained momentum over the last year, following a staggering rise of 203.6%. During the same time period, the company's shares outperformed the sub-industry and the broader oil and energy sector's rally of 55% and 38.4%, respectively.</t>
+          <t>SG Americas Securities LLC trimmed its holdings in Delek US Holdings, Inc. (NYSE: DK) by 38.1% in the fourth quarter, according to the company in its most recent Form 13F filing with the Securities and Exchange Commission. The fund owned 49,056 shares of the oil and gas company's stock after selling 30,236 shares</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2892409/delek-shares-surges-204-in-a-year-should-investors-lock-in-profits?cid=CS-STOCKNEWSAPI-FT-analyst_blog|rank_focused-2892409</t>
+          <t>https://www.defenseworld.net/2026/04/07/sg-americas-securities-llc-sells-30236-shares-of-delek-us-holdings-inc-dk.html</t>
         </is>
       </c>
     </row>
@@ -720,37 +720,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-31 08:16:48</t>
+          <t>2026-04-06 09:58:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>U.S. Refiners: Recent Trends And Relative Value</t>
+          <t>A Delek Director Sold 5,000 Company Shares. Here's What It Means for Investors.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/us-refiners-recent-trends-and-relative-value-20260331.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/a-delek-director-sold-5000-company-shares-heres-what-20260406.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Refiners are  most profitable when oil prices are elevated, gasoline demand remains robust, and refiner margins are high. Refiner margins are dependent on crack spread - the difference between the value of the gasoline and diesel produced and the input cost of crude oil. The 3-2-1 crack spread has already nearly doubled this year from $0.65 to $1.65 per gallon of fuel.</t>
+          <t>Director William Finnerty sold 5,000 shares for a transaction value of ~$238,000 on March 27, 2026. The sale represented 12.09% of his direct holdings at the time, reducing his direct position from 41,369 to 36,369 shares.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4887380-us-refiners-recent-trends-and-relative-value</t>
+          <t>https://www.fool.com/coverage/filings/2026/04/06/director-sells-dk-5000-shares-for-238000/</t>
         </is>
       </c>
     </row>
@@ -762,37 +762,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-26 12:08:40</t>
+          <t>2026-04-02 17:01:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Delek US Holdings Director Sells $6.1 Million in Shares -- What Should Investors Know?</t>
+          <t>Delek US Holdings: Iran War Benefits Justify The Rally (Downgrade)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-director-sells-61-million-in-shares-20260326.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-iran-war-benefits-justify-the-rally-20260402.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ezra Uzi Yemin sold a combined 140,006 shares across two separate transactions -- on March 4 and March 18, 2026 -- for a total of roughly $6.1 million. Together, the two transactions reduced Yemin's aggregate holdings by approximately 14.9%, from 938,076 shares pre-transaction to 798,070 shares as of March 18.</t>
+          <t>Delek US Holdings has surged nearly 200% over the past year, driven by regulatory relief and surging crack spreads from geopolitical disruptions. DK benefits from EPA small refinery exemptions and a favorable balance sheet, with $615 million in cash, $889 million in debt, and a valuable DKL stake. I estimate DK's fair value at $53, reflecting both a one-time windfall from the Iran War and normalized free cash flow, implying ~20% upside.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.fool.com/coverage/filings/2026/03/26/delek-us-holdings-director-sells-usd6-1-million-in-shares-what-should-investors-know/</t>
+          <t>https://seekingalpha.com/article/4888191-delek-us-holdings-iran-war-benefits-justify-the-rally-downgrade</t>
         </is>
       </c>
     </row>
@@ -804,37 +804,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-25 14:25:19</t>
+          <t>2026-03-31 12:36:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Delek Director Sells $338K in Stock as Shares Surge 180% in One Year</t>
+          <t>Delek Shares Surges 204% in a Year: Should Investors Lock In Profits?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-director-sells-338k-in-stock-as-shares-surge-20260325.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-shares-surges-204-in-a-year-should-investors-20260331.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A Delek director reported the sale of 7,343 shares for about $338,000 on March 19, 2026. The transaction involved only direct, open-market sales; no indirect or derivative interests were reported in this filing.</t>
+          <t>Shares of Delek US Holdings, Inc.  DK gained momentum over the last year, following a staggering rise of 203.6%. During the same time period, the company's shares outperformed the sub-industry and the broader oil and energy sector's rally of 55% and 38.4%, respectively.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.fool.com/coverage/filings/2026/03/25/delek-director-sells-usd338k-in-stock-as-shares-surge-180-in-one-year/</t>
+          <t>https://www.zacks.com/stock/news/2892409/delek-shares-surges-204-in-a-year-should-investors-lock-in-profits?cid=CS-STOCKNEWSAPI-FT-analyst_blog|rank_focused-2892409</t>
         </is>
       </c>
     </row>
@@ -846,37 +846,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-24 19:09:26</t>
+          <t>2026-03-31 08:16:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Here's Why Shares in Delek US Soared Today</t>
+          <t>U.S. Refiners: Recent Trends And Relative Value</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/heres-why-shares-in-delek-us-soared-today-20260324.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/us-refiners-recent-trends-and-relative-value-20260331.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The refining crack spread continues to soar. Delek US sources crude oil from the domestic market and refines it in the U.S. as well.</t>
+          <t>Refiners are  most profitable when oil prices are elevated, gasoline demand remains robust, and refiner margins are high. Refiner margins are dependent on crack spread - the difference between the value of the gasoline and diesel produced and the input cost of crude oil. The 3-2-1 crack spread has already nearly doubled this year from $0.65 to $1.65 per gallon of fuel.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.fool.com/investing/2026/03/24/heres-why-shares-in-delek-us-soared-today/</t>
+          <t>https://seekingalpha.com/article/4887380-us-refiners-recent-trends-and-relative-value</t>
         </is>
       </c>
     </row>
@@ -888,37 +888,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-08 05:14:59</t>
+          <t>2026-03-26 12:08:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Joseph Israel Sells 38,000 Shares of Delek US (NYSE:DK) Stock</t>
+          <t>Delek US Holdings Director Sells $6.1 Million in Shares -- What Should Investors Know?</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/joseph-israel-sells-38000-shares-of-delek-us-nysedk-20260308.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-director-sells-61-million-in-shares-20260326.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. (NYSE: DK - Get Free Report) EVP Joseph Israel sold 38,000 shares of the firm's stock in a transaction that occurred on Wednesday, March 4th. The shares were sold at an average price of $40.65, for a total value of $1,544,700.00. Following the completion of the sale, the executive vice president owned</t>
+          <t>Ezra Uzi Yemin sold a combined 140,006 shares across two separate transactions -- on March 4 and March 18, 2026 -- for a total of roughly $6.1 million. Together, the two transactions reduced Yemin's aggregate holdings by approximately 14.9%, from 938,076 shares pre-transaction to 798,070 shares as of March 18.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/08/joseph-israel-sells-38000-shares-of-delek-us-nysedk-stock.html</t>
+          <t>https://www.fool.com/coverage/filings/2026/03/26/delek-us-holdings-director-sells-usd6-1-million-in-shares-what-should-investors-know/</t>
         </is>
       </c>
     </row>
@@ -930,37 +930,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-08 05:14:58</t>
+          <t>2026-03-25 14:25:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Shlomo Zohar Sells 22,029 Shares of Delek US (NYSE:DK) Stock</t>
+          <t>Delek Director Sells $338K in Stock as Shares Surge 180% in One Year</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/shlomo-zohar-sells-22029-shares-of-delek-us-nysedk-20260308.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-director-sells-338k-in-stock-as-shares-surge-20260325.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. (NYSE: DK - Get Free Report) Director Shlomo Zohar sold 22,029 shares of the firm's stock in a transaction that occurred on Thursday, March 5th. The shares were sold at an average price of $44.83, for a total value of $987,560.07. Following the sale, the director owned 18,989 shares of the company's</t>
+          <t>A Delek director reported the sale of 7,343 shares for about $338,000 on March 19, 2026. The transaction involved only direct, open-market sales; no indirect or derivative interests were reported in this filing.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/08/shlomo-zohar-sells-22029-shares-of-delek-us-nysedk-stock.html</t>
+          <t>https://www.fool.com/coverage/filings/2026/03/25/delek-director-sells-usd338k-in-stock-as-shares-surge-180-in-one-year/</t>
         </is>
       </c>
     </row>
@@ -972,37 +972,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-08 05:14:51</t>
+          <t>2026-03-24 19:09:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Reuven Spiegel Sells 20,000 Shares of Delek US (NYSE:DK) Stock</t>
+          <t>Here's Why Shares in Delek US Soared Today</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/reuven-spiegel-sells-20000-shares-of-delek-us-nysedk-20260308.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/heres-why-shares-in-delek-us-soared-today-20260324.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. (NYSE: DK - Get Free Report) EVP Reuven Spiegel sold 20,000 shares of the firm's stock in a transaction dated Wednesday, March 4th. The shares were sold at an average price of $42.84, for a total transaction of $856,800.00. Following the transaction, the executive vice president directly owned 48,530 shares in the</t>
+          <t>The refining crack spread continues to soar. Delek US sources crude oil from the domestic market and refines it in the U.S. as well.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/08/reuven-spiegel-sells-20000-shares-of-delek-us-nysedk-stock.html</t>
+          <t>https://www.fool.com/investing/2026/03/24/heres-why-shares-in-delek-us-soared-today/</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-07 05:04:54</t>
+          <t>2026-03-08 05:14:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. (NYSE:DK) Given Average Recommendation of “Hold” by Analysts</t>
+          <t>Joseph Israel Sells 38,000 Shares of Delek US (NYSE:DK) Stock</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-inc-nysedk-given-average-recommendation-of-20260307.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/joseph-israel-sells-38000-shares-of-delek-us-nysedk-20260308.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Shares of Delek US Holdings, Inc. (NYSE: DK - Get Free Report) have been given a consensus recommendation of "Hold" by the fourteen ratings firms that are currently covering the stock, MarketBeat reports. Two equities research analysts have rated the stock with a sell rating, eight have issued a hold rating and four have assigned a</t>
+          <t>Delek US Holdings, Inc. (NYSE: DK - Get Free Report) EVP Joseph Israel sold 38,000 shares of the firm's stock in a transaction that occurred on Wednesday, March 4th. The shares were sold at an average price of $40.65, for a total value of $1,544,700.00. Following the completion of the sale, the executive vice president owned</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/07/delek-us-holdings-inc-nysedk-given-average-recommendation-of-hold-by-analysts.html</t>
+          <t>https://www.defenseworld.net/2026/03/08/joseph-israel-sells-38000-shares-of-delek-us-nysedk-stock.html</t>
         </is>
       </c>
     </row>
@@ -1056,37 +1056,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-04 08:25:17</t>
+          <t>2026-03-08 05:14:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Delek US Stock: Not a Buy, But Still Worth Holding for Now</t>
+          <t>Shlomo Zohar Sells 22,029 Shares of Delek US (NYSE:DK) Stock</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-stock-not-a-buy-but-still-worth-20260304.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/shlomo-zohar-sells-22029-shares-of-delek-us-nysedk-20260308.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DK strengthens its financial position with strategic cash flow improvements and shareholder returns, but faces risks from regulatory challenges and refining market volatility.</t>
+          <t>Delek US Holdings, Inc. (NYSE: DK - Get Free Report) Director Shlomo Zohar sold 22,029 shares of the firm's stock in a transaction that occurred on Thursday, March 5th. The shares were sold at an average price of $44.83, for a total value of $987,560.07. Following the sale, the director owned 18,989 shares of the company's</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2878423/delek-us-stock-not-a-buy-but-still-worth-holding-for-now?cid=CS-STOCKNEWSAPI-FT-analyst_blog|rank_focused-2878423</t>
+          <t>https://www.defenseworld.net/2026/03/08/shlomo-zohar-sells-22029-shares-of-delek-us-nysedk-stock.html</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-04 04:22:55</t>
+          <t>2026-03-08 05:14:51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fisher Asset Management LLC Sells 42,727 Shares of Delek US Holdings, Inc. $DK</t>
+          <t>Reuven Spiegel Sells 20,000 Shares of Delek US (NYSE:DK) Stock</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/fisher-asset-management-llc-sells-42727-shares-of-delek-20260304.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/reuven-spiegel-sells-20000-shares-of-delek-us-nysedk-20260308.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fisher Asset Management LLC decreased its holdings in shares of Delek US Holdings, Inc. (NYSE: DK) by 3.1% in the undefined quarter, according to the company in its most recent 13F filing with the Securities and Exchange Commission (SEC). The firm owned 1,340,572 shares of the oil and gas company's stock after selling</t>
+          <t>Delek US Holdings, Inc. (NYSE: DK - Get Free Report) EVP Reuven Spiegel sold 20,000 shares of the firm's stock in a transaction dated Wednesday, March 4th. The shares were sold at an average price of $42.84, for a total transaction of $856,800.00. Following the transaction, the executive vice president directly owned 48,530 shares in the</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/04/fisher-asset-management-llc-sells-42727-shares-of-delek-us-holdings-inc-dk.html</t>
+          <t>https://www.defenseworld.net/2026/03/08/reuven-spiegel-sells-20000-shares-of-delek-us-nysedk-stock.html</t>
         </is>
       </c>
     </row>
@@ -1140,37 +1140,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-02 08:30:30</t>
+          <t>2026-03-07 05:04:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Delek US Q4 Earnings &amp; Revenues Beat Estimates, Adjusted EBITDA Up Y/Y</t>
+          <t>Delek US Holdings, Inc. (NYSE:DK) Given Average Recommendation of “Hold” by Analysts</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-q4-earnings-revenues-beat-estimates-adjusted-ebitda-20260302.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-inc-nysedk-given-average-recommendation-of-20260307.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DK expects total crude throughput in the range of 212,000-247,000 bpd and total throughput in the band of 240,000-259,000 bpd for the first quarter of 2026.</t>
+          <t>Shares of Delek US Holdings, Inc. (NYSE: DK - Get Free Report) have been given a consensus recommendation of "Hold" by the fourteen ratings firms that are currently covering the stock, MarketBeat reports. Two equities research analysts have rated the stock with a sell rating, eight have issued a hold rating and four have assigned a</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2877221/delek-us-q4-earnings-revenues-beat-estimates-adjusted-ebitda-up-y-y?cid=CS-STOCKNEWSAPI-FT-analyst_blog|earnings_article-2877221</t>
+          <t>https://www.defenseworld.net/2026/03/07/delek-us-holdings-inc-nysedk-given-average-recommendation-of-hold-by-analysts.html</t>
         </is>
       </c>
     </row>
@@ -1182,37 +1182,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-02-27 19:21:36</t>
+          <t>2026-03-04 08:25:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Why Delek Holdings Stock Flew Almost 5% Higher on Friday</t>
+          <t>Delek US Stock: Not a Buy, But Still Worth Holding for Now</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-delek-holdings-stock-flew-almost-5-higher-on-20260227.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-stock-not-a-buy-but-still-worth-20260304.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The oil company's fourth quarter was a gusher, in several respects. It did especially well on the bottom line.</t>
+          <t>DK strengthens its financial position with strategic cash flow improvements and shareholder returns, but faces risks from regulatory challenges and refining market volatility.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.fool.com/investing/2026/02/27/why-delek-holdings-stock-flew-almost-5-higher-on-f/</t>
+          <t>https://www.zacks.com/stock/news/2878423/delek-us-stock-not-a-buy-but-still-worth-holding-for-now?cid=CS-STOCKNEWSAPI-FT-analyst_blog|rank_focused-2878423</t>
         </is>
       </c>
     </row>
@@ -1224,37 +1224,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-02-27 13:37:56</t>
+          <t>2026-03-04 04:22:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. (DK) Q4 2025 Earnings Call Transcript</t>
+          <t>Fisher Asset Management LLC Sells 42,727 Shares of Delek US Holdings, Inc. $DK</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-inc-dk-q4-2025-earnings-call-20260227.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/fisher-asset-management-llc-sells-42727-shares-of-delek-20260304.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. (DK) Q4 2025 Earnings Call Transcript</t>
+          <t>Fisher Asset Management LLC decreased its holdings in shares of Delek US Holdings, Inc. (NYSE: DK) by 3.1% in the undefined quarter, according to the company in its most recent 13F filing with the Securities and Exchange Commission (SEC). The firm owned 1,340,572 shares of the oil and gas company's stock after selling</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4876489-delek-us-holdings-inc-dk-q4-2025-earnings-call-transcript</t>
+          <t>https://www.defenseworld.net/2026/03/04/fisher-asset-management-llc-sells-42727-shares-of-delek-us-holdings-inc-dk.html</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-02-27 10:30:37</t>
+          <t>2026-03-02 08:30:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Delek US Holdings (DK) Q4 Earnings: How Key Metrics Compare to Wall Street Estimates</t>
+          <t>Delek US Q4 Earnings &amp; Revenues Beat Estimates, Adjusted EBITDA Up Y/Y</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-dk-q4-earnings-how-key-metrics-20260227.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-q4-earnings-revenues-beat-estimates-adjusted-ebitda-20260302.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Although the revenue and EPS for Delek US Holdings (DK) give a sense of how its business performed in the quarter ended December 2025, it might be worth considering how some key metrics compare with Wall Street estimates and the year-ago numbers.</t>
+          <t>DK expects total crude throughput in the range of 212,000-247,000 bpd and total throughput in the band of 240,000-259,000 bpd for the first quarter of 2026.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2876683/delek-us-holdings-dk-q4-earnings-how-key-metrics-compare-to-wall-street-estimates?cid=CS-STOCKNEWSAPI-FT-fundamental_analysis|nfm-2876683</t>
+          <t>https://www.zacks.com/stock/news/2877221/delek-us-q4-earnings-revenues-beat-estimates-adjusted-ebitda-up-y-y?cid=CS-STOCKNEWSAPI-FT-analyst_blog|earnings_article-2877221</t>
         </is>
       </c>
     </row>
@@ -1308,37 +1308,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-02-27 06:30:00</t>
+          <t>2026-02-27 19:21:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Delek US Holdings Reports Fourth Quarter 2025 Results</t>
+          <t>Why Delek Holdings Stock Flew Almost 5% Higher on Friday</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-reports-fourth-quarter-2025-results-20260227.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/why-delek-holdings-stock-flew-almost-5-higher-on-20260227.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>businesswire.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE: DK) (“Delek US”, “Company”) today announced financial results for its fourth quarter ended December 31, 2025. “2025 has been a transformational year for DK in improving its cash flow profile through successful implementation of the Enterprise Optimization Plan, reducing the costs of Inventory Intermediation Agreements, and progressing its economic separation with Delek Logistics,” said Avigal Soreq, President and Chief Executive.</t>
+          <t>The oil company's fourth quarter was a gusher, in several respects. It did especially well on the bottom line.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260227707703/en/Delek-US-Holdings-Reports-Fourth-Quarter-2025-Results/</t>
+          <t>https://www.fool.com/investing/2026/02/27/why-delek-holdings-stock-flew-almost-5-higher-on-f/</t>
         </is>
       </c>
     </row>
@@ -1350,37 +1350,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-02-27 02:01:07</t>
+          <t>2026-02-27 13:37:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Delek US Holdings Gears Up For Q4 Print; Here Are The Recent Forecast Changes From Wall Street's Most Accurate Analysts</t>
+          <t>Delek US Holdings, Inc. (DK) Q4 2025 Earnings Call Transcript</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-gears-up-for-q4-print-here-are-20260227.jpeg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-inc-dk-q4-2025-earnings-call-20260227.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>benzinga.com</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. (NYSE: DK) will release earnings for the fourth quarter before the opening bell on Friday, Feb. 27.</t>
+          <t>Delek US Holdings, Inc. (DK) Q4 2025 Earnings Call Transcript</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.benzinga.com/analyst-stock-ratings/price-target/26/02/50919320/delek-us-holdings-gears-up-for-q4-print-here-are-the-recent-forecast-changes-from-wall-streets-most-accurate-analysts</t>
+          <t>https://seekingalpha.com/article/4876489-delek-us-holdings-inc-dk-q4-2025-earnings-call-transcript</t>
         </is>
       </c>
     </row>
@@ -1392,37 +1392,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-02-24 05:02:45</t>
+          <t>2026-02-27 10:30:37</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Counterpoint Mutual Funds LLC Invests $2.83 Million in Delek US Holdings, Inc. $DK</t>
+          <t>Delek US Holdings (DK) Q4 Earnings: How Key Metrics Compare to Wall Street Estimates</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/counterpoint-mutual-funds-llc-invests-283-million-in-delek-20260224.jpeg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-dk-q4-earnings-how-key-metrics-20260227.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Counterpoint Mutual Funds LLC purchased a new position in Delek US Holdings, Inc. (NYSE: DK) during the undefined quarter, according to the company in its most recent filing with the Securities and Exchange Commission. The fund purchased 87,821 shares of the oil and gas company's stock, valued at approximately $2,834,000. Delek US makes</t>
+          <t>Although the revenue and EPS for Delek US Holdings (DK) give a sense of how its business performed in the quarter ended December 2025, it might be worth considering how some key metrics compare with Wall Street estimates and the year-ago numbers.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/02/24/counterpoint-mutual-funds-llc-invests-2-83-million-in-delek-us-holdings-inc-dk.html</t>
+          <t>https://www.zacks.com/stock/news/2876683/delek-us-holdings-dk-q4-earnings-how-key-metrics-compare-to-wall-street-estimates?cid=CS-STOCKNEWSAPI-FT-fundamental_analysis|nfm-2876683</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-02-18 20:00:00</t>
+          <t>2026-02-27 06:30:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. Announces Quarterly Dividend</t>
+          <t>Delek US Holdings Reports Fourth Quarter 2025 Results</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-inc-announces-quarterly-dividend-20260218.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-reports-fourth-quarter-2025-results-20260227.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE:DK) (“Delek”) today announced that its Board of Directors has approved a quarterly dividend of $0.255 per share, to be paid on March 9, 2026, to shareholders of record on March 2, 2026. About Delek US Holdings, Inc. Delek US Holdings, Inc. is a diversified downstream energy company with assets in petroleum refining, logistics, and pipelines. The refining assets consist primarily of refineries operated in Tyler and Big Spring, Texa.</t>
+          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE: DK) (“Delek US”, “Company”) today announced financial results for its fourth quarter ended December 31, 2025. “2025 has been a transformational year for DK in improving its cash flow profile through successful implementation of the Enterprise Optimization Plan, reducing the costs of Inventory Intermediation Agreements, and progressing its economic separation with Delek Logistics,” said Avigal Soreq, President and Chief Executive.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260218943172/en/Delek-US-Holdings-Inc.-Announces-Quarterly-Dividend/</t>
+          <t>https://www.businesswire.com/news/home/20260227707703/en/Delek-US-Holdings-Reports-Fourth-Quarter-2025-Results/</t>
         </is>
       </c>
     </row>
@@ -1476,37 +1476,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-02-12 16:39:22</t>
+          <t>2026-02-27 02:01:07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>This $17 Million Delek Exit Came Amid a Staggering One-Year Stock Surge</t>
+          <t>Delek US Holdings Gears Up For Q4 Print; Here Are The Recent Forecast Changes From Wall Street's Most Accurate Analysts</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/this-17-million-delek-exit-came-amid-a-staggering-20260212.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-gears-up-for-q4-print-here-are-20260227.jpeg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>benzinga.com</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Denver-based Towle &amp; Co. sold 536,133 shares of Delek US Holdings in the fourth quarter. The quarter-end position value fell by $17.30 million as a result.</t>
+          <t>Delek US Holdings, Inc. (NYSE: DK) will release earnings for the fourth quarter before the opening bell on Friday, Feb. 27.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.fool.com/coverage/filings/2026/02/12/this-usd17-million-delek-exit-came-amid-a-staggering-one-year-stock-surge/</t>
+          <t>https://www.benzinga.com/analyst-stock-ratings/price-target/26/02/50919320/delek-us-holdings-gears-up-for-q4-print-here-are-the-recent-forecast-changes-from-wall-streets-most-accurate-analysts</t>
         </is>
       </c>
     </row>
@@ -1518,37 +1518,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-01-30 16:30:00</t>
+          <t>2026-02-24 05:02:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Delek US Holdings to Host Fourth Quarter 2025 Conference Call on February 27th</t>
+          <t>Counterpoint Mutual Funds LLC Invests $2.83 Million in Delek US Holdings, Inc. $DK</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-to-host-fourth-quarter-2025-conference-call-20260130.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/counterpoint-mutual-funds-llc-invests-283-million-in-delek-20260224.jpeg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>businesswire.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE: DK) (“Delek US”) today announced that the Company intends to issue a press release summarizing fourth quarter 2025 results before the U.S. stock market opens on Friday, February 27, 2026. A conference call to discuss these results is scheduled to begin at 10:00 a.m. CT (11:00 a.m. ET) on Friday, February 27, 2026. The live broadcast of this conference call will be available online by going to www.DelekUS.com and clicking on the i.</t>
+          <t>Counterpoint Mutual Funds LLC purchased a new position in Delek US Holdings, Inc. (NYSE: DK) during the undefined quarter, according to the company in its most recent filing with the Securities and Exchange Commission. The fund purchased 87,821 shares of the oil and gas company's stock, valued at approximately $2,834,000. Delek US makes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260130957216/en/Delek-US-Holdings-to-Host-Fourth-Quarter-2025-Conference-Call-on-February-27th/</t>
+          <t>https://www.defenseworld.net/2026/02/24/counterpoint-mutual-funds-llc-invests-2-83-million-in-delek-us-holdings-inc-dk.html</t>
         </is>
       </c>
     </row>
@@ -1560,37 +1560,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-01-22 10:42:02</t>
+          <t>2026-02-18 20:00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fool - Investing News</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Kawa Capital Ditches Entire $6.5 Million Stake in Delek, According to Recent SEC Filing</t>
+          <t>Delek US Holdings, Inc. Announces Quarterly Dividend</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/kawa-capital-ditches-entire-65-million-stake-in-delek-according-20260122.jpeg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-inc-announces-quarterly-dividend-20260218.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>businesswire.com</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Delek US Holdings runs refineries, pipelines, and retail fuel outlets across the southern U.S., serving wholesale and consumer markets.</t>
+          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE:DK) (“Delek”) today announced that its Board of Directors has approved a quarterly dividend of $0.255 per share, to be paid on March 9, 2026, to shareholders of record on March 2, 2026. About Delek US Holdings, Inc. Delek US Holdings, Inc. is a diversified downstream energy company with assets in petroleum refining, logistics, and pipelines. The refining assets consist primarily of refineries operated in Tyler and Big Spring, Texa.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.fool.com/coverage/filings/2026/01/22/kawa-capital-ditches-entire-usd6-5-million-stake-in-delek-according-to-recent-sec-filing/</t>
+          <t>https://www.businesswire.com/news/home/20260218943172/en/Delek-US-Holdings-Inc.-Announces-Quarterly-Dividend/</t>
         </is>
       </c>
     </row>
@@ -1602,37 +1602,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-01-21 15:12:59</t>
+          <t>2026-02-12 16:39:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The Best Risk-Adjusted Way To Bet On Energy Right Now</t>
+          <t>This $17 Million Delek Exit Came Amid a Staggering One-Year Stock Surge</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/the-best-riskadjusted-way-to-bet-on-energy-right-20260121.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/this-17-million-delek-exit-came-amid-a-staggering-20260212.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>One energy investment is far less risky than investors think. Others look increasingly speculative despite strong headlines. This overlooked high-yielding opportunity keeps quietly compounding cash.</t>
+          <t>Denver-based Towle &amp; Co. sold 536,133 shares of Delek US Holdings in the fourth quarter. The quarter-end position value fell by $17.30 million as a result.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4861605-the-best-risk-adjusted-way-to-bet-on-energy-right-now</t>
+          <t>https://www.fool.com/coverage/filings/2026/02/12/this-usd17-million-delek-exit-came-amid-a-staggering-one-year-stock-surge/</t>
         </is>
       </c>
     </row>
@@ -1644,37 +1644,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-01-14 21:01:54</t>
+          <t>2026-01-30 16:30:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Delek: Sum Of The Parts Points To Substantial Upside</t>
+          <t>Delek US Holdings to Host Fourth Quarter 2025 Conference Call on February 27th</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-sum-of-the-parts-points-to-substantial-upside-20260114.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-to-host-fourth-quarter-2025-conference-call-20260130.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>businesswire.com</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Delek US Holdings is upgraded to 'strong buy' after a 25% pullback, offering compelling value and a significant margin of safety. DK benefits materially from EPA SRE relief, unlocking $400M in cash and a $200M ongoing annual cash flow boost. Refining margins have normalized to ~$25, but DK's cost-cutting and DKL stake underpin robust 2026 cash flow and buyback potential.</t>
+          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE: DK) (“Delek US”) today announced that the Company intends to issue a press release summarizing fourth quarter 2025 results before the U.S. stock market opens on Friday, February 27, 2026. A conference call to discuss these results is scheduled to begin at 10:00 a.m. CT (11:00 a.m. ET) on Friday, February 27, 2026. The live broadcast of this conference call will be available online by going to www.DelekUS.com and clicking on the i.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4859954-delek-sum-of-the-parts-points-to-substantial-upside-upgrade</t>
+          <t>https://www.businesswire.com/news/home/20260130957216/en/Delek-US-Holdings-to-Host-Fourth-Quarter-2025-Conference-Call-on-February-27th/</t>
         </is>
       </c>
     </row>
@@ -1686,37 +1686,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-01-13 14:43:00</t>
+          <t>2026-01-22 10:42:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Fool - Investing News</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Burney U.S. Factor Rotation ETF Buys Shares of Delek US Holdings Inc (NYSE:DK)</t>
+          <t>Kawa Capital Ditches Entire $6.5 Million Stake in Delek, According to Recent SEC Filing</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/burney-us-factor-rotation-etf-buys-shares-of-delek-20260113.png</t>
+          <t>https://images.financialmodelingprep.com/news/kawa-capital-ditches-entire-65-million-stake-in-delek-according-20260122.jpeg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>gurufocus.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Summary Burney U.S. Factor Rotation ETF initiated a new position in Delek US Holdings Inc, purchasing 130,529 shares to hold a total of 130,529 shares as of</t>
+          <t>Delek US Holdings runs refineries, pipelines, and retail fuel outlets across the southern U.S., serving wholesale and consumer markets.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/4109369/burney-us-factor-rotation-etf-buys-shares-of-delek-us-holdings-inc-nysedk</t>
+          <t>https://www.fool.com/coverage/filings/2026/01/22/kawa-capital-ditches-entire-usd6-5-million-stake-in-delek-according-to-recent-sec-filing/</t>
         </is>
       </c>
     </row>
@@ -1728,37 +1728,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-12-31 17:58:23</t>
+          <t>2026-01-21 15:12:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Delek Shares Surge 60% but One Fund Walked Away From a $15 Million Position</t>
+          <t>The Best Risk-Adjusted Way To Bet On Energy Right Now</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-shares-surge-60-but-one-fund-walked-away-20251231.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/the-best-riskadjusted-way-to-bet-on-energy-right-20260121.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Boston-based Callodine Capital Management sold 717,245 shares of Delek in the third quarter. The shares were worth about $15.19 million.</t>
+          <t>One energy investment is far less risky than investors think. Others look increasingly speculative despite strong headlines. This overlooked high-yielding opportunity keeps quietly compounding cash.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.fool.com/coverage/filings/2025/12/31/delek-shares-surge-60-but-one-fund-walked-away-from-a-usd15-million-position/</t>
+          <t>https://seekingalpha.com/article/4861605-the-best-risk-adjusted-way-to-bet-on-energy-right-now</t>
         </is>
       </c>
     </row>
@@ -1770,37 +1770,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-12-30 10:45:30</t>
+          <t>2026-01-14 21:01:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Still Holding Delek US Stock? Here's Why That's Justified</t>
+          <t>Delek: Sum Of The Parts Points To Substantial Upside</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/still-holding-delek-us-stock-heres-why-thats-justified-20251230.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-sum-of-the-parts-points-to-substantial-upside-20260114.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DK benefits from structural improvements, a solid balance sheet and growth in sour gas but faces challenges from rising costs, corporate complexity and fluctuating refining margins.</t>
+          <t>Delek US Holdings is upgraded to 'strong buy' after a 25% pullback, offering compelling value and a significant margin of safety. DK benefits materially from EPA SRE relief, unlocking $400M in cash and a $200M ongoing annual cash flow boost. Refining margins have normalized to ~$25, but DK's cost-cutting and DKL stake underpin robust 2026 cash flow and buyback potential.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2810194/still-holding-delek-us-stock-here-s-why-that-s-justified?cid=CS-STOCKNEWSAPI-FT-analyst_blog|rank_focused-2810194</t>
+          <t>https://seekingalpha.com/article/4859954-delek-sum-of-the-parts-points-to-substantial-upside-upgrade</t>
         </is>
       </c>
     </row>
@@ -1812,37 +1812,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-12-11 11:54:49</t>
+          <t>2026-01-13 14:43:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Delek Director Sells $281,300 in Shares After Regulatory Win Boosts Stock</t>
+          <t>Burney U.S. Factor Rotation ETF Buys Shares of Delek US Holdings Inc (NYSE:DK)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-director-sells-281300-in-shares-after-regulatory-win-20251211.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/burney-us-factor-rotation-etf-buys-shares-of-delek-20260113.png</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>gurufocus.com</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>The shares sold represented 4.25% of the executive's position. Delek is a diversified downstream energy company with operations across the southern United States.</t>
+          <t>Summary Burney U.S. Factor Rotation ETF initiated a new position in Delek US Holdings Inc, purchasing 130,529 shares to hold a total of 130,529 shares as of</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.fool.com/coverage/filings/2025/12/11/delek-director-sells-usd281-300-in-shares-after-regulatory-win-boosts-stock/</t>
+          <t>https://www.gurufocus.com/news/4109369/burney-us-factor-rotation-etf-buys-shares-of-delek-us-holdings-inc-nysedk</t>
         </is>
       </c>
     </row>
@@ -1854,37 +1854,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-12-07 04:21:01</t>
+          <t>2025-12-31 17:58:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Callodine Capital Management LP Purchases 42,584 Shares of Delek US Holdings, Inc. $DK</t>
+          <t>Delek Shares Surge 60% but One Fund Walked Away From a $15 Million Position</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/callodine-capital-management-lp-purchases-42584-shares-of-delek-20251207.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-shares-surge-60-but-one-fund-walked-away-20251231.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callodine Capital Management LP boosted its holdings in Delek US Holdings, Inc. (NYSE: DK) by 6.3% during the undefined quarter, according to its most recent 13F filing with the Securities and Exchange Commission. The institutional investor owned 717,245 shares of the oil and gas company's stock after acquiring an additional 42,584 shares during</t>
+          <t>Boston-based Callodine Capital Management sold 717,245 shares of Delek in the third quarter. The shares were worth about $15.19 million.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2025/12/07/callodine-capital-management-lp-purchases-42584-shares-of-delek-us-holdings-inc-dk.html</t>
+          <t>https://www.fool.com/coverage/filings/2025/12/31/delek-shares-surge-60-but-one-fund-walked-away-from-a-usd15-million-position/</t>
         </is>
       </c>
     </row>
@@ -1896,37 +1896,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-12-04 17:03:29</t>
+          <t>2025-12-30 10:45:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Delek Stock Up 200% Since April: What a New $4.8M Stake Signals Now</t>
+          <t>Still Holding Delek US Stock? Here's Why That's Justified</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-stock-up-200-since-april-what-a-new-20251204.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/still-holding-delek-us-stock-heres-why-thats-justified-20251230.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Florida-based GeoSphere Capital Management initiated a 150,000-share holding in Delek during the third quarter. The resulting position was worth about $4.8 million at quarter-end and represented 3.7% of 13F reportable assets under management.</t>
+          <t>DK benefits from structural improvements, a solid balance sheet and growth in sour gas but faces challenges from rising costs, corporate complexity and fluctuating refining margins.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.fool.com/coverage/filings/2025/12/04/geosphere-loads-up-dk-with-150k-shares-worth-48-million/</t>
+          <t>https://www.zacks.com/stock/news/2810194/still-holding-delek-us-stock-here-s-why-that-s-justified?cid=CS-STOCKNEWSAPI-FT-analyst_blog|rank_focused-2810194</t>
         </is>
       </c>
     </row>
@@ -1938,37 +1938,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-12-03 04:34:56</t>
+          <t>2025-12-11 11:54:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. $DK Shares Sold by Fisher Asset Management LLC</t>
+          <t>Delek Director Sells $281,300 in Shares After Regulatory Win Boosts Stock</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-inc-dk-shares-sold-by-fisher-asset-20251203.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-director-sells-281300-in-shares-after-regulatory-win-20251211.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fisher Asset Management LLC reduced its position in shares of Delek US Holdings, Inc. (NYSE: DK) by 13.7% in the undefined quarter, according to the company in its most recent disclosure with the Securities and Exchange Commission. The fund owned 1,383,299 shares of the oil and gas company's stock after selling 219,212 shares</t>
+          <t>The shares sold represented 4.25% of the executive's position. Delek is a diversified downstream energy company with operations across the southern United States.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2025/12/03/delek-us-holdings-inc-dk-shares-sold-by-fisher-asset-management-llc.html</t>
+          <t>https://www.fool.com/coverage/filings/2025/12/11/delek-director-sells-usd281-300-in-shares-after-regulatory-win-boosts-stock/</t>
         </is>
       </c>
     </row>
@@ -1980,37 +1980,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-11-24 11:08:05</t>
+          <t>2025-12-07 04:21:01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Delek US Holdings Stock: Not a Buy Yet, But Still Worth Holding On</t>
+          <t>Callodine Capital Management LP Purchases 42,584 Shares of Delek US Holdings, Inc. $DK</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-stock-not-a-buy-yet-but-20251124.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/callodine-capital-management-lp-purchases-42584-shares-of-delek-20251207.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DK shows margin strength, record throughput and midstream growth, but faces pressure from high debt, volatile spreads, capex needs and regulatory risks.</t>
+          <t>Callodine Capital Management LP boosted its holdings in Delek US Holdings, Inc. (NYSE: DK) by 6.3% during the undefined quarter, according to its most recent 13F filing with the Securities and Exchange Commission. The institutional investor owned 717,245 shares of the oil and gas company's stock after acquiring an additional 42,584 shares during</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2794880/delek-us-holdings-stock-not-a-buy-yet-but-still-worth-holding-on?cid=CS-STOCKNEWSAPI-FT-analyst_blog|rank_focused-2794880</t>
+          <t>https://www.defenseworld.net/2025/12/07/callodine-capital-management-lp-purchases-42584-shares-of-delek-us-holdings-inc-dk.html</t>
         </is>
       </c>
     </row>
@@ -2022,37 +2022,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2025-11-11 10:35:34</t>
+          <t>2025-12-04 17:03:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3 Oil Pipeline MLP Stocks to Watch Despite Industry Headwinds</t>
+          <t>Delek Stock Up 200% Since April: What a New $4.8M Stake Signals Now</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/3-oil-pipeline-mlp-stocks-to-watch-despite-industry-20251111.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-stock-up-200-since-april-what-a-new-20251204.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Conservative capital spending by upstream players and gradual shifting to renewables may hurt the demand for midstream players??? assets. DK, ET and PAA are surviving the industry challenges.</t>
+          <t>Florida-based GeoSphere Capital Management initiated a 150,000-share holding in Delek during the third quarter. The resulting position was worth about $4.8 million at quarter-end and represented 3.7% of 13F reportable assets under management.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/commentary/2789189/3-oil-pipeline-mlp-stocks-to-watch-despite-industry-headwinds?cid=CS-STOCKNEWSAPI-FT-industry_outlook-2789189</t>
+          <t>https://www.fool.com/coverage/filings/2025/12/04/geosphere-loads-up-dk-with-150k-shares-worth-48-million/</t>
         </is>
       </c>
     </row>
@@ -2064,37 +2064,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-11-11 09:15:59</t>
+          <t>2025-12-03 04:34:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Delek US Q3 Earnings &amp; Revenues Beat Estimates, Adjusted EBITDA Up Y/Y</t>
+          <t>Delek US Holdings, Inc. $DK Shares Sold by Fisher Asset Management LLC</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-q3-earnings-revenues-beat-estimates-adjusted-ebitda-20251111.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-inc-dk-shares-sold-by-fisher-asset-20251203.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DK expects total crude throughput in the range of 252,000-284,000 bpd and total throughput in the band of 271,000-303,000 bpd for the fourth quarter of 2025.</t>
+          <t>Fisher Asset Management LLC reduced its position in shares of Delek US Holdings, Inc. (NYSE: DK) by 13.7% in the undefined quarter, according to the company in its most recent disclosure with the Securities and Exchange Commission. The fund owned 1,383,299 shares of the oil and gas company's stock after selling 219,212 shares</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2789106/delek-us-q3-earnings-revenues-beat-estimates-adjusted-ebitda-up-y-y?cid=CS-STOCKNEWSAPI-FT-analyst_blog|earnings_article-2789106</t>
+          <t>https://www.defenseworld.net/2025/12/03/delek-us-holdings-inc-dk-shares-sold-by-fisher-asset-management-llc.html</t>
         </is>
       </c>
     </row>
@@ -2106,37 +2106,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2025-11-10 12:34:02</t>
+          <t>2025-11-24 11:08:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Delek US Holdings Analysts Boost Their Forecasts After Q3 Results</t>
+          <t>Delek US Holdings Stock: Not a Buy Yet, But Still Worth Holding On</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-analysts-boost-their-forecasts-after-q3-20251110.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-stock-not-a-buy-yet-but-20251124.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>benzinga.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. (NYSE:DK) reported better-than-expected third-quarter sales results on Friday.</t>
+          <t>DK shows margin strength, record throughput and midstream growth, but faces pressure from high debt, volatile spreads, capex needs and regulatory risks.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.benzinga.com/analyst-stock-ratings/price-target/25/11/48759947/delek-us-holdings-analysts-boost-their-forecasts-after-q3-results</t>
+          <t>https://www.zacks.com/stock/news/2794880/delek-us-holdings-stock-not-a-buy-yet-but-still-worth-holding-on?cid=CS-STOCKNEWSAPI-FT-analyst_blog|rank_focused-2794880</t>
         </is>
       </c>
     </row>
@@ -2148,37 +2148,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025-11-07 16:26:09</t>
+          <t>2025-11-11 10:35:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. (DK) Q3 2025 Earnings Call Transcript</t>
+          <t>3 Oil Pipeline MLP Stocks to Watch Despite Industry Headwinds</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-inc-dk-q3-2025-earnings-call-transcript-20251107.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/3-oil-pipeline-mlp-stocks-to-watch-despite-industry-20251111.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. ( DK ) Q3 2025 Earnings Call November 7, 2025 10:30 AM EST Company Participants Robert Wright - Senior VP, Deputy CFO &amp; Chief Accounting Officer Avigal Soreq - President, CEO &amp; Director Joseph Israel - Executive VP and President of Refining &amp; Renewables Mark Hobbs - Executive VP &amp; CFO Mohit Bhardwaj - Senior Vice President of Strategy &amp; Growth Conference Call Participants Douglas George Blyth Leggate - Wolfe Research, LLC Manav Gupta - UBS Investment Bank, Research Division Vikram Bagri - Citigroup Inc., Research Division Alexa Petrick - Goldman Sachs Group, Inc., Research Division Paul Cheng - Scotiabank Global Banking and Markets, Research Division Jason Gabelman - TD Cowen, Research Division Presentation Operator Thank you for standing by. My name is Jayle, and I'll be your conference operator today.</t>
+          <t>Conservative capital spending by upstream players and gradual shifting to renewables may hurt the demand for midstream players??? assets. DK, ET and PAA are surviving the industry challenges.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4840603-delek-us-holdings-inc-dk-q3-2025-earnings-call-transcript</t>
+          <t>https://www.zacks.com/commentary/2789189/3-oil-pipeline-mlp-stocks-to-watch-despite-industry-headwinds?cid=CS-STOCKNEWSAPI-FT-industry_outlook-2789189</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025-11-07 10:31:04</t>
+          <t>2025-11-11 09:15:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2200,12 +2200,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Delek US Holdings (DK) Q3 Earnings: How Key Metrics Compare to Wall Street Estimates</t>
+          <t>Delek US Q3 Earnings &amp; Revenues Beat Estimates, Adjusted EBITDA Up Y/Y</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-dk-q3-earnings-how-key-metrics-20251107.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-q3-earnings-revenues-beat-estimates-adjusted-ebitda-20251111.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>The headline numbers for Delek US Holdings (DK) give insight into how the company performed in the quarter ended September 2025, but it may be worthwhile to compare some of its key metrics to Wall Street estimates and the year-ago actuals.</t>
+          <t>DK expects total crude throughput in the range of 252,000-284,000 bpd and total throughput in the band of 271,000-303,000 bpd for the fourth quarter of 2025.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2787742/delek-us-holdings-dk-q3-earnings-how-key-metrics-compare-to-wall-street-estimates?cid=CS-STOCKNEWSAPI-FT-fundamental_analysis|nfm-2787742</t>
+          <t>https://www.zacks.com/stock/news/2789106/delek-us-q3-earnings-revenues-beat-estimates-adjusted-ebitda-up-y-y?cid=CS-STOCKNEWSAPI-FT-analyst_blog|earnings_article-2789106</t>
         </is>
       </c>
     </row>
@@ -2232,37 +2232,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025-11-07 06:30:00</t>
+          <t>2025-11-10 12:34:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Delek US Holdings Reports Third Quarter 2025 Results</t>
+          <t>Delek US Holdings Analysts Boost Their Forecasts After Q3 Results</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-reports-third-quarter-2025-results-20251107.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-analysts-boost-their-forecasts-after-q3-20251110.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>businesswire.com</t>
+          <t>benzinga.com</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE: DK) (“Delek US”, "Company") today announced financial results for its third quarter ended September 30, 2025. “We continue to make progress in achieving our Sum of the Parts goals and improving the overall profitability of the company as highlighted by a strong EOP contribution in 3Q'25,” said Avigal Soreq, President and Chief Executive Officer of Delek US. “Our EOP efforts, which are exceeding previous guidance, and clarity on S.</t>
+          <t>Delek US Holdings, Inc. (NYSE:DK) reported better-than-expected third-quarter sales results on Friday.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20251107386370/en/Delek-US-Holdings-Reports-Third-Quarter-2025-Results/</t>
+          <t>https://www.benzinga.com/analyst-stock-ratings/price-target/25/11/48759947/delek-us-holdings-analysts-boost-their-forecasts-after-q3-results</t>
         </is>
       </c>
     </row>
@@ -2274,37 +2274,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2025-11-04 11:56:08</t>
+          <t>2025-11-07 16:26:09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Q3 Energy Earnings: 4 Stocks That Could Surpass Forecasts</t>
+          <t>Delek US Holdings, Inc. (DK) Q3 2025 Earnings Call Transcript</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/q3-energy-earnings-4-stocks-that-could-surpass-forecasts-20251104.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-inc-dk-q3-2025-earnings-call-transcript-20251107.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Energy stocks like CNQ, DK, CLMT and NOG have the potential to deliver better-than-expected Q3 earnings.</t>
+          <t>Delek US Holdings, Inc. ( DK ) Q3 2025 Earnings Call November 7, 2025 10:30 AM EST Company Participants Robert Wright - Senior VP, Deputy CFO &amp; Chief Accounting Officer Avigal Soreq - President, CEO &amp; Director Joseph Israel - Executive VP and President of Refining &amp; Renewables Mark Hobbs - Executive VP &amp; CFO Mohit Bhardwaj - Senior Vice President of Strategy &amp; Growth Conference Call Participants Douglas George Blyth Leggate - Wolfe Research, LLC Manav Gupta - UBS Investment Bank, Research Division Vikram Bagri - Citigroup Inc., Research Division Alexa Petrick - Goldman Sachs Group, Inc., Research Division Paul Cheng - Scotiabank Global Banking and Markets, Research Division Jason Gabelman - TD Cowen, Research Division Presentation Operator Thank you for standing by. My name is Jayle, and I'll be your conference operator today.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2784741/q3-energy-earnings-4-stocks-that-could-surpass-forecasts?cid=CS-STOCKNEWSAPI-FT-earnings_esp-2784741</t>
+          <t>https://seekingalpha.com/article/4840603-delek-us-holdings-inc-dk-q3-2025-earnings-call-transcript</t>
         </is>
       </c>
     </row>
@@ -2316,37 +2316,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2025-11-02 21:42:12</t>
+          <t>2025-11-07 10:31:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Delek US Holdings: Upside Expected As EPA Actions Are A Game-Changer</t>
+          <t>Delek US Holdings (DK) Q3 Earnings: How Key Metrics Compare to Wall Street Estimates</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-upside-expected-as-epa-actions-are-20251102.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-dk-q3-earnings-how-key-metrics-20251107.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Delek US Holdings has surged over 140% in the past year, benefiting from improved refining conditions and favorable regulatory changes. DK's unique position as a small refinery owner makes it a prime beneficiary of recent EPA approvals for small refinery exemptions (SREs). The stock's upside is now more moderate, with a 12-18% gain potential including dividends, prompting a rating change from 'strong buy' to 'buy.'</t>
+          <t>The headline numbers for Delek US Holdings (DK) give insight into how the company performed in the quarter ended September 2025, but it may be worthwhile to compare some of its key metrics to Wall Street estimates and the year-ago actuals.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4836792-delek-us-holdings-upside-expected-as-epa-actions-game-changer</t>
+          <t>https://www.zacks.com/stock/news/2787742/delek-us-holdings-dk-q3-earnings-how-key-metrics-compare-to-wall-street-estimates?cid=CS-STOCKNEWSAPI-FT-fundamental_analysis|nfm-2787742</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2025-10-29 17:30:00</t>
+          <t>2025-11-07 06:30:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Delek US Holdings, Inc. Announces Quarterly Dividend</t>
+          <t>Delek US Holdings Reports Third Quarter 2025 Results</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-inc-announces-quarterly-dividend-20251029.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-reports-third-quarter-2025-results-20251107.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE:DK) (“Delek”) today announced that its Board of Directors has approved a quarterly dividend of $0.255 per share, to be paid on November 17, 2025, to shareholders as of record on November 10, 2025. About Delek US Holdings, Inc. Delek US Holdings, Inc. is a diversified downstream energy company with assets in petroleum refining, logistics, pipelines, and renewable fuels. The refining assets consist primarily of refineries operated i.</t>
+          <t>BRENTWOOD, Tenn.--(BUSINESS WIRE)--Delek US Holdings, Inc. (NYSE: DK) (“Delek US”, "Company") today announced financial results for its third quarter ended September 30, 2025. “We continue to make progress in achieving our Sum of the Parts goals and improving the overall profitability of the company as highlighted by a strong EOP contribution in 3Q'25,” said Avigal Soreq, President and Chief Executive Officer of Delek US. “Our EOP efforts, which are exceeding previous guidance, and clarity on S.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20251029247641/en/Delek-US-Holdings-Inc.-Announces-Quarterly-Dividend/</t>
+          <t>https://www.businesswire.com/news/home/20251107386370/en/Delek-US-Holdings-Reports-Third-Quarter-2025-Results/</t>
         </is>
       </c>
     </row>
@@ -2400,37 +2400,79 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2025-10-23 10:43:34</t>
+          <t>2025-11-04 11:56:08</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Zacks Investment Research</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Q3 Energy Earnings: 4 Stocks That Could Surpass Forecasts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://images.financialmodelingprep.com/news/q3-energy-earnings-4-stocks-that-could-surpass-forecasts-20251104.jpg</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>zacks.com</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Energy stocks like CNQ, DK, CLMT and NOG have the potential to deliver better-than-expected Q3 earnings.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.zacks.com/stock/news/2784741/q3-energy-earnings-4-stocks-that-could-surpass-forecasts?cid=CS-STOCKNEWSAPI-FT-earnings_esp-2784741</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-11-02 21:42:12</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>10%+ Yielding Stocks Too Cheap To Ignore Right Now</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>https://images.financialmodelingprep.com/news/10-yielding-stocks-too-cheap-to-ignore-right-now-20251023.jpg</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Delek US Holdings: Upside Expected As EPA Actions Are A Game-Changer</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://images.financialmodelingprep.com/news/delek-us-holdings-upside-expected-as-epa-actions-are-20251102.jpg</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>seekingalpha.com</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>10%+ yielding stocks tend to be risky. However, there are some sustainable 10%+ yields out there that also offer attractive capital appreciation potential. I share two 10%+ yields that are too cheap to ignore right now.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://seekingalpha.com/article/4832440-10-percent-yielding-stocks-too-cheap-to-ignore-right-now</t>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Delek US Holdings has surged over 140% in the past year, benefiting from improved refining conditions and favorable regulatory changes. DK's unique position as a small refinery owner makes it a prime beneficiary of recent EPA approvals for small refinery exemptions (SREs). The stock's upside is now more moderate, with a 12-18% gain potential including dividends, prompting a rating change from 'strong buy' to 'buy.'</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://seekingalpha.com/article/4836792-delek-us-holdings-upside-expected-as-epa-actions-game-changer</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2540,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-18 04:05:15</t>
+          <t>2026-04-25 07:24:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2508,12 +2550,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lbp Am Sa Reduces Position in Marathon Petroleum Corporation $MPC</t>
+          <t>Calamos Advisors LLC Cuts Stock Holdings in Marathon Petroleum Corporation $MPC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/lbp-am-sa-reduces-position-in-marathon-petroleum-corporation-20260418.png</t>
+          <t>https://images.financialmodelingprep.com/news/calamos-advisors-llc-cuts-stock-holdings-in-marathon-petroleum-20260425.png</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2523,12 +2565,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lbp Am Sa trimmed its holdings in shares of Marathon Petroleum Corporation (NYSE: MPC) by 70.5% during the fourth quarter, according to the company in its most recent Form 13F filing with the SEC. The fund owned 25,881 shares of the oil and gas company's stock after selling 61,725 shares during the quarter.</t>
+          <t>Calamos Advisors LLC lowered its stake in Marathon Petroleum Corporation (NYSE: MPC) by 6.8% during the undefined quarter, according to the company in its most recent disclosure with the Securities and Exchange Commission. The firm owned 313,204 shares of the oil and gas company's stock after selling 23,002 shares during the period. Calamos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/04/18/lbp-am-sa-reduces-position-in-marathon-petroleum-corporation-mpc.html</t>
+          <t>https://www.defenseworld.net/2026/04/25/calamos-advisors-llc-cuts-stock-holdings-in-marathon-petroleum-corporation-mpc.html</t>
         </is>
       </c>
     </row>
@@ -2540,37 +2582,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-17 17:02:33</t>
+          <t>2026-04-24 18:46:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Low-Stress 8% Yields I Would Bet My Retirement On</t>
+          <t>Marathon Petroleum (MPC) Rises Higher Than Market: Key Facts</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/lowstress-8-yields-i-would-bet-my-retirement-on-20260417.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-rises-higher-than-market-key-facts-20260424.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Most retirees are forced to choose between yield and safety — discover two rare investments that deliver 8%+ income without forcing that painful tradeoff. One is a bond ETF that actually grows its dividend (something almost no bond fund can claim), and the other is a cash-flow machine with 12.5% guided distribution growth. In a volatile market where most high yields are getting crushed, these two holdings have the balance sheet strength, inflation protection, and structural advantages to keep paying and growing.</t>
+          <t>Marathon Petroleum (MPC) closed at $224.14 in the latest trading session, marking a +1.37% move from the prior day.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4891696-low-stress-8-percent-yields-i-would-bet-my-retirement-on</t>
+          <t>https://www.zacks.com/stock/news/2907935/marathon-petroleum-mpc-rises-higher-than-market-key-facts?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_6-2907935</t>
         </is>
       </c>
     </row>
@@ -2582,37 +2624,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-16 18:46:19</t>
+          <t>2026-04-23 15:29:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Fool - Investing News</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Why Marathon Petroleum (MPC) Outpaced the Stock Market Today</t>
+          <t>Here's Why the Price of Oil is Likely to Remain High Even After the War Ends</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-marathon-petroleum-mpc-outpaced-the-stock-market-today-20260416.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/heres-why-the-price-of-oil-is-likely-to-20260423.jpeg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>The latest trading day saw Marathon Petroleum (MPC) settling at $226.24, representing a +1.44% change from its previous close.</t>
+          <t>Massive war-related damage to oil infrastructure in the Middle East could keep oil prices elevated for months.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2901888/why-marathon-petroleum-mpc-outpaced-the-stock-market-today</t>
+          <t>https://www.fool.com/investing/2026/04/23/why-price-oil-likely-remain-high-iran-war-xle/</t>
         </is>
       </c>
     </row>
@@ -2624,37 +2666,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-16 10:47:11</t>
+          <t>2026-04-23 09:30:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24/7 Wall Street</t>
+          <t>GlobeNewsWire</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3 Energy Stocks For Steady Passive Income</t>
+          <t>Trust Stamp and Partisia partner with Digital Platformer to Combine Biometric Tokenisation and MPC Technologies to Advance Decentralised Identity Solutions in Japan and the Region</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/3-energy-stocks-for-steady-passive-income-20260416.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/trust-stamp-and-partisia-partner-with-digital-platformer-to-20260423.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>247wallst.com</t>
+          <t>globenewswire.com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Energy prices surged above $100 per barrel in April 2026, with WTI crude sitting at $100.72, near the 96.7th percentile of its 12-month range.</t>
+          <t>A signed commercial agreement brings together Trust Stamp's advanced biometric identity capabilities and Partisia's Multi-Party Computation platform as the core technology stack underpinning Digital Platformer's next-generation decentralised identity solutions A signed commercial agreement brings together Trust Stamp's advanced biometric identity capabilities and Partisia's Multi-Party Computation platform as the core technology stack underpinning Digital Platformer's next-generation decentralised identity solutions</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://247wallst.com/investing/2026/04/16/3-energy-stocks-for-steady-passive-income/</t>
+          <t>https://www.globenewswire.com/news-release/2026/04/23/3280071/0/en/Trust-Stamp-and-Partisia-partner-with-Digital-Platformer-to-Combine-Biometric-Tokenisation-and-MPC-Technologies-to-Advance-Decentralised-Identity-Solutions-in-Japan-and-the-Region.html</t>
         </is>
       </c>
     </row>
@@ -2666,37 +2708,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-16 10:41:16</t>
+          <t>2026-04-23 04:07:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Why Marathon Petroleum (MPC) is a Top Value Stock for the Long-Term</t>
+          <t>Cwm LLC Boosts Stock Holdings in Marathon Petroleum Corporation $MPC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-marathon-petroleum-mpc-is-a-top-value-stock-20260416.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/cwm-llc-boosts-stock-holdings-in-marathon-petroleum-corporation-20260423.png</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Wondering how to pick strong, market-beating stocks for your investment portfolio? Look no further than the Zacks Style Scores.</t>
+          <t>Cwm LLC lifted its position in Marathon Petroleum Corporation (NYSE: MPC) by 19.2% in the undefined quarter, according to the company in its most recent 13F filing with the Securities and Exchange Commission (SEC). The institutional investor owned 24,116 shares of the oil and gas company's stock after acquiring an additional 3,882 shares</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2901427/why-marathon-petroleum-mpc-is-a-top-value-stock-for-the-long-term</t>
+          <t>https://www.defenseworld.net/2026/04/23/cwm-llc-boosts-stock-holdings-in-marathon-petroleum-corporation-mpc.html</t>
         </is>
       </c>
     </row>
@@ -2708,37 +2750,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-04-15 12:20:13</t>
+          <t>2026-04-18 04:05:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Why Oil Refiners Are the Real Winners of $100 Oil Prices</t>
+          <t>Lbp Am Sa Reduces Position in Marathon Petroleum Corporation $MPC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-oil-refiners-are-the-real-winners-of-100-20260415.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/lbp-am-sa-reduces-position-in-marathon-petroleum-corporation-20260418.png</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>marketbeat.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Consumers can easily relate to the impact of crude oil prices, which topped $100 on April 13 but have since fallen back. It means higher prices for gasoline and diesel.</t>
+          <t>Lbp Am Sa trimmed its holdings in shares of Marathon Petroleum Corporation (NYSE: MPC) by 70.5% during the fourth quarter, according to the company in its most recent Form 13F filing with the SEC. The fund owned 25,881 shares of the oil and gas company's stock after selling 61,725 shares during the quarter.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.marketbeat.com/originals/why-oil-refiners-are-the-real-winners-of-100-oil-prices/</t>
+          <t>https://www.defenseworld.net/2026/04/18/lbp-am-sa-reduces-position-in-marathon-petroleum-corporation-mpc.html</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2792,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-04-15 07:00:00</t>
+          <t>2026-04-17 17:02:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2760,12 +2802,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5 Best Energy Stocks That Can Outperform After The Strait Opens</t>
+          <t>Low-Stress 8% Yields I Would Bet My Retirement On</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/5-best-energy-stocks-that-can-outperform-after-the-20260415.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/lowstress-8-yields-i-would-bet-my-retirement-on-20260417.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2775,12 +2817,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>The "crack spread" is the difference between the cost of crude oil and the price of refined products like gasoline and diesel, representing a refiner's profit margin from processing crude. When oil prices peak and begin to stabilize or decline, refined product prices often remain relatively firm, allowing margins to expand. Therefore, refiners can outperform even after oil prices have rolled over, making them well worth a look amid the ongoing geopolitical headline noise.</t>
+          <t>Most retirees are forced to choose between yield and safety — discover two rare investments that deliver 8%+ income without forcing that painful tradeoff. One is a bond ETF that actually grows its dividend (something almost no bond fund can claim), and the other is a cash-flow machine with 12.5% guided distribution growth. In a volatile market where most high yields are getting crushed, these two holdings have the balance sheet strength, inflation protection, and structural advantages to keep paying and growing.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4890710-5-best-energy-stocks-that-can-outperform-after-the-strait-opens</t>
+          <t>https://seekingalpha.com/article/4891696-low-stress-8-percent-yields-i-would-bet-my-retirement-on</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2834,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04-14 10:01:10</t>
+          <t>2026-04-16 18:46:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2802,12 +2844,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation (MPC) is Attracting Investor Attention: Here is What You Should Know</t>
+          <t>Why Marathon Petroleum (MPC) Outpaced the Stock Market Today</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corporation-mpc-is-attracting-investor-attention-here-20260414.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/why-marathon-petroleum-mpc-outpaced-the-stock-market-today-20260416.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2817,12 +2859,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) has received quite a bit of attention from Zacks.com users lately. Therefore, it is wise to be aware of the facts that can impact the stock's prospects.</t>
+          <t>The latest trading day saw Marathon Petroleum (MPC) settling at $226.24, representing a +1.44% change from its previous close.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2899567/marathon-petroleum-corporation-mpc-is-attracting-investor-attention-here-is-what-you-should-know</t>
+          <t>https://www.zacks.com/stock/news/2901888/why-marathon-petroleum-mpc-outpaced-the-stock-market-today</t>
         </is>
       </c>
     </row>
@@ -2834,37 +2876,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-04-09 10:32:17</t>
+          <t>2026-04-16 10:47:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>24/7 Wall Street</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Is Marathon Petroleum (MPC) a Buy as Wall Street Analysts Look Optimistic?</t>
+          <t>3 Energy Stocks For Steady Passive Income</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/is-marathon-petroleum-mpc-a-buy-as-wall-street-20260409.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/3-energy-stocks-for-steady-passive-income-20260416.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>247wallst.com</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>The recommendations of Wall Street analysts are often relied on by investors when deciding whether to buy, sell, or hold a stock. Media reports about these brokerage-firm-employed (or sell-side) analysts changing their ratings often affect a stock's price.</t>
+          <t>Energy prices surged above $100 per barrel in April 2026, with WTI crude sitting at $100.72, near the 96.7th percentile of its 12-month range.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2897254/is-marathon-petroleum-mpc-a-buy-as-wall-street-analysts-look-optimistic</t>
+          <t>https://247wallst.com/investing/2026/04/16/3-energy-stocks-for-steady-passive-income/</t>
         </is>
       </c>
     </row>
@@ -2876,37 +2918,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-04-09 07:35:24</t>
+          <t>2026-04-16 10:41:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>24/7 Wall Street</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Marathon and Valero Have Surged: Is the Party Over or Just Getting Started?</t>
+          <t>Why Marathon Petroleum (MPC) is a Top Value Stock for the Long-Term</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-and-valero-have-surged-is-the-party-over-20260409.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/why-marathon-petroleum-mpc-is-a-top-value-stock-20260416.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>247wallst.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (NYSE: MPC) and Valero Energy (NYSE: VLO) have both staged remarkable recoveries.</t>
+          <t>Wondering how to pick strong, market-beating stocks for your investment portfolio? Look no further than the Zacks Style Scores.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://247wallst.com/investing/2026/04/09/marathon-and-valero-have-surged-is-the-party-over-or-just-getting-started/</t>
+          <t>https://www.zacks.com/stock/news/2901427/why-marathon-petroleum-mpc-is-a-top-value-stock-for-the-long-term</t>
         </is>
       </c>
     </row>
@@ -2918,37 +2960,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-04-08 18:46:23</t>
+          <t>2026-04-15 12:20:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) Stock Drops Despite Market Gains: Important Facts to Note</t>
+          <t>Why Oil Refiners Are the Real Winners of $100 Oil Prices</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-stock-drops-despite-market-gains-important-20260408.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/why-oil-refiners-are-the-real-winners-of-100-20260415.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>marketbeat.com</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>In the latest trading session, Marathon Petroleum (MPC) closed at $231.98, marking a -5.48% move from the previous day.</t>
+          <t>Consumers can easily relate to the impact of crude oil prices, which topped $100 on April 13 but have since fallen back. It means higher prices for gasoline and diesel.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2896868/marathon-petroleum-mpc-stock-drops-despite-market-gains-important-facts-to-note</t>
+          <t>https://www.marketbeat.com/originals/why-oil-refiners-are-the-real-winners-of-100-oil-prices/</t>
         </is>
       </c>
     </row>
@@ -2960,37 +3002,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-04-08 13:11:14</t>
+          <t>2026-04-15 07:00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Investopedia</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Not Everything Is Rallying Today. These Stocks Are Sliding After the US-Iran Ceasefire Deal</t>
+          <t>5 Best Energy Stocks That Can Outperform After The Strait Opens</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/not-everything-is-rallying-today-these-stocks-are-sliding-20260408.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/5-best-energy-stocks-that-can-outperform-after-the-20260415.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>investopedia.com</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Markets are rallying Wednesday on the news of a two-week ceasefire in Iran, but some stocks are bucking the trend.</t>
+          <t>The "crack spread" is the difference between the cost of crude oil and the price of refined products like gasoline and diesel, representing a refiner's profit margin from processing crude. When oil prices peak and begin to stabilize or decline, refined product prices often remain relatively firm, allowing margins to expand. Therefore, refiners can outperform even after oil prices have rolled over, making them well worth a look amid the ongoing geopolitical headline noise.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.investopedia.com/not-everything-is-rallying-today-these-stocks-are-sliding-after-the-us-iran-ceasefire-deal-11945309</t>
+          <t>https://seekingalpha.com/article/4890710-5-best-energy-stocks-that-can-outperform-after-the-strait-opens</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3044,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-04-08 06:21:06</t>
+          <t>2026-04-14 10:01:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3012,12 +3054,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Best Value Stocks to Buy for April 8th</t>
+          <t>Marathon Petroleum Corporation (MPC) is Attracting Investor Attention: Here is What You Should Know</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/best-value-stocks-to-buy-for-april-8th-20260408.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corporation-mpc-is-attracting-investor-attention-here-20260414.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3027,12 +3069,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SM, BP and MPC made it to the Zacks Rank #1 (Strong Buy) value stocks list on April 8th, 2026.</t>
+          <t>Marathon Petroleum (MPC) has received quite a bit of attention from Zacks.com users lately. Therefore, it is wise to be aware of the facts that can impact the stock's prospects.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/commentary/2896147/best-value-stocks-to-buy-for-april-8th</t>
+          <t>https://www.zacks.com/stock/news/2899567/marathon-petroleum-corporation-mpc-is-attracting-investor-attention-here-is-what-you-should-know</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3086,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-04-07 11:01:24</t>
+          <t>2026-04-09 10:32:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3054,12 +3096,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Is Marathon Petroleum (MPC) Outperforming Other Oils-Energy Stocks This Year?</t>
+          <t>Is Marathon Petroleum (MPC) a Buy as Wall Street Analysts Look Optimistic?</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/is-marathon-petroleum-mpc-outperforming-other-oilsenergy-stocks-this-20260407.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/is-marathon-petroleum-mpc-a-buy-as-wall-street-20260409.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3069,12 +3111,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Here is how Marathon Petroleum (MPC) and Pedevco Corp. (PED) have performed compared to their sector so far this year.</t>
+          <t>The recommendations of Wall Street analysts are often relied on by investors when deciding whether to buy, sell, or hold a stock. Media reports about these brokerage-firm-employed (or sell-side) analysts changing their ratings often affect a stock's price.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2895547/is-marathon-petroleum-mpc-outperforming-other-oils-energy-stocks-this-year</t>
+          <t>https://www.zacks.com/stock/news/2897254/is-marathon-petroleum-mpc-a-buy-as-wall-street-analysts-look-optimistic</t>
         </is>
       </c>
     </row>
@@ -3086,37 +3128,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-04-07 09:34:38</t>
+          <t>2026-04-09 07:35:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>24/7 Wall Street</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Energy Stocks: Winners And Losers At The Beginning Of Q2 2026</t>
+          <t>Marathon and Valero Have Surged: Is the Party Over or Just Getting Started?</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/energy-stocks-winners-and-losers-at-the-beginning-of-20260407.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-and-valero-have-surged-is-the-party-over-20260409.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>247wallst.com</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Q1 2026 was an exceptional quarter for energy stocks thanks to war in the Middle East, but Q2 2026 is not guaranteed to step in its footsteps. Energy prices can go higher and push the sector higher, but they do not have to if the U.S. can neutralize Iran's ability to project force. While energy stocks are benefiting from the fighting in the short term, it may actually come back to hurt them in the long run.</t>
+          <t>Marathon Petroleum (NYSE: MPC) and Valero Energy (NYSE: VLO) have both staged remarkable recoveries.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4888905-energy-stocks-winners-and-losers-at-the-beginning-of-q2-2026</t>
+          <t>https://247wallst.com/investing/2026/04/09/marathon-and-valero-have-surged-is-the-party-over-or-just-getting-started/</t>
         </is>
       </c>
     </row>
@@ -3128,37 +3170,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-04-05 14:00:20</t>
+          <t>2026-04-08 18:46:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Forbes</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Why Oil Prices Just Soared 70% Despite A U.S. Supply Glut. Here Are The Surprise Winners And Losers</t>
+          <t>Marathon Petroleum (MPC) Stock Drops Despite Market Gains: Important Facts to Note</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-oil-prices-just-soared-70-despite-a-us-20260405.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-stock-drops-despite-market-gains-important-20260408.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>forbes.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The U.S. produces more energy than it consumes. Yet the price of oil has soared about 70% since Feb. 28 when the U.S. and Israel attacked Iran, according to LiteFinance.</t>
+          <t>In the latest trading session, Marathon Petroleum (MPC) closed at $231.98, marking a -5.48% move from the previous day.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.forbes.com/sites/petercohan/2026/04/05/why-oil-prices-just-soared-70-despite-a-us-supply-glut-here-are-the-surprise-winners-and-losers/</t>
+          <t>https://www.zacks.com/stock/news/2896868/marathon-petroleum-mpc-stock-drops-despite-market-gains-important-facts-to-note</t>
         </is>
       </c>
     </row>
@@ -3170,37 +3212,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-04-02 18:45:53</t>
+          <t>2026-04-08 13:11:14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Investopedia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) Beats Stock Market Upswing: What Investors Need to Know</t>
+          <t>Not Everything Is Rallying Today. These Stocks Are Sliding After the US-Iran Ceasefire Deal</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-beats-stock-market-upswing-what-investors-20260402.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/not-everything-is-rallying-today-these-stocks-are-sliding-20260408.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>investopedia.com</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) concluded the recent trading session at $241.56, signifying a +1.43% move from its prior day's close.</t>
+          <t>Markets are rallying Wednesday on the news of a two-week ceasefire in Iran, but some stocks are bucking the trend.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2894035/marathon-petroleum-mpc-beats-stock-market-upswing-what-investors-need-to-know</t>
+          <t>https://www.investopedia.com/not-everything-is-rallying-today-these-stocks-are-sliding-after-the-us-iran-ceasefire-deal-11945309</t>
         </is>
       </c>
     </row>
@@ -3212,37 +3254,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-04-01 15:00:00</t>
+          <t>2026-04-08 06:21:06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Only 1 Sector Is Up Over the Past Month</t>
+          <t>Best Value Stocks to Buy for April 8th</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/only-1-sector-is-up-over-the-past-month-20260401.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/best-value-stocks-to-buy-for-april-8th-20260408.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The sharp spike in oil and gasoline prices is very good for energy companies. Even after its recent run-up, the sector looks likely to have a very good 2026.</t>
+          <t>SM, BP and MPC made it to the Zacks Rank #1 (Strong Buy) value stocks list on April 8th, 2026.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.fool.com/investing/2026/04/01/only-1-sector-is-up-over-the-past-month/</t>
+          <t>https://www.zacks.com/commentary/2896147/best-value-stocks-to-buy-for-april-8th</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3296,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:46</t>
+          <t>2026-04-07 11:01:24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3264,12 +3306,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation (MPC) Is a Trending Stock: Facts to Know Before Betting on It</t>
+          <t>Is Marathon Petroleum (MPC) Outperforming Other Oils-Energy Stocks This Year?</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corporation-mpc-is-a-trending-stock-facts-20260401.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/is-marathon-petroleum-mpc-outperforming-other-oilsenergy-stocks-this-20260407.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3279,12 +3321,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zacks.com users have recently been watching Marathon Petroleum (MPC) quite a bit. Thus, it is worth knowing the facts that could determine the stock's prospects.</t>
+          <t>Here is how Marathon Petroleum (MPC) and Pedevco Corp. (PED) have performed compared to their sector so far this year.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2892792/marathon-petroleum-corporation-mpc-is-a-trending-stock-facts-to-know-before-betting-on-it?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|most_searched_stocks-2892792</t>
+          <t>https://www.zacks.com/stock/news/2895547/is-marathon-petroleum-mpc-outperforming-other-oils-energy-stocks-this-year</t>
         </is>
       </c>
     </row>
@@ -3296,37 +3338,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-31 10:41:19</t>
+          <t>2026-04-07 09:34:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Here's Why Marathon Petroleum (MPC) is a Strong Value Stock</t>
+          <t>Energy Stocks: Winners And Losers At The Beginning Of Q2 2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/heres-why-marathon-petroleum-mpc-is-a-strong-value-20260331.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/energy-stocks-winners-and-losers-at-the-beginning-of-20260407.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Wondering how to pick strong, market-beating stocks for your investment portfolio? Look no further than the Zacks Style Scores.</t>
+          <t>Q1 2026 was an exceptional quarter for energy stocks thanks to war in the Middle East, but Q2 2026 is not guaranteed to step in its footsteps. Energy prices can go higher and push the sector higher, but they do not have to if the U.S. can neutralize Iran's ability to project force. While energy stocks are benefiting from the fighting in the short term, it may actually come back to hurt them in the long run.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2892176/here-s-why-marathon-petroleum-mpc-is-a-strong-value-stock?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_value_score-2892176</t>
+          <t>https://seekingalpha.com/article/4888905-energy-stocks-winners-and-losers-at-the-beginning-of-q2-2026</t>
         </is>
       </c>
     </row>
@@ -3338,37 +3380,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-31 08:16:48</t>
+          <t>2026-04-05 14:00:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Forbes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>U.S. Refiners: Recent Trends And Relative Value</t>
+          <t>Why Oil Prices Just Soared 70% Despite A U.S. Supply Glut. Here Are The Surprise Winners And Losers</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/us-refiners-recent-trends-and-relative-value-20260331.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/why-oil-prices-just-soared-70-despite-a-us-20260405.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>forbes.com</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Refiners are  most profitable when oil prices are elevated, gasoline demand remains robust, and refiner margins are high. Refiner margins are dependent on crack spread - the difference between the value of the gasoline and diesel produced and the input cost of crude oil. The 3-2-1 crack spread has already nearly doubled this year from $0.65 to $1.65 per gallon of fuel.</t>
+          <t>The U.S. produces more energy than it consumes. Yet the price of oil has soared about 70% since Feb. 28 when the U.S. and Israel attacked Iran, according to LiteFinance.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4887380-us-refiners-recent-trends-and-relative-value</t>
+          <t>https://www.forbes.com/sites/petercohan/2026/04/05/why-oil-prices-just-soared-70-despite-a-us-supply-glut-here-are-the-surprise-winners-and-losers/</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3422,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-03-27 18:46:29</t>
+          <t>2026-04-02 18:45:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3390,12 +3432,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) Ascends While Market Falls: Some Facts to Note</t>
+          <t>Marathon Petroleum (MPC) Beats Stock Market Upswing: What Investors Need to Know</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-ascends-while-market-falls-some-facts-20260327.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-beats-stock-market-upswing-what-investors-20260402.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3405,12 +3447,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>In the latest trading session, Marathon Petroleum (MPC) closed at $251.91, marking a +1.45% move from the previous day.</t>
+          <t>Marathon Petroleum (MPC) concluded the recent trading session at $241.56, signifying a +1.43% move from its prior day's close.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2891182/marathon-petroleum-mpc-ascends-while-market-falls-some-facts-to-note?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_6-2891182</t>
+          <t>https://www.zacks.com/stock/news/2894035/marathon-petroleum-mpc-beats-stock-market-upswing-what-investors-need-to-know</t>
         </is>
       </c>
     </row>
@@ -3422,37 +3464,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-27 10:51:14</t>
+          <t>2026-04-01 15:00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) is a Top-Ranked Momentum Stock: Should You Buy?</t>
+          <t>Only 1 Sector Is Up Over the Past Month</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-is-a-topranked-momentum-stock-should-20260327.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/only-1-sector-is-up-over-the-past-month-20260401.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Wondering how to pick strong, market-beating stocks for your investment portfolio? Look no further than the Zacks Style Scores.</t>
+          <t>The sharp spike in oil and gasoline prices is very good for energy companies. Even after its recent run-up, the sector looks likely to have a very good 2026.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2890884/marathon-petroleum-mpc-is-a-top-ranked-momentum-stock-should-you-buy?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_momentum_score-2890884</t>
+          <t>https://www.fool.com/investing/2026/04/01/only-1-sector-is-up-over-the-past-month/</t>
         </is>
       </c>
     </row>
@@ -3464,37 +3506,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-27 04:19:18</t>
+          <t>2026-04-01 10:01:46</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Czech National Bank Increases Stock Holdings in Marathon Petroleum Corporation $MPC</t>
+          <t>Marathon Petroleum Corporation (MPC) Is a Trending Stock: Facts to Know Before Betting on It</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/czech-national-bank-increases-stock-holdings-in-marathon-petroleum-20260327.png</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corporation-mpc-is-a-trending-stock-facts-20260401.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Czech National Bank boosted its stake in shares of Marathon Petroleum Corporation (NYSE: MPC) by 2.7% during the undefined quarter, according to its most recent 13F filing with the SEC. The firm owned 79,265 shares of the oil and gas company's stock after buying an additional 2,050 shares during the period. Czech National</t>
+          <t>Zacks.com users have recently been watching Marathon Petroleum (MPC) quite a bit. Thus, it is worth knowing the facts that could determine the stock's prospects.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/27/czech-national-bank-increases-stock-holdings-in-marathon-petroleum-corporation-mpc.html</t>
+          <t>https://www.zacks.com/stock/news/2892792/marathon-petroleum-corporation-mpc-is-a-trending-stock-facts-to-know-before-betting-on-it?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|most_searched_stocks-2892792</t>
         </is>
       </c>
     </row>
@@ -3506,37 +3548,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-25 10:45:49</t>
+          <t>2026-03-31 10:41:19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>24/7 Wall Street</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Why Raymond James Sees Marathon Petroleum Reaching $270</t>
+          <t>Here's Why Marathon Petroleum (MPC) is a Strong Value Stock</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-raymond-james-sees-marathon-petroleum-reaching-270-20260325.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/heres-why-marathon-petroleum-mpc-is-a-strong-value-20260331.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>247wallst.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corp. (NYSE:MPC) has been a standout energy sector performer, with shares up nearly 25% over the past month and nearly 48% year to date.</t>
+          <t>Wondering how to pick strong, market-beating stocks for your investment portfolio? Look no further than the Zacks Style Scores.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://247wallst.com/investing/2026/03/25/why-raymond-james-sees-marathon-petroleum-reaching-270/</t>
+          <t>https://www.zacks.com/stock/news/2892176/here-s-why-marathon-petroleum-mpc-is-a-strong-value-stock?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_value_score-2892176</t>
         </is>
       </c>
     </row>
@@ -3548,37 +3590,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-24 13:39:20</t>
+          <t>2026-03-31 08:16:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Acquires The Home Depot, Inc. (NYSE:HD) Stock</t>
+          <t>U.S. Refiners: Recent Trends And Relative Value</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-acquires-the-home-depot-inc-nysehd-20260324.gif</t>
+          <t>https://images.financialmodelingprep.com/news/us-refiners-recent-trends-and-relative-value-20260331.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently bought shares of The Home Depot, Inc. (NYSE: HD). In a filing disclosed on March 20th, the Representative disclosed that they had bought between $1,001 and $15,000 in Home Depot stock on March 12th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account.</t>
+          <t>Refiners are  most profitable when oil prices are elevated, gasoline demand remains robust, and refiner margins are high. Refiner margins are dependent on crack spread - the difference between the value of the gasoline and diesel produced and the input cost of crude oil. The 3-2-1 crack spread has already nearly doubled this year from $0.65 to $1.65 per gallon of fuel.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/24/rep-david-taylor-acquires-the-home-depot-inc-nysehd-stock.html</t>
+          <t>https://seekingalpha.com/article/4887380-us-refiners-recent-trends-and-relative-value</t>
         </is>
       </c>
     </row>
@@ -3590,37 +3632,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-03-24 12:56:04</t>
+          <t>2026-03-27 18:46:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Why Marathon Petroleum Stock Is Breaking Out To Fresh All-Time Highs Today</t>
+          <t>Marathon Petroleum (MPC) Ascends While Market Falls: Some Facts to Note</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-marathon-petroleum-stock-is-breaking-out-to-fresh-20260324.jpeg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-ascends-while-market-falls-some-facts-20260327.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>feeds.benzinga.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corp (NYSE: MPC) shares are trading higher Tuesday afternoon, hitting all-time highs as fresh escalation in the U.S.-Israel-Iran conflict puts more geopolitical risk back into global energy markets.</t>
+          <t>In the latest trading session, Marathon Petroleum (MPC) closed at $251.91, marking a +1.45% move from the previous day.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.benzinga.com/trading-ideas/movers/26/03/51438754/why-marathon-petroleum-stock-is-breaking-out-to-fresh-all-time-highs-today</t>
+          <t>https://www.zacks.com/stock/news/2891182/marathon-petroleum-mpc-ascends-while-market-falls-some-facts-to-note?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_6-2891182</t>
         </is>
       </c>
     </row>
@@ -3632,37 +3674,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-03-23 17:09:58</t>
+          <t>2026-03-27 10:51:14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>24/7 Wall Street</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3 Oil Stocks Set to Deliver 50%+ Returns in 2026</t>
+          <t>Marathon Petroleum (MPC) is a Top-Ranked Momentum Stock: Should You Buy?</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/3-oil-stocks-set-to-deliver-50-returns-in-20260323.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-is-a-topranked-momentum-stock-should-20260327.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>247wallst.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Oil prices have soared by over 50% in the past month, with WTI crude trading sideways in the $90 to $100 band.</t>
+          <t>Wondering how to pick strong, market-beating stocks for your investment portfolio? Look no further than the Zacks Style Scores.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://247wallst.com/investing/2026/03/23/3-oil-stocks-set-to-deliver-50-returns-in-2026/</t>
+          <t>https://www.zacks.com/stock/news/2890884/marathon-petroleum-mpc-is-a-top-ranked-momentum-stock-should-you-buy?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_momentum_score-2890884</t>
         </is>
       </c>
     </row>
@@ -3674,37 +3716,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-03-23 16:15:00</t>
+          <t>2026-03-27 04:19:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PRNewsWire</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corp. to Report First-Quarter Financial Results on May 5, 2026</t>
+          <t>Czech National Bank Increases Stock Holdings in Marathon Petroleum Corporation $MPC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corp-to-report-firstquarter-financial-results-on-20260323.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/czech-national-bank-increases-stock-holdings-in-marathon-petroleum-20260327.png</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>FINDLAY, Ohio, March 23, 2026 /PRNewswire/ -- Marathon Petroleum Corp. (NYSE: MPC) will host a conference call on Tuesday, May 5, 2026, at 11 a.m. EDT to discuss 2026 first-quarter financial results.</t>
+          <t>Czech National Bank boosted its stake in shares of Marathon Petroleum Corporation (NYSE: MPC) by 2.7% during the undefined quarter, according to its most recent 13F filing with the SEC. The firm owned 79,265 shares of the oil and gas company's stock after buying an additional 2,050 shares during the period. Czech National</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/marathon-petroleum-corp-to-report-first-quarter-financial-results-on-may-5-2026-302722440.html</t>
+          <t>https://www.defenseworld.net/2026/03/27/czech-national-bank-increases-stock-holdings-in-marathon-petroleum-corporation-mpc.html</t>
         </is>
       </c>
     </row>
@@ -3716,37 +3758,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-03-18 10:02:38</t>
+          <t>2026-03-25 10:45:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>24/7 Wall Street</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Investors Heavily Search Marathon Petroleum Corporation (MPC): Here is What You Need to Know</t>
+          <t>Why Raymond James Sees Marathon Petroleum Reaching $270</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/investors-heavily-search-marathon-petroleum-corporation-mpc-here-is-20260318.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/why-raymond-james-sees-marathon-petroleum-reaching-270-20260325.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>247wallst.com</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) has been one of the stocks most watched by Zacks.com users lately. So, it is worth exploring what lies ahead for the stock.</t>
+          <t>Marathon Petroleum Corp. (NYSE:MPC) has been a standout energy sector performer, with shares up nearly 25% over the past month and nearly 48% year to date.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2885773/investors-heavily-search-marathon-petroleum-corporation-mpc-here-is-what-you-need-to-know?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|most_searched_stocks-2885773</t>
+          <t>https://247wallst.com/investing/2026/03/25/why-raymond-james-sees-marathon-petroleum-reaching-270/</t>
         </is>
       </c>
     </row>
@@ -3758,37 +3800,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-03-17 13:10:56</t>
+          <t>2026-03-24 13:39:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>I'm Buying These 2 High-Conviction Deeply Discounted Picks Yielding 5-7%</t>
+          <t>Rep. David Taylor Acquires The Home Depot, Inc. (NYSE:HD) Stock</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/im-buying-these-2-highconviction-deeply-discounted-picks-yielding-20260317.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-acquires-the-home-depot-inc-nysehd-20260324.gif</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I love buying stocks that trade at huge discounts yet have a high probability of being long-term winners. These picks pay me to wait thanks to attractive yields and big buybacks. I detail the major catalyst that the market is overlooking for Rayonier and why Energy Transfer is very underrated.</t>
+          <t>Representative David Taylor (Republican-Ohio) recently bought shares of The Home Depot, Inc. (NYSE: HD). In a filing disclosed on March 20th, the Representative disclosed that they had bought between $1,001 and $15,000 in Home Depot stock on March 12th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4883230-im-buying-these-two-high-conviction-deeply-discounted-picks-yielding-5-7-percent</t>
+          <t>https://www.defenseworld.net/2026/03/24/rep-david-taylor-acquires-the-home-depot-inc-nysehd-stock.html</t>
         </is>
       </c>
     </row>
@@ -3800,37 +3842,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-03-17 05:22:42</t>
+          <t>2026-03-24 12:56:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>California Public Employees Retirement System Has $114.97 Million Stake in Marathon Petroleum Corporation $MPC</t>
+          <t>Why Marathon Petroleum Stock Is Breaking Out To Fresh All-Time Highs Today</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/california-public-employees-retirement-system-has-11497-million-stake-in-20260317.png</t>
+          <t>https://images.financialmodelingprep.com/news/why-marathon-petroleum-stock-is-breaking-out-to-fresh-20260324.jpeg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>feeds.benzinga.com</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>California Public Employees Retirement System grew its stake in shares of Marathon Petroleum Corporation (NYSE: MPC) by 3.0% during the third quarter, according to the company in its most recent disclosure with the Securities and Exchange Commission. The fund owned 596,488 shares of the oil and gas company's stock after buying an additional</t>
+          <t>Marathon Petroleum Corp (NYSE: MPC) shares are trading higher Tuesday afternoon, hitting all-time highs as fresh escalation in the U.S.-Israel-Iran conflict puts more geopolitical risk back into global energy markets.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/17/california-public-employees-retirement-system-has-114-97-million-stake-in-marathon-petroleum-corporation-mpc.html</t>
+          <t>https://www.benzinga.com/trading-ideas/movers/26/03/51438754/why-marathon-petroleum-stock-is-breaking-out-to-fresh-all-time-highs-today</t>
         </is>
       </c>
     </row>
@@ -3842,37 +3884,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-03-17 04:02:52</t>
+          <t>2026-03-23 17:09:58</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>24/7 Wall Street</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia Increases Holdings in Marathon Petroleum Corporation $MPC</t>
+          <t>3 Oil Stocks Set to Deliver 50%+ Returns in 2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/bank-of-nova-scotia-increases-holdings-in-marathon-petroleum-corporation-20260317.png</t>
+          <t>https://images.financialmodelingprep.com/news/3-oil-stocks-set-to-deliver-50-returns-in-20260323.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>247wallst.com</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia grew its holdings in Marathon Petroleum Corporation (NYSE: MPC) by 81.8% in the undefined quarter, according to the company in its most recent filing with the SEC. The firm owned 170,589 shares of the oil and gas company's stock after buying an additional 76,762 shares during the quarter. Bank</t>
+          <t>Oil prices have soared by over 50% in the past month, with WTI crude trading sideways in the $90 to $100 band.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/17/bank-of-nova-scotia-increases-holdings-in-marathon-petroleum-corporation-mpc.html</t>
+          <t>https://247wallst.com/investing/2026/03/23/3-oil-stocks-set-to-deliver-50-returns-in-2026/</t>
         </is>
       </c>
     </row>
@@ -3884,37 +3926,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-03-17 01:00:00</t>
+          <t>2026-03-23 16:15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>PRNewsWire</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PGIM Jennison Energy Infrastructure Fund Q4 2025: Who Moved The Needle</t>
+          <t>Marathon Petroleum Corp. to Report First-Quarter Financial Results on May 5, 2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pgim-jennison-energy-infrastructure-fund-q4-2025-who-moved-20260317.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corp-to-report-firstquarter-financial-results-on-may-20260323.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Though relatively flat for the fourth quarter, the Fund outperformed the -1.6% return of the Alerian Midstream Energy Select Index. MPLX's high yield and compelling dividend growth above many peers continue to attract investors in a choppy market. DT Midstream benefits from increasing power demand and despite recent macro events, the call on natural gas remains unchanged.</t>
+          <t>FINDLAY, Ohio, March 23, 2026 /PRNewswire/ -- Marathon Petroleum Corp. (NYSE: MPC) will host a conference call on Tuesday, May 5, 2026, at 11 a.m. EDT to discuss 2026 first-quarter financial results.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4882993-pgim-jennison-energy-infrastructure-fund-q4-2025-who-moved-the-needle</t>
+          <t>https://www.prnewswire.com/news-releases/marathon-petroleum-corp-to-report-first-quarter-financial-results-on-may-5-2026-302722440.html</t>
         </is>
       </c>
     </row>
@@ -3926,37 +3968,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-03-16 03:27:05</t>
+          <t>2026-03-18 10:02:38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ameriprise Financial Inc. Sells 537,272 Shares of Marathon Petroleum Corporation $MPC</t>
+          <t>Investors Heavily Search Marathon Petroleum Corporation (MPC): Here is What You Need to Know</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/ameriprise-financial-inc-sells-537272-shares-of-marathon-petroleum-20260316.png</t>
+          <t>https://images.financialmodelingprep.com/news/investors-heavily-search-marathon-petroleum-corporation-mpc-here-is-20260318.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ameriprise Financial Inc. cut its position in Marathon Petroleum Corporation (NYSE: MPC) by 19.3% in the third quarter, according to the company in its most recent disclosure with the Securities and Exchange Commission (SEC). The institutional investor owned 2,244,349 shares of the oil and gas company's stock after selling 537,272 shares during the</t>
+          <t>Marathon Petroleum (MPC) has been one of the stocks most watched by Zacks.com users lately. So, it is worth exploring what lies ahead for the stock.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/16/ameriprise-financial-inc-sells-537272-shares-of-marathon-petroleum-corporation-mpc.html</t>
+          <t>https://www.zacks.com/stock/news/2885773/investors-heavily-search-marathon-petroleum-corporation-mpc-here-is-what-you-need-to-know?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|most_searched_stocks-2885773</t>
         </is>
       </c>
     </row>
@@ -3968,7 +4010,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-03-15 09:59:11</t>
+          <t>2026-03-17 13:10:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3978,12 +4020,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>My 6-8% Yielding Money Machine Choices For Early Retirement</t>
+          <t>I'm Buying These 2 High-Conviction Deeply Discounted Picks Yielding 5-7%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/my-68-yielding-money-machine-choices-for-early-retirement-20260315.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/im-buying-these-2-highconviction-deeply-discounted-picks-yielding-20260317.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3993,12 +4035,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Discover two high-yielding securities that offer a powerful combination of current income and long-term inflation protection. Learn why these specific investments are uniquely positioned to thrive in an AI-driven economy. Explore the robust distribution growth and defensive characteristics that make these "money machines" ideal for early retirees.</t>
+          <t>I love buying stocks that trade at huge discounts yet have a high probability of being long-term winners. These picks pay me to wait thanks to attractive yields and big buybacks. I detail the major catalyst that the market is overlooking for Rayonier and why Energy Transfer is very underrated.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4882528-my-6-8-percent-yielding-money-machine-choices-for-early-retirement</t>
+          <t>https://seekingalpha.com/article/4883230-im-buying-these-two-high-conviction-deeply-discounted-picks-yielding-5-7-percent</t>
         </is>
       </c>
     </row>
@@ -4010,37 +4052,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-03-12 18:46:39</t>
+          <t>2026-03-17 05:22:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) Ascends While Market Falls: Some Facts to Note</t>
+          <t>California Public Employees Retirement System Has $114.97 Million Stake in Marathon Petroleum Corporation $MPC</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-ascends-while-market-falls-some-facts-20260312.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/california-public-employees-retirement-system-has-11497-million-stake-in-20260317.png</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>In the latest trading session, Marathon Petroleum (MPC) closed at $230.09, marking a +1.48% move from the previous day.</t>
+          <t>California Public Employees Retirement System grew its stake in shares of Marathon Petroleum Corporation (NYSE: MPC) by 3.0% during the third quarter, according to the company in its most recent disclosure with the Securities and Exchange Commission. The fund owned 596,488 shares of the oil and gas company's stock after buying an additional</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2883390/marathon-petroleum-mpc-ascends-while-market-falls-some-facts-to-note?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_6-2883390</t>
+          <t>https://www.defenseworld.net/2026/03/17/california-public-employees-retirement-system-has-114-97-million-stake-in-marathon-petroleum-corporation-mpc.html</t>
         </is>
       </c>
     </row>
@@ -4052,37 +4094,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-12 10:40:56</t>
+          <t>2026-03-17 04:02:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Why Marathon Petroleum (MPC) is a Top Value Stock for the Long-Term</t>
+          <t>Bank of Nova Scotia Increases Holdings in Marathon Petroleum Corporation $MPC</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-marathon-petroleum-mpc-is-a-top-value-stock-20260312.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/bank-of-nova-scotia-increases-holdings-in-marathon-petroleum-corporation-20260317.png</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Whether you're a value, growth, or momentum investor, finding strong stocks becomes easier with the Zacks Style Scores, a top feature of the Zacks Premium research service.</t>
+          <t>Bank of Nova Scotia grew its holdings in Marathon Petroleum Corporation (NYSE: MPC) by 81.8% in the undefined quarter, according to the company in its most recent filing with the SEC. The firm owned 170,589 shares of the oil and gas company's stock after buying an additional 76,762 shares during the quarter. Bank</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2882990/why-marathon-petroleum-mpc-is-a-top-value-stock-for-the-long-term?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_value_score-2882990</t>
+          <t>https://www.defenseworld.net/2026/03/17/bank-of-nova-scotia-increases-holdings-in-marathon-petroleum-corporation-mpc.html</t>
         </is>
       </c>
     </row>
@@ -4094,37 +4136,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-12 03:54:58</t>
+          <t>2026-03-17 01:00:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Banque Cantonale Vaudoise Purchases 6,625 Shares of Marathon Petroleum Corporation $MPC</t>
+          <t>PGIM Jennison Energy Infrastructure Fund Q4 2025: Who Moved The Needle</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/banque-cantonale-vaudoise-purchases-6625-shares-of-marathon-petroleum-corporation-20260312.png</t>
+          <t>https://images.financialmodelingprep.com/news/pgim-jennison-energy-infrastructure-fund-q4-2025-who-moved-20260317.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Banque Cantonale Vaudoise boosted its position in Marathon Petroleum Corporation (NYSE: MPC) by 308.4% during the third quarter, according to its most recent 13F filing with the Securities and Exchange Commission. The fund owned 8,773 shares of the oil and gas company's stock after buying an additional 6,625 shares during the quarter. Banque</t>
+          <t>Though relatively flat for the fourth quarter, the Fund outperformed the -1.6% return of the Alerian Midstream Energy Select Index. MPLX's high yield and compelling dividend growth above many peers continue to attract investors in a choppy market. DT Midstream benefits from increasing power demand and despite recent macro events, the call on natural gas remains unchanged.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/12/banque-cantonale-vaudoise-purchases-6625-shares-of-marathon-petroleum-corporation-mpc.html</t>
+          <t>https://seekingalpha.com/article/4882993-pgim-jennison-energy-infrastructure-fund-q4-2025-who-moved-the-needle</t>
         </is>
       </c>
     </row>
@@ -4136,37 +4178,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-11 15:20:07</t>
+          <t>2026-03-16 03:27:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Surges After IEA Plans 400M-Barrel Release</t>
+          <t>Ameriprise Financial Inc. Sells 537,272 Shares of Marathon Petroleum Corporation $MPC</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-surges-after-iea-plans-400mbarrel-release-20260311.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/ameriprise-financial-inc-sells-537272-shares-of-marathon-petroleum-20260316.png</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>benzinga.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corp (NYSE: MPC) shares are trading higher on Wednesday after the International Energy Agency announced that its 32 member countries will make 400 million barrels of emergency oil reserves available to the market.</t>
+          <t>Ameriprise Financial Inc. cut its position in Marathon Petroleum Corporation (NYSE: MPC) by 19.3% in the third quarter, according to the company in its most recent disclosure with the Securities and Exchange Commission (SEC). The institutional investor owned 2,244,349 shares of the oil and gas company's stock after selling 537,272 shares during the</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.benzinga.com/trading-ideas/movers/26/03/51197319/marathon-petroleum-surges-after-iea-plans-400m-barrel-release</t>
+          <t>https://www.defenseworld.net/2026/03/16/ameriprise-financial-inc-sells-537272-shares-of-marathon-petroleum-corporation-mpc.html</t>
         </is>
       </c>
     </row>
@@ -4178,37 +4220,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-11 11:50:00</t>
+          <t>2026-03-15 09:59:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Schaeffers Research</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Stocks Drifting Lower as Oil Prices Resume Rally</t>
+          <t>My 6-8% Yielding Money Machine Choices For Early Retirement</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/stocks-drifting-lower-as-oil-prices-resume-rally-20260311.png</t>
+          <t>https://images.financialmodelingprep.com/news/my-68-yielding-money-machine-choices-for-early-retirement-20260315.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>schaeffersresearch.com</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>The Dow is down triple digits, but the Nasdaq and S&amp;P 500 are clinging to gains as oil prices resume their climb</t>
+          <t>Discover two high-yielding securities that offer a powerful combination of current income and long-term inflation protection. Learn why these specific investments are uniquely positioned to thrive in an AI-driven economy. Explore the robust distribution growth and defensive characteristics that make these "money machines" ideal for early retirees.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.schaeffersresearch.com/content/ezines/2026/03/11/stocks-drifting-lower-as-oil-prices-resume-rally</t>
+          <t>https://seekingalpha.com/article/4882528-my-6-8-percent-yielding-money-machine-choices-for-early-retirement</t>
         </is>
       </c>
     </row>
@@ -4220,37 +4262,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-11 11:25:54</t>
+          <t>2026-03-12 18:46:39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>24/7 Wall Street</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Refiners Are Quiet Winners in 2026: Wall Street's Signals Are Hard to Ignore</t>
+          <t>Marathon Petroleum (MPC) Ascends While Market Falls: Some Facts to Note</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/refiners-are-quiet-winners-in-2026-wall-streets-signals-20260311.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-ascends-while-market-falls-some-facts-20260312.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>247wallst.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Institutional money is moving into U.S. refiners with conviction, and the earnings data backs it up.</t>
+          <t>In the latest trading session, Marathon Petroleum (MPC) closed at $230.09, marking a +1.48% move from the previous day.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://247wallst.com/investing/2026/03/11/refiners-are-quiet-winners-in-2026-wall-streets-signals-are-hard-to-ignore/</t>
+          <t>https://www.zacks.com/stock/news/2883390/marathon-petroleum-mpc-ascends-while-market-falls-some-facts-to-note?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_6-2883390</t>
         </is>
       </c>
     </row>
@@ -4262,37 +4304,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-11 10:54:59</t>
+          <t>2026-03-12 10:40:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>24/7 Wall Street</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Trump Hails First New U.S. Refinery in 50 Years — Why Smart Investors Are Choosing Marathon Petroleum Instead</t>
+          <t>Why Marathon Petroleum (MPC) is a Top Value Stock for the Long-Term</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/trump-hails-first-new-us-refinery-in-50-years-20260311.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/why-marathon-petroleum-mpc-is-a-top-value-stock-20260312.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>247wallst.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) operates 13 refineries with 3 million barrels per day of crude distillation capacity, including the largest single refinery in the U.S. at Galveston Bay with 631,000 barrels per day capacity optimized for Permian and Eagle Ford shale oil. The company delivered $13.22 adjusted EPS in 2025, with refining margins expanding 44% year-over-year to $18.65 per barrel, and returned $4.5 billion to shareholders through dividends and buybacks.</t>
+          <t>Whether you're a value, growth, or momentum investor, finding strong stocks becomes easier with the Zacks Style Scores, a top feature of the Zacks Premium research service.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://247wallst.com/investing/2026/03/11/trump-hails-first-new-u-s-refinery-in-50-years-why-smart-investors-are-choosing-marathon-petroleum-instead/</t>
+          <t>https://www.zacks.com/stock/news/2882990/why-marathon-petroleum-mpc-is-a-top-value-stock-for-the-long-term?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_value_score-2882990</t>
         </is>
       </c>
     </row>
@@ -4304,37 +4346,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-11 10:50:21</t>
+          <t>2026-03-12 03:54:58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Here's Why Marathon Petroleum (MPC) is a Strong Momentum Stock</t>
+          <t>Banque Cantonale Vaudoise Purchases 6,625 Shares of Marathon Petroleum Corporation $MPC</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/heres-why-marathon-petroleum-mpc-is-a-strong-momentum-20260311.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/banque-cantonale-vaudoise-purchases-6625-shares-of-marathon-petroleum-corporation-20260312.png</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Wondering how to pick strong, market-beating stocks for your investment portfolio? Look no further than the Zacks Style Scores.</t>
+          <t>Banque Cantonale Vaudoise boosted its position in Marathon Petroleum Corporation (NYSE: MPC) by 308.4% during the third quarter, according to its most recent 13F filing with the Securities and Exchange Commission. The fund owned 8,773 shares of the oil and gas company's stock after buying an additional 6,625 shares during the quarter. Banque</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2882300/here-s-why-marathon-petroleum-mpc-is-a-strong-momentum-stock?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_momentum_score-2882300</t>
+          <t>https://www.defenseworld.net/2026/03/12/banque-cantonale-vaudoise-purchases-6625-shares-of-marathon-petroleum-corporation-mpc.html</t>
         </is>
       </c>
     </row>
@@ -4346,37 +4388,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-11 07:38:05</t>
+          <t>2026-03-11 15:20:07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Five things to know about Iran's new supreme leader, Mojtaba Khamenei</t>
+          <t>Marathon Petroleum Surges After IEA Plans 400M-Barrel Release</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/five-things-to-know-about-irans-new-supreme-leader-20260311.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-surges-after-iea-plans-400mbarrel-release-20260311.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>benzinga.com</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Mojtaba Khamenei has been appointed Iran's new Supreme Leader, taking over from his late father, Ayatollah Ali Khamenei. More hardline and conservative than his father, Khameini has already drawn criticism from U.S. President Donald Trump, who expressed "disappointment" in his selection.</t>
+          <t>Marathon Petroleum Corp (NYSE: MPC) shares are trading higher on Wednesday after the International Energy Agency announced that its 32 member countries will make 400 million barrels of emergency oil reserves available to the market.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/03/11/five-things-to-know-about-irans-new-supreme-leader-mojtaba-khamenei.html</t>
+          <t>https://www.benzinga.com/trading-ideas/movers/26/03/51197319/marathon-petroleum-surges-after-iea-plans-400m-barrel-release</t>
         </is>
       </c>
     </row>
@@ -4388,37 +4430,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-10 11:33:03</t>
+          <t>2026-03-11 11:50:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Schaeffers Research</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Gas prices pass $3.50 per gallon to highest level since 2024 amid U.S.-Iran war</t>
+          <t>Stocks Drifting Lower as Oil Prices Resume Rally</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/gas-prices-pass-350-per-gallon-to-highest-level-20260310.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/stocks-drifting-lower-as-oil-prices-resume-rally-20260311.png</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>schaeffersresearch.com</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>The average price per gallon of unleaded gas in the U.S. climbed to about $3.54 per gallon, the highest price since 2024. Prices are up 21% from a month ago with the oil market roiled by the U.S.-Iran war.</t>
+          <t>The Dow is down triple digits, but the Nasdaq and S&amp;P 500 are clinging to gains as oil prices resume their climb</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/03/10/aaa-gas-prices-iran-affordability-trump.html</t>
+          <t>https://www.schaeffersresearch.com/content/ezines/2026/03/11/stocks-drifting-lower-as-oil-prices-resume-rally</t>
         </is>
       </c>
     </row>
@@ -4430,37 +4472,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:50</t>
+          <t>2026-03-11 11:25:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>24/7 Wall Street</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Sells Off Shares of International Business Machines Corporation (NYSE:IBM)</t>
+          <t>Refiners Are Quiet Winners in 2026: Wall Street's Signals Are Hard to Ignore</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-off-shares-of-international-business-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/refiners-are-quiet-winners-in-2026-wall-streets-signals-20260311.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>247wallst.com</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of International Business Machines Corporation (NYSE: IBM). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in International Business Machines stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SCHWAB JOINT BROKERAGE #1 (HOME GROWN)"</t>
+          <t>Institutional money is moving into U.S. refiners with conviction, and the earnings data backs it up.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-off-shares-of-international-business-machines-corporation-nyseibm.html</t>
+          <t>https://247wallst.com/investing/2026/03/11/refiners-are-quiet-winners-in-2026-wall-streets-signals-are-hard-to-ignore/</t>
         </is>
       </c>
     </row>
@@ -4472,37 +4514,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:50</t>
+          <t>2026-03-11 10:54:59</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>24/7 Wall Street</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Purchases Shares of Microsoft Corporation (NASDAQ:MSFT)</t>
+          <t>Trump Hails First New U.S. Refinery in 50 Years — Why Smart Investors Are Choosing Marathon Petroleum Instead</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-purchases-shares-of-microsoft-corporation-nasdaqmsft-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/trump-hails-first-new-us-refinery-in-50-years-20260311.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>247wallst.com</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently bought shares of Microsoft Corporation (NASDAQ: MSFT). In a filing disclosed on March 06th, the Representative disclosed that they had bought between $1,001 and $15,000 in Microsoft stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
+          <t>Marathon Petroleum (MPC) operates 13 refineries with 3 million barrels per day of crude distillation capacity, including the largest single refinery in the U.S. at Galveston Bay with 631,000 barrels per day capacity optimized for Permian and Eagle Ford shale oil. The company delivered $13.22 adjusted EPS in 2025, with refining margins expanding 44% year-over-year to $18.65 per barrel, and returned $4.5 billion to shareholders through dividends and buybacks.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-purchases-shares-of-microsoft-corporation-nasdaqmsft.html</t>
+          <t>https://247wallst.com/investing/2026/03/11/trump-hails-first-new-u-s-refinery-in-50-years-why-smart-investors-are-choosing-marathon-petroleum-instead/</t>
         </is>
       </c>
     </row>
@@ -4514,37 +4556,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:50</t>
+          <t>2026-03-11 10:50:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Sells Fifth Third Bancorp (NASDAQ:FITB) Shares</t>
+          <t>Here's Why Marathon Petroleum (MPC) is a Strong Momentum Stock</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-fifth-third-bancorp-nasdaqfitb-shares-20260310.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/heres-why-marathon-petroleum-mpc-is-a-strong-momentum-20260311.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Fifth Third Bancorp (NASDAQ: FITB). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Fifth Third Bancorp stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account.</t>
+          <t>Wondering how to pick strong, market-beating stocks for your investment portfolio? Look no further than the Zacks Style Scores.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-fifth-third-bancorp-nasdaqfitb-shares.html</t>
+          <t>https://www.zacks.com/stock/news/2882300/here-s-why-marathon-petroleum-mpc-is-a-strong-momentum-stock?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_momentum_score-2882300</t>
         </is>
       </c>
     </row>
@@ -4556,37 +4598,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:49</t>
+          <t>2026-03-11 07:38:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Sells Off Shares of Salesforce Inc. (NYSE:CRM)</t>
+          <t>Five things to know about Iran's new supreme leader, Mojtaba Khamenei</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-off-shares-of-salesforce-inc-nysecrm-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/five-things-to-know-about-irans-new-supreme-leader-20260311.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Salesforce Inc. (NYSE: CRM). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $15,001 and $50,000 in Salesforce stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
+          <t>Mojtaba Khamenei has been appointed Iran's new Supreme Leader, taking over from his late father, Ayatollah Ali Khamenei. More hardline and conservative than his father, Khameini has already drawn criticism from U.S. President Donald Trump, who expressed "disappointment" in his selection.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-off-shares-of-salesforce-inc-nysecrm-2.html</t>
+          <t>https://www.cnbc.com/2026/03/11/five-things-to-know-about-irans-new-supreme-leader-mojtaba-khamenei.html</t>
         </is>
       </c>
     </row>
@@ -4598,37 +4640,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:49</t>
+          <t>2026-03-10 11:33:03</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Alphabet (NASDAQ:GOOGL) Shares Acquired Rep. David Taylor</t>
+          <t>Gas prices pass $3.50 per gallon to highest level since 2024 amid U.S.-Iran war</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/alphabet-nasdaqgoogl-shares-acquired-rep-david-taylor-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/gas-prices-pass-350-per-gallon-to-highest-level-20260310.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently bought shares of Alphabet Inc. (NASDAQ: GOOGL). In a filing disclosed on March 06th, the Representative disclosed that they had bought between $1,001 and $15,000 in Alphabet stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
+          <t>The average price per gallon of unleaded gas in the U.S. climbed to about $3.54 per gallon, the highest price since 2024. Prices are up 21% from a month ago with the oil market roiled by the U.S.-Iran war.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/alphabet-nasdaqgoogl-shares-acquired-rep-david-taylor.html</t>
+          <t>https://www.cnbc.com/2026/03/10/aaa-gas-prices-iran-affordability-trump.html</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4682,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:49</t>
+          <t>2026-03-10 02:06:50</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4650,12 +4692,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Parker-Hannifin (NYSE:PH) Shares Unloaded Rep. David Taylor</t>
+          <t>Rep. David Taylor Sells Off Shares of International Business Machines Corporation (NYSE:IBM)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/parkerhannifin-nyseph-shares-unloaded-rep-david-taylor-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-off-shares-of-international-business-20260310.png</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4665,12 +4707,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Parker-Hannifin Corporation (NYSE: PH). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Parker-Hannifin stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of International Business Machines Corporation (NYSE: IBM). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in International Business Machines stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SCHWAB JOINT BROKERAGE #1 (HOME GROWN)"</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/parker-hannifin-nyseph-shares-unloaded-rep-david-taylor-2.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-off-shares-of-international-business-machines-corporation-nyseibm.html</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4724,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:49</t>
+          <t>2026-03-10 02:06:50</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4692,12 +4734,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Prologis (NYSE:PLD) Shares Unloaded Rep. David Taylor</t>
+          <t>Rep. David Taylor Purchases Shares of Microsoft Corporation (NASDAQ:MSFT)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/prologis-nysepld-shares-unloaded-rep-david-taylor-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-purchases-shares-of-microsoft-corporation-nasdaqmsft-20260310.png</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4707,12 +4749,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Prologis, Inc. (NYSE: PLD). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Prologis stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
+          <t>Representative David Taylor (Republican-Ohio) recently bought shares of Microsoft Corporation (NASDAQ: MSFT). In a filing disclosed on March 06th, the Representative disclosed that they had bought between $1,001 and $15,000 in Microsoft stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/prologis-nysepld-shares-unloaded-rep-david-taylor.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-purchases-shares-of-microsoft-corporation-nasdaqmsft.html</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4766,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:49</t>
+          <t>2026-03-10 02:06:50</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4734,12 +4776,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Buys Broadcom Inc. (NASDAQ:AVGO) Shares</t>
+          <t>Rep. David Taylor Sells Fifth Third Bancorp (NASDAQ:FITB) Shares</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-buys-broadcom-inc-nasdaqavgo-shares-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-fifth-third-bancorp-nasdaqfitb-shares-20260310.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4749,12 +4791,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently bought shares of Broadcom Inc. (NASDAQ: AVGO). In a filing disclosed on March 06th, the Representative disclosed that they had bought between $1,001 and $15,000 in Broadcom stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Fifth Third Bancorp (NASDAQ: FITB). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Fifth Third Bancorp stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-buys-broadcom-inc-nasdaqavgo-shares.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-fifth-third-bancorp-nasdaqfitb-shares.html</t>
         </is>
       </c>
     </row>
@@ -4776,12 +4818,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Buys Medpace Holdings, Inc. (NASDAQ:MEDP) Stock</t>
+          <t>Rep. David Taylor Sells Off Shares of Salesforce Inc. (NYSE:CRM)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-buys-medpace-holdings-inc-nasdaqmedp-stock-20260310.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-off-shares-of-salesforce-inc-nysecrm-20260310.png</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4791,12 +4833,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently bought shares of Medpace Holdings, Inc. (NASDAQ: MEDP). In a filing disclosed on March 06th, the Representative disclosed that they had bought between $1,001 and $15,000 in Medpace stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Salesforce Inc. (NYSE: CRM). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $15,001 and $50,000 in Salesforce stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-buys-medpace-holdings-inc-nasdaqmedp-stock.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-off-shares-of-salesforce-inc-nysecrm-2.html</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4860,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Eaton (NYSE:ETN) Shares Unloaded Rep. David Taylor</t>
+          <t>Alphabet (NASDAQ:GOOGL) Shares Acquired Rep. David Taylor</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/eaton-nyseetn-shares-unloaded-rep-david-taylor-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/alphabet-nasdaqgoogl-shares-acquired-rep-david-taylor-20260310.png</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4833,12 +4875,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Eaton Corporation, PLC (NYSE: ETN). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Eaton stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David</t>
+          <t>Representative David Taylor (Republican-Ohio) recently bought shares of Alphabet Inc. (NASDAQ: GOOGL). In a filing disclosed on March 06th, the Representative disclosed that they had bought between $1,001 and $15,000 in Alphabet stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/eaton-nyseetn-shares-unloaded-rep-david-taylor.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/alphabet-nasdaqgoogl-shares-acquired-rep-david-taylor.html</t>
         </is>
       </c>
     </row>
@@ -4860,12 +4902,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Sells Apple Inc. (NASDAQ:AAPL) Stock</t>
+          <t>Parker-Hannifin (NYSE:PH) Shares Unloaded Rep. David Taylor</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-apple-inc-nasdaqaapl-stock-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/parkerhannifin-nyseph-shares-unloaded-rep-david-taylor-20260310.png</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4875,12 +4917,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Apple Inc. (NASDAQ: AAPL). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Apple stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Parker-Hannifin Corporation (NYSE: PH). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Parker-Hannifin stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-apple-inc-nasdaqaapl-stock.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/parker-hannifin-nyseph-shares-unloaded-rep-david-taylor-2.html</t>
         </is>
       </c>
     </row>
@@ -4902,12 +4944,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Buys Visa Inc. (NYSE:V) Shares</t>
+          <t>Prologis (NYSE:PLD) Shares Unloaded Rep. David Taylor</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-buys-visa-inc-nysev-shares-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/prologis-nysepld-shares-unloaded-rep-david-taylor-20260310.png</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4917,12 +4959,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently bought shares of Visa Inc. (NYSE: V). In a filing disclosed on March 06th, the Representative disclosed that they had bought between $1,001 and $15,000 in Visa stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Prologis, Inc. (NYSE: PLD). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Prologis stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-buys-visa-inc-nysev-shares.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/prologis-nysepld-shares-unloaded-rep-david-taylor.html</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4976,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:48</t>
+          <t>2026-03-10 02:06:49</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4944,12 +4986,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Sells International Business Machines Corporation (NYSE:IBM) Stock</t>
+          <t>Rep. David Taylor Buys Broadcom Inc. (NASDAQ:AVGO) Shares</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-international-business-machines-corporation-nyseibm-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-buys-broadcom-inc-nasdaqavgo-shares-20260310.png</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4959,12 +5001,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of International Business Machines Corporation (NYSE: IBM). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $15,001 and $50,000 in International Business Machines stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE"</t>
+          <t>Representative David Taylor (Republican-Ohio) recently bought shares of Broadcom Inc. (NASDAQ: AVGO). In a filing disclosed on March 06th, the Representative disclosed that they had bought between $1,001 and $15,000 in Broadcom stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-international-business-machines-corporation-nyseibm-stock.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-buys-broadcom-inc-nasdaqavgo-shares.html</t>
         </is>
       </c>
     </row>
@@ -4976,7 +5018,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:48</t>
+          <t>2026-03-10 02:06:49</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4986,12 +5028,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Sells Installed Building Products, Inc. (NYSE:IBP) Shares</t>
+          <t>Rep. David Taylor Buys Medpace Holdings, Inc. (NASDAQ:MEDP) Stock</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-installed-building-products-inc-nyseibp-20260310.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-buys-medpace-holdings-inc-nasdaqmedp-stock-20260310.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5001,12 +5043,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Installed Building Products, Inc. (NYSE: IBP). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Installed Building Products stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE"</t>
+          <t>Representative David Taylor (Republican-Ohio) recently bought shares of Medpace Holdings, Inc. (NASDAQ: MEDP). In a filing disclosed on March 06th, the Representative disclosed that they had bought between $1,001 and $15,000 in Medpace stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-installed-building-products-inc-nyseibp-shares.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-buys-medpace-holdings-inc-nasdaqmedp-stock.html</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5060,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:48</t>
+          <t>2026-03-10 02:06:49</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5028,12 +5070,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Kroger (NYSE:KR) Stock Unloaded Rep. David Taylor</t>
+          <t>Eaton (NYSE:ETN) Shares Unloaded Rep. David Taylor</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/kroger-nysekr-stock-unloaded-rep-david-taylor-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/eaton-nyseetn-shares-unloaded-rep-david-taylor-20260310.png</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5043,12 +5085,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of The Kroger Co. (NYSE: KR). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Kroger stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Eaton Corporation, PLC (NYSE: ETN). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Eaton stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/kroger-nysekr-stock-unloaded-rep-david-taylor.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/eaton-nyseetn-shares-unloaded-rep-david-taylor.html</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5102,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:48</t>
+          <t>2026-03-10 02:06:49</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5070,12 +5112,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble (NYSE:PG) Shares Unloaded Rep. David Taylor</t>
+          <t>Rep. David Taylor Sells Apple Inc. (NASDAQ:AAPL) Stock</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/procter-gamble-nysepg-shares-unloaded-rep-david-taylor-20260310.gif</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-apple-inc-nasdaqaapl-stock-20260310.png</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5085,12 +5127,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Procter and Gamble Company (The) (NYSE: PG). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Procter and Gamble stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) -</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Apple Inc. (NASDAQ: AAPL). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Apple stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/procter-gamble-nysepg-shares-unloaded-rep-david-taylor.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-apple-inc-nasdaqaapl-stock.html</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5144,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:47</t>
+          <t>2026-03-10 02:06:49</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5112,12 +5154,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (NYSE:MPC) Shares Unloaded Rep. David Taylor</t>
+          <t>Rep. David Taylor Buys Visa Inc. (NYSE:V) Shares</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-nysempc-shares-unloaded-rep-david-taylor-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-buys-visa-inc-nysev-shares-20260310.png</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5127,12 +5169,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Marathon Petroleum Corporation (NYSE: MPC). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Marathon Petroleum stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative</t>
+          <t>Representative David Taylor (Republican-Ohio) recently bought shares of Visa Inc. (NYSE: V). In a filing disclosed on March 06th, the Representative disclosed that they had bought between $1,001 and $15,000 in Visa stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David Taylor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/marathon-petroleum-nysempc-shares-unloaded-rep-david-taylor.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-buys-visa-inc-nysev-shares.html</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5186,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:47</t>
+          <t>2026-03-10 02:06:48</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5154,12 +5196,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Sells Off Shares of RPM International Inc. (NYSE:RPM)</t>
+          <t>Rep. David Taylor Sells International Business Machines Corporation (NYSE:IBM) Stock</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-off-shares-of-rpm-international-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-international-business-machines-corporation-nyseibm-20260310.png</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5169,12 +5211,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of RPM International Inc. (NYSE: RPM). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in RPM International stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of International Business Machines Corporation (NYSE: IBM). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $15,001 and $50,000 in International Business Machines stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE"</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-off-shares-of-rpm-international-inc-nyserpm.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-international-business-machines-corporation-nyseibm-stock.html</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5228,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:47</t>
+          <t>2026-03-10 02:06:48</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5196,12 +5238,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Sells Off Shares of Salesforce Inc. (NYSE:CRM)</t>
+          <t>Rep. David Taylor Sells Installed Building Products, Inc. (NYSE:IBP) Shares</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-off-shares-of-salesforce-inc-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-installed-building-products-inc-nyseibp-20260310.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5211,12 +5253,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Salesforce Inc. (NYSE: CRM). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Salesforce stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SCHWAB JOINT BROKERAGE #1 (HOME GROWN)" account. Representative David Taylor</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Installed Building Products, Inc. (NYSE: IBP). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Installed Building Products stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE"</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-off-shares-of-salesforce-inc-nysecrm.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-installed-building-products-inc-nyseibp-shares.html</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5270,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:47</t>
+          <t>2026-03-10 02:06:48</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5238,12 +5280,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>American Electric Power (NASDAQ:AEP) Shares Unloaded Rep. David Taylor</t>
+          <t>Kroger (NYSE:KR) Stock Unloaded Rep. David Taylor</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/american-electric-power-nasdaqaep-shares-unloaded-rep-david-taylor-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/kroger-nysekr-stock-unloaded-rep-david-taylor-20260310.png</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5253,12 +5295,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of American Electric Power Company, Inc. (NASDAQ: AEP). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in American Electric Power stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) -</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of The Kroger Co. (NYSE: KR). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Kroger stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative David</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/american-electric-power-nasdaqaep-shares-unloaded-rep-david-taylor.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/kroger-nysekr-stock-unloaded-rep-david-taylor.html</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5312,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-03-10 02:06:47</t>
+          <t>2026-03-10 02:06:48</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5280,12 +5322,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Rep. David Taylor Sells Off Shares of Lam Research Corporation (NASDAQ:LRCX)</t>
+          <t>Procter &amp; Gamble (NYSE:PG) Shares Unloaded Rep. David Taylor</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-off-shares-of-lam-research-20260310.png</t>
+          <t>https://images.financialmodelingprep.com/news/procter-gamble-nysepg-shares-unloaded-rep-david-taylor-20260310.gif</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5295,12 +5337,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Lam Research Corporation (NASDAQ: LRCX). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Lam Research stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Procter and Gamble Company (The) (NYSE: PG). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Procter and Gamble stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) -</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-off-shares-of-lam-research-corporation-nasdaqlrcx.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/procter-gamble-nysepg-shares-unloaded-rep-david-taylor.html</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5354,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-03-09 03:03:14</t>
+          <t>2026-03-10 02:06:47</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5322,12 +5364,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>American Century Companies Inc. Sells 231,741 Shares of Marathon Petroleum Corporation $MPC</t>
+          <t>Marathon Petroleum (NYSE:MPC) Shares Unloaded Rep. David Taylor</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/american-century-companies-inc-sells-231741-shares-of-marathon-20260309.png</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-nysempc-shares-unloaded-rep-david-taylor-20260310.png</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5337,12 +5379,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>American Century Companies Inc. lessened its position in shares of Marathon Petroleum Corporation (NYSE: MPC) by 63.7% in the third quarter, according to the company in its most recent 13F filing with the Securities and Exchange Commission. The firm owned 132,035 shares of the oil and gas company's stock after selling 231,741 shares</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Marathon Petroleum Corporation (NYSE: MPC). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Marathon Petroleum stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/09/american-century-companies-inc-sells-231741-shares-of-marathon-petroleum-corporation-mpc.html</t>
+          <t>https://www.defenseworld.net/2026/03/10/marathon-petroleum-nysempc-shares-unloaded-rep-david-taylor.html</t>
         </is>
       </c>
     </row>
@@ -5354,37 +5396,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-03-06 10:37:37</t>
+          <t>2026-03-10 02:06:47</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>24/7 Wall Street</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Oil Is Surging and These 3 Energy Stocks Could Double Your Money Before 2027</t>
+          <t>Rep. David Taylor Sells Off Shares of RPM International Inc. (NYSE:RPM)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/oil-is-surging-and-these-3-energy-stocks-could-20260306.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-off-shares-of-rpm-international-20260310.png</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>247wallst.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oil prices are absolutely ripping higher, with investors of all stripes increasingly viewing oil stocks as a great place to invest.</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of RPM International Inc. (NYSE: RPM). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in RPM International stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://247wallst.com/investing/2026/03/06/oil-is-surging-and-these-3-energy-stocks-could-double-your-money-before-2027/</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-off-shares-of-rpm-international-inc-nyserpm.html</t>
         </is>
       </c>
     </row>
@@ -5396,37 +5438,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-03-06 10:00:40</t>
+          <t>2026-03-10 02:06:47</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Here is What to Know Beyond Why Marathon Petroleum Corporation (MPC) is a Trending Stock</t>
+          <t>Rep. David Taylor Sells Off Shares of Salesforce Inc. (NYSE:CRM)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/here-is-what-to-know-beyond-why-marathon-petroleum-20260306.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-off-shares-of-salesforce-inc-20260310.png</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) has received quite a bit of attention from Zacks.com users lately. Therefore, it is wise to be aware of the facts that can impact the stock's prospects.</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Salesforce Inc. (NYSE: CRM). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Salesforce stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SCHWAB JOINT BROKERAGE #1 (HOME GROWN)" account. Representative David Taylor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2879936/here-is-what-to-know-beyond-why-marathon-petroleum-corporation-mpc-is-a-trending-stock?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|most_searched_stocks-2879936</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-off-shares-of-salesforce-inc-nysecrm.html</t>
         </is>
       </c>
     </row>
@@ -5438,37 +5480,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-03-06 04:06:24</t>
+          <t>2026-03-10 02:06:47</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>24/7 Wall Street</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4 High Yield Refiners Built for Exactly These Spiking Oil Prices and Geopolitical Swings</t>
+          <t>American Electric Power (NASDAQ:AEP) Shares Unloaded Rep. David Taylor</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/4-high-yield-refiners-built-for-exactly-these-spiking-20260306.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/american-electric-power-nasdaqaep-shares-unloaded-rep-david-taylor-20260310.png</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>247wallst.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>When crude prices surge on geopolitical shock, refiners do not all respond equally.</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of American Electric Power Company, Inc. (NASDAQ: AEP). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in American Electric Power stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) -</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://247wallst.com/investing/2026/03/06/4-high-yield-refiners-built-for-exactly-these-spiking-oil-prices-and-geopolitical-swings/</t>
+          <t>https://www.defenseworld.net/2026/03/10/american-electric-power-nasdaqaep-shares-unloaded-rep-david-taylor.html</t>
         </is>
       </c>
     </row>
@@ -5480,37 +5522,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-03-05 18:20:34</t>
+          <t>2026-03-10 02:06:47</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Why One Energy Expert Is Betting on These 3 Oil Stocks Now</t>
+          <t>Rep. David Taylor Sells Off Shares of Lam Research Corporation (NASDAQ:LRCX)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-one-energy-expert-is-betting-on-these-3-20260305.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/rep-david-taylor-sells-off-shares-of-lam-research-20260310.png</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>marketbeat.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Energy markets have been anything but calm lately. Oil prices surged before pulling back again as geopolitical tensions in the Middle East sent shockwaves through global markets.</t>
+          <t>Representative David Taylor (Republican-Ohio) recently sold shares of Lam Research Corporation (NASDAQ: LRCX). In a filing disclosed on March 06th, the Representative disclosed that they had sold between $1,001 and $15,000 in Lam Research stock on February 26th. The trade occurred in the Representative's "DAVID TAYLOR TRUST &gt; SARDINIA READY MIX 401(K) - DAVE" account. Representative</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.marketbeat.com/stock-ideas/why-one-energy-expert-is-betting-on-these-3-oil-stocks-now/</t>
+          <t>https://www.defenseworld.net/2026/03/10/rep-david-taylor-sells-off-shares-of-lam-research-corporation-nasdaqlrcx.html</t>
         </is>
       </c>
     </row>
@@ -5522,37 +5564,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-03-05 13:00:12</t>
+          <t>2026-03-09 03:03:14</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Schwab Network</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>The Big 3: GLW, INTC, MPC</t>
+          <t>American Century Companies Inc. Sells 231,741 Shares of Marathon Petroleum Corporation $MPC</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/the-big-3-glw-intc-mpc-20260305.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/american-century-companies-inc-sells-231741-shares-of-marathon-20260309.png</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>youtube.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dan Deming has his eye on the market rotation happening as stocks take a backseat in Thursday's trading session. His Big 3 include trading opportunities amid geopolitical volatility.</t>
+          <t>American Century Companies Inc. lessened its position in shares of Marathon Petroleum Corporation (NYSE: MPC) by 63.7% in the third quarter, according to the company in its most recent 13F filing with the Securities and Exchange Commission. The firm owned 132,035 shares of the oil and gas company's stock after selling 231,741 shares</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BMfMTKqMfK0</t>
+          <t>https://www.defenseworld.net/2026/03/09/american-century-companies-inc-sells-231741-shares-of-marathon-petroleum-corporation-mpc.html</t>
         </is>
       </c>
     </row>
@@ -5564,37 +5606,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-03-05 12:35:53</t>
+          <t>2026-03-06 10:37:37</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>24/7 Wall Street</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) Up 12.7% Since Last Earnings Report: Can It Continue?</t>
+          <t>Oil Is Surging and These 3 Energy Stocks Could Double Your Money Before 2027</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-up-127-since-last-earnings-report-20260305.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/oil-is-surging-and-these-3-energy-stocks-could-20260306.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>247wallst.com</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) reported earnings 30 days ago. What's next for the stock?</t>
+          <t>Oil prices are absolutely ripping higher, with investors of all stripes increasingly viewing oil stocks as a great place to invest.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2879531/marathon-petroleum-mpc-up-12-7-since-last-earnings-report-can-it-continue?cid=CS-STOCKNEWSAPI-FT-realtime_blog-2879531</t>
+          <t>https://247wallst.com/investing/2026/03/06/oil-is-surging-and-these-3-energy-stocks-could-double-your-money-before-2027/</t>
         </is>
       </c>
     </row>
@@ -5606,37 +5648,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-03-03 12:05:04</t>
+          <t>2026-03-06 10:00:40</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Investopedia</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Stock Market Today: Major Indexes Tank as Iran War Escalates; Dow Drops 950 Points; Oil Surges Further</t>
+          <t>Here is What to Know Beyond Why Marathon Petroleum Corporation (MPC) is a Trending Stock</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/stock-market-today-major-indexes-tank-as-iran-war-20260303.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/here-is-what-to-know-beyond-why-marathon-petroleum-20260306.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>investopedia.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Major stock indexes plummeted Tuesday, with the Dow Jones Industrial Average shedding 850 points, as the conflict in the Middle East escalated. Meanwhile, oil futures soared for a second straight day.</t>
+          <t>Marathon Petroleum (MPC) has received quite a bit of attention from Zacks.com users lately. Therefore, it is wise to be aware of the facts that can impact the stock's prospects.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.investopedia.com/stock-market-today-dow-jones-s-and-p-500-03032026-11917935</t>
+          <t>https://www.zacks.com/stock/news/2879936/here-is-what-to-know-beyond-why-marathon-petroleum-corporation-mpc-is-a-trending-stock?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|most_searched_stocks-2879936</t>
         </is>
       </c>
     </row>
@@ -5648,37 +5690,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-02-27 10:30:34</t>
+          <t>2026-03-06 04:06:24</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>24/7 Wall Street</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Compared to Estimates, Marathon Petroleum (MPC) Q4 Earnings: A Look at Key Metrics</t>
+          <t>4 High Yield Refiners Built for Exactly These Spiking Oil Prices and Geopolitical Swings</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/compared-to-estimates-marathon-petroleum-mpc-q4-earnings-a-20260227.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/4-high-yield-refiners-built-for-exactly-these-spiking-20260306.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>247wallst.com</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>While the top- and bottom-line numbers for Marathon Petroleum (MPC) give a sense of how the business performed in the quarter ended December 2025, it could be worth looking at how some of its key metrics compare to Wall Street estimates and year-ago values.</t>
+          <t>When crude prices surge on geopolitical shock, refiners do not all respond equally.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2876684/compared-to-estimates-marathon-petroleum-mpc-q4-earnings-a-look-at-key-metrics?cid=CS-STOCKNEWSAPI-FT-fundamental_analysis|nfm-2876684</t>
+          <t>https://247wallst.com/investing/2026/03/06/4-high-yield-refiners-built-for-exactly-these-spiking-oil-prices-and-geopolitical-swings/</t>
         </is>
       </c>
     </row>
@@ -5690,37 +5732,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-02-27 03:30:53</t>
+          <t>2026-03-05 18:20:34</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Aster Capital Management DIFC Ltd Acquires New Stake in Marathon Petroleum Corporation $MPC</t>
+          <t>Why One Energy Expert Is Betting on These 3 Oil Stocks Now</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/aster-capital-management-difc-ltd-acquires-new-stake-in-20260227.png</t>
+          <t>https://images.financialmodelingprep.com/news/why-one-energy-expert-is-betting-on-these-3-20260305.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>marketbeat.com</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Aster Capital Management DIFC Ltd purchased a new position in shares of Marathon Petroleum Corporation (NYSE: MPC) during the undefined quarter, according to the company in its most recent filing with the Securities and Exchange Commission. The firm purchased 5,209 shares of the oil and gas company's stock, valued at approximately $1,004,000. A</t>
+          <t>Energy markets have been anything but calm lately. Oil prices surged before pulling back again as geopolitical tensions in the Middle East sent shockwaves through global markets.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/02/27/aster-capital-management-difc-ltd-acquires-new-stake-in-marathon-petroleum-corporation-mpc.html</t>
+          <t>https://www.marketbeat.com/stock-ideas/why-one-energy-expert-is-betting-on-these-3-oil-stocks-now/</t>
         </is>
       </c>
     </row>
@@ -5732,37 +5774,37 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-02-25 13:32:44</t>
+          <t>2026-03-05 13:00:12</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>24/7 Wall Street</t>
+          <t>Schwab Network</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Marathon Petroleum's 389% Free Cash Flow Jump Has Reddit Convinced</t>
+          <t>The Big 3: GLW, INTC, MPC</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleums-389-free-cash-flow-jump-has-reddit-20260225.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/the-big-3-glw-intc-mpc-20260305.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>247wallst.com</t>
+          <t>youtube.com</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Marathon Petroleum might be a household name for retail investors, but it ( NYSE:MPC ) has climbed 19% year-to-date and more than 28% over the past year, with Reddit sentiment tracking right alongside it.</t>
+          <t>Dan Deming has his eye on the market rotation happening as stocks take a backseat in Thursday's trading session. His Big 3 include trading opportunities amid geopolitical volatility.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://247wallst.com/investing/2026/02/25/marathon-petroleums-389-free-cash-flow-jump-has-reddit-convinced/</t>
+          <t>https://www.youtube.com/watch?v=BMfMTKqMfK0</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5816,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-02-23 10:01:42</t>
+          <t>2026-03-05 12:35:53</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5784,12 +5826,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Is Trending Stock Marathon Petroleum Corporation (MPC) a Buy Now?</t>
+          <t>Marathon Petroleum (MPC) Up 12.7% Since Last Earnings Report: Can It Continue?</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/is-trending-stock-marathon-petroleum-corporation-mpc-a-buy-20260223.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-up-127-since-last-earnings-report-20260305.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5799,12 +5841,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) has been one of the stocks most watched by Zacks.com users lately. So, it is worth exploring what lies ahead for the stock.</t>
+          <t>Marathon Petroleum (MPC) reported earnings 30 days ago. What's next for the stock?</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2873344/is-trending-stock-marathon-petroleum-corporation-mpc-a-buy-now?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|most_searched_stocks-2873344</t>
+          <t>https://www.zacks.com/stock/news/2879531/marathon-petroleum-mpc-up-12-7-since-last-earnings-report-can-it-continue?cid=CS-STOCKNEWSAPI-FT-realtime_blog-2879531</t>
         </is>
       </c>
     </row>
@@ -5816,37 +5858,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-02-21 12:39:00</t>
+          <t>2026-03-03 12:05:04</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Investopedia</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Returned $4.5 Billion to Shareholders in 2025. Here's Why It Could Happen Again.</t>
+          <t>Stock Market Today: Major Indexes Tank as Iran War Escalates; Dow Drops 950 Points; Oil Surges Further</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-returned-45-billion-to-shareholders-in-2025-20260221.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/stock-market-today-major-indexes-tank-as-iran-war-20260303.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>investopedia.com</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Quarterly cash flow reached its highest level in two years. MPLX distributions to Marathon are growing at a 12.5% annual clip.</t>
+          <t>Major stock indexes plummeted Tuesday, with the Dow Jones Industrial Average shedding 850 points, as the conflict in the Middle East escalated. Meanwhile, oil futures soared for a second straight day.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.fool.com/investing/2026/02/21/marathon-petroleum-returned-45-billion-to-sharehol/</t>
+          <t>https://www.investopedia.com/stock-market-today-dow-jones-s-and-p-500-03032026-11917935</t>
         </is>
       </c>
     </row>
@@ -5858,37 +5900,37 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-02-20 04:58:50</t>
+          <t>2026-02-27 10:30:34</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Axxcess Wealth Management LLC Boosts Stock Position in Marathon Petroleum Corporation $MPC</t>
+          <t>Compared to Estimates, Marathon Petroleum (MPC) Q4 Earnings: A Look at Key Metrics</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/axxcess-wealth-management-llc-boosts-stock-position-in-marathon-20260220.png</t>
+          <t>https://images.financialmodelingprep.com/news/compared-to-estimates-marathon-petroleum-mpc-q4-earnings-a-20260227.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Axxcess Wealth Management LLC boosted its stake in shares of Marathon Petroleum Corporation (NYSE: MPC) by 43.2% in the third quarter, according to its most recent 13F filing with the Securities and Exchange Commission. The firm owned 9,441 shares of the oil and gas company's stock after acquiring an additional 2,848 shares during</t>
+          <t>While the top- and bottom-line numbers for Marathon Petroleum (MPC) give a sense of how the business performed in the quarter ended December 2025, it could be worth looking at how some of its key metrics compare to Wall Street estimates and year-ago values.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/02/20/axxcess-wealth-management-llc-boosts-stock-position-in-marathon-petroleum-corporation-mpc.html</t>
+          <t>https://www.zacks.com/stock/news/2876684/compared-to-estimates-marathon-petroleum-mpc-q4-earnings-a-look-at-key-metrics?cid=CS-STOCKNEWSAPI-FT-fundamental_analysis|nfm-2876684</t>
         </is>
       </c>
     </row>
@@ -5900,37 +5942,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-02-18 17:34:00</t>
+          <t>2026-02-27 03:30:53</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Market Today: Moderna rebounds; oil and gold jump</t>
+          <t>Aster Capital Management DIFC Ltd Acquires New Stake in Marathon Petroleum Corporation $MPC</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/market-today-moderna-rebounds-oil-and-gold-jump-20260218.png</t>
+          <t>https://images.financialmodelingprep.com/news/aster-capital-management-difc-ltd-acquires-new-stake-in-20260227.png</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>gurufocus.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Guru Stock PicksLouis Moore Bacon has made the following transactions:Reduce in XLF by 69.62%Sold out in CEGAdd in CLS by 386.7%New position in CLJoel Greenblat</t>
+          <t>Aster Capital Management DIFC Ltd purchased a new position in shares of Marathon Petroleum Corporation (NYSE: MPC) during the undefined quarter, according to the company in its most recent filing with the Securities and Exchange Commission. The firm purchased 5,209 shares of the oil and gas company's stock, valued at approximately $1,004,000. A</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/8629482/market-today-moderna-rebounds-oil-and-gold-jump</t>
+          <t>https://www.defenseworld.net/2026/02/27/aster-capital-management-difc-ltd-acquires-new-stake-in-marathon-petroleum-corporation-mpc.html</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5984,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-02-18 08:45:27</t>
+          <t>2026-02-25 13:32:44</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5952,12 +5994,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Marathon Petroleum vs Phillips 66: Which Refining Giant Wins as Energy Sector Dominates 2026?</t>
+          <t>Marathon Petroleum's 389% Free Cash Flow Jump Has Reddit Convinced</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-vs-phillips-66-which-refining-giant-wins-20260218.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleums-389-free-cash-flow-jump-has-reddit-20260225.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5967,12 +6009,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (NYSE: MPC) and Phillips 66 (NYSE: PSX) just reported fourth-quarter earnings that underscore why refiners are riding the energy sector's extraordinary run.</t>
+          <t>Marathon Petroleum might be a household name for retail investors, but it ( NYSE:MPC ) has climbed 19% year-to-date and more than 28% over the past year, with Reddit sentiment tracking right alongside it.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://247wallst.com/investing/2026/02/18/marathon-petroleum-vs-phillips-66-which-refining-giant-wins-as-energy-sector-dominates-2026/</t>
+          <t>https://247wallst.com/investing/2026/02/25/marathon-petroleums-389-free-cash-flow-jump-has-reddit-convinced/</t>
         </is>
       </c>
     </row>
@@ -5984,37 +6026,37 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-02-18 07:38:00</t>
+          <t>2026-02-23 10:01:42</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>First Look: Nvidia-Meta chip pact, Bayer deal, WBD talks</t>
+          <t>Is Trending Stock Marathon Petroleum Corporation (MPC) a Buy Now?</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/first-look-nvidiameta-chip-pact-bayer-deal-wbd-talks-20260218.png</t>
+          <t>https://images.financialmodelingprep.com/news/is-trending-stock-marathon-petroleum-corporation-mpc-a-buy-20260223.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>gurufocus.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Stock News Goldman flags immigration shock: Goldman Sachs (GS) estimates an 80% plunge in U.S. net immigration is lowering labor-force growth and the âbreak-e</t>
+          <t>Marathon Petroleum (MPC) has been one of the stocks most watched by Zacks.com users lately. So, it is worth exploring what lies ahead for the stock.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/8626564/first-look-nvidiameta-chip-pact-bayer-deal-wbd-talks</t>
+          <t>https://www.zacks.com/stock/news/2873344/is-trending-stock-marathon-petroleum-corporation-mpc-a-buy-now?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|most_searched_stocks-2873344</t>
         </is>
       </c>
     </row>
@@ -6026,37 +6068,37 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-02-16 04:27:13</t>
+          <t>2026-02-21 12:39:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp Trims Stock Holdings in Marathon Petroleum Corporation $MPC</t>
+          <t>Marathon Petroleum Returned $4.5 Billion to Shareholders in 2025. Here's Why It Could Happen Again.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/fifth-third-bancorp-trims-stock-holdings-in-marathon-petroleum-20260216.png</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-returned-45-billion-to-shareholders-in-2025-20260221.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp cut its holdings in shares of Marathon Petroleum Corporation (NYSE: MPC) by 1.5% during the third quarter, according to the company in its most recent Form 13F filing with the Securities and Exchange Commission. The fund owned 536,024 shares of the oil and gas company's stock after selling 8,395 shares</t>
+          <t>Quarterly cash flow reached its highest level in two years. MPLX distributions to Marathon are growing at a 12.5% annual clip.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/02/16/fifth-third-bancorp-trims-stock-holdings-in-marathon-petroleum-corporation-mpc.html</t>
+          <t>https://www.fool.com/investing/2026/02/21/marathon-petroleum-returned-45-billion-to-sharehol/</t>
         </is>
       </c>
     </row>
@@ -6068,37 +6110,37 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-02-15 01:20:00</t>
+          <t>2026-02-20 04:58:50</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Oil Refiner Stocks Are Having a Banner 2026. Should You Invest $1,000?</t>
+          <t>Axxcess Wealth Management LLC Boosts Stock Position in Marathon Petroleum Corporation $MPC</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/oil-refiner-stocks-are-having-a-banner-2026-should-20260215.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/axxcess-wealth-management-llc-boosts-stock-position-in-marathon-20260220.png</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>A glut of oil has sent the price of unrefined crude lower. Increased manufacturing and air travel are driving demand for refined fuels higher.</t>
+          <t>Axxcess Wealth Management LLC boosted its stake in shares of Marathon Petroleum Corporation (NYSE: MPC) by 43.2% in the third quarter, according to its most recent 13F filing with the Securities and Exchange Commission. The firm owned 9,441 shares of the oil and gas company's stock after acquiring an additional 2,848 shares during</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.fool.com/investing/2026/02/15/oil-refiner-stocks-are-having-a-banner-2026-should/</t>
+          <t>https://www.defenseworld.net/2026/02/20/axxcess-wealth-management-llc-boosts-stock-position-in-marathon-petroleum-corporation-mpc.html</t>
         </is>
       </c>
     </row>
@@ -6110,37 +6152,37 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-02-14 03:27:04</t>
+          <t>2026-02-18 17:34:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation $MPC Shares Sold by Atria Investments Inc</t>
+          <t>Market Today: Moderna rebounds; oil and gold jump</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corporation-mpc-shares-sold-by-atria-investments-inc-20260214.png</t>
+          <t>https://images.financialmodelingprep.com/news/market-today-moderna-rebounds-oil-and-gold-jump-20260218.png</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>gurufocus.com</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Atria Investments Inc trimmed its stake in shares of Marathon Petroleum Corporation (NYSE: MPC) by 12.7% in the undefined quarter, according to the company in its most recent Form 13F filing with the Securities and Exchange Commission. The fund owned 34,297 shares of the oil and gas company's stock after selling 5,007 shares</t>
+          <t>Guru Stock PicksLouis Moore Bacon has made the following transactions:Reduce in XLF by 69.62%Sold out in CEGAdd in CLS by 386.7%New position in CLJoel Greenblat</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/02/14/marathon-petroleum-corporation-mpc-shares-sold-by-atria-investments-inc.html</t>
+          <t>https://www.gurufocus.com/news/8629482/market-today-moderna-rebounds-oil-and-gold-jump</t>
         </is>
       </c>
     </row>
@@ -6152,37 +6194,37 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-02-10 11:32:10</t>
+          <t>2026-02-18 08:45:27</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>24/7 Wall Street</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6%-8% Yields: 2 Of The Best Retirement Income Machines</t>
+          <t>Marathon Petroleum vs Phillips 66: Which Refining Giant Wins as Energy Sector Dominates 2026?</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/68-yields-2-of-the-best-retirement-income-machines-20260210.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-vs-phillips-66-which-refining-giant-wins-20260218.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>247wallst.com</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>High yield is easy; sustaining it is the real challenge. Two overlooked income machines quietly solve a major retirement problem. Why inflation may matter far less than most investors think.</t>
+          <t>Marathon Petroleum (NYSE: MPC) and Phillips 66 (NYSE: PSX) just reported fourth-quarter earnings that underscore why refiners are riding the energy sector's extraordinary run.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4868173-6-percent-yields-2-of-the-best-retirement-income-machines</t>
+          <t>https://247wallst.com/investing/2026/02/18/marathon-petroleum-vs-phillips-66-which-refining-giant-wins-as-energy-sector-dominates-2026/</t>
         </is>
       </c>
     </row>
@@ -6194,37 +6236,37 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-02-10 10:25:16</t>
+          <t>2026-02-18 07:38:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>3 Refining &amp; Marketing Stocks Investors Should Track Closely</t>
+          <t>First Look: Nvidia-Meta chip pact, Bayer deal, WBD talks</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/3-refining-marketing-stocks-investors-should-track-closely-20260210.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/first-look-nvidiameta-chip-pact-bayer-deal-wbd-talks-20260218.png</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>gurufocus.com</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>PSX, MPC and VLO stand out in the Oil and Gas - Refining &amp; Marketing industry as volatility persists, valuations stay low, and opportunities remain.</t>
+          <t>Stock News Goldman flags immigration shock: Goldman Sachs (GS) estimates an 80% plunge in U.S. net immigration is lowering labor-force growth and the âbreak-e</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/commentary/2846448/3-refining-marketing-stocks-investors-should-track-closely?cid=CS-STOCKNEWSAPI-FT-industry_outlook-2846448</t>
+          <t>https://www.gurufocus.com/news/8626564/first-look-nvidiameta-chip-pact-bayer-deal-wbd-talks</t>
         </is>
       </c>
     </row>
@@ -6236,37 +6278,37 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-02-10 10:01:05</t>
+          <t>2026-02-16 04:27:13</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation (MPC) is Attracting Investor Attention: Here is What You Should Know</t>
+          <t>Fifth Third Bancorp Trims Stock Holdings in Marathon Petroleum Corporation $MPC</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corporation-mpc-is-attracting-investor-attention-here-20260210.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/fifth-third-bancorp-trims-stock-holdings-in-marathon-petroleum-20260216.png</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Zacks.com users have recently been watching Marathon Petroleum (MPC) quite a bit. Thus, it is worth knowing the facts that could determine the stock's prospects.</t>
+          <t>Fifth Third Bancorp cut its holdings in shares of Marathon Petroleum Corporation (NYSE: MPC) by 1.5% during the third quarter, according to the company in its most recent Form 13F filing with the Securities and Exchange Commission. The fund owned 536,024 shares of the oil and gas company's stock after selling 8,395 shares</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2846741/marathon-petroleum-corporation-mpc-is-attracting-investor-attention-here-is-what-you-should-know?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|most_searched_stocks-2846741</t>
+          <t>https://www.defenseworld.net/2026/02/16/fifth-third-bancorp-trims-stock-holdings-in-marathon-petroleum-corporation-mpc.html</t>
         </is>
       </c>
     </row>
@@ -6278,37 +6320,37 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-02-06 06:50:15</t>
+          <t>2026-02-15 01:20:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>New Strong Sell Stocks for February 6th</t>
+          <t>Oil Refiner Stocks Are Having a Banner 2026. Should You Invest $1,000?</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/new-strong-sell-stocks-for-february-6th-20260206.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/oil-refiner-stocks-are-having-a-banner-2026-should-20260215.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MPC, NVGS and AKZOY have been added to the Zacks Rank #5 (Strong Sell) List on February 6, 2026.</t>
+          <t>A glut of oil has sent the price of unrefined crude lower. Increased manufacturing and air travel are driving demand for refined fuels higher.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2834881/new-strong-sell-stocks-for-february-6th?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|new_zacks_5_rank_stocks-2834881</t>
+          <t>https://www.fool.com/investing/2026/02/15/oil-refiner-stocks-are-having-a-banner-2026-should/</t>
         </is>
       </c>
     </row>
@@ -6320,37 +6362,37 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-02-05 08:51:14</t>
+          <t>2026-02-14 03:27:04</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Marathon Q4 Earnings &amp; Revenues Beat Estimates, Expenses Down Y/Y</t>
+          <t>Marathon Petroleum Corporation $MPC Shares Sold by Atria Investments Inc</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-q4-earnings-revenues-beat-estimates-expenses-down-yy-20260205.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corporation-mpc-shares-sold-by-atria-investments-inc-20260214.png</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>MPC, a Findlay, OH-based oil and gas refining and marketing company, expects refining operating costs to average $5.85 per barrel in the first quarter of 2026.</t>
+          <t>Atria Investments Inc trimmed its stake in shares of Marathon Petroleum Corporation (NYSE: MPC) by 12.7% in the undefined quarter, according to the company in its most recent Form 13F filing with the Securities and Exchange Commission. The fund owned 34,297 shares of the oil and gas company's stock after selling 5,007 shares</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2829571/marathon-q4-earnings-revenues-beat-estimates-expenses-down-y-y?cid=CS-STOCKNEWSAPI-FT-analyst_blog|earnings_article-2829571</t>
+          <t>https://www.defenseworld.net/2026/02/14/marathon-petroleum-corporation-mpc-shares-sold-by-atria-investments-inc.html</t>
         </is>
       </c>
     </row>
@@ -6362,37 +6404,37 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-02-03 18:09:45</t>
+          <t>2026-02-10 11:32:10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Company Is Ready to Sprint Higher</t>
+          <t>6%-8% Yields: 2 Of The Best Retirement Income Machines</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-company-is-ready-to-sprint-higher-20260203.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/68-yields-2-of-the-best-retirement-income-machines-20260210.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>marketbeat.com</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Company NYSE: MPC was poised to advance ahead of its Q4 earnings release, and the report triggered the move. Affirming the company's strong position in petroleum refining and the strength of its capital return, the report catalyzed a trend-following signal with the potential to take this market to new highs.</t>
+          <t>High yield is easy; sustaining it is the real challenge. Two overlooked income machines quietly solve a major retirement problem. Why inflation may matter far less than most investors think.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.marketbeat.com/originals/marathon-petroleum-company-is-ready-to-sprint-higher/</t>
+          <t>https://seekingalpha.com/article/4868173-6-percent-yields-2-of-the-best-retirement-income-machines</t>
         </is>
       </c>
     </row>
@@ -6404,37 +6446,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-02-03 18:01:00</t>
+          <t>2026-02-10 10:25:16</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corp (MPC) Q4 2025 Earnings Call Highlights: Strong Operational Performance and Strategic Investments</t>
+          <t>3 Refining &amp; Marketing Stocks Investors Should Track Closely</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corp-mpc-q4-2025-earnings-call-highlights-20260203.png</t>
+          <t>https://images.financialmodelingprep.com/news/3-refining-marketing-stocks-investors-should-track-closely-20260210.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>gurufocus.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Adjusted Earnings Per Share (EPS): $4.07 for Q4 2025; $10.70 for the full year.Adjusted EBITDA: $3.5 billion for Q4 2025; $12 billion for the full year.Cash Fl</t>
+          <t>PSX, MPC and VLO stand out in the Oil and Gas - Refining &amp; Marketing industry as volatility persists, valuations stay low, and opportunities remain.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/8579170/marathon-petroleum-corp-mpc-q4-2025-earnings-call-highlights-strong-operational-performance-and-strategic-investments</t>
+          <t>https://www.zacks.com/commentary/2846448/3-refining-marketing-stocks-investors-should-track-closely?cid=CS-STOCKNEWSAPI-FT-industry_outlook-2846448</t>
         </is>
       </c>
     </row>
@@ -6446,37 +6488,37 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-02-03 17:10:30</t>
+          <t>2026-02-10 10:01:05</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation (MPC) Q4 2025 Earnings Call Transcript</t>
+          <t>Marathon Petroleum Corporation (MPC) is Attracting Investor Attention: Here is What You Should Know</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corporation-mpc-q4-2025-earnings-call-transcript-20260203.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corporation-mpc-is-attracting-investor-attention-here-20260210.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation (MPC) Q4 2025 Earnings Call Transcript</t>
+          <t>Zacks.com users have recently been watching Marathon Petroleum (MPC) quite a bit. Thus, it is worth knowing the facts that could determine the stock's prospects.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4865408-marathon-petroleum-corporation-mpc-q4-2025-earnings-call-transcript</t>
+          <t>https://www.zacks.com/stock/news/2846741/marathon-petroleum-corporation-mpc-is-attracting-investor-attention-here-is-what-you-should-know?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|most_searched_stocks-2846741</t>
         </is>
       </c>
     </row>
@@ -6488,37 +6530,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-02-03 13:01:45</t>
+          <t>2026-02-06 06:50:15</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Marathon Petroleum buys Venezuelan crude for US refineries</t>
+          <t>New Strong Sell Stocks for February 6th</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-buys-venezuelan-crude-for-us-refineries-20260203.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/new-strong-sell-stocks-for-february-6th-20260206.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Marathon Petroleum said it bought two cargoes of Venezuelan crude oil at the end of January and expects its refineries to process more heavy grades, company executive said during a post-earnings call on Tuesday.</t>
+          <t>MPC, NVGS and AKZOY have been added to the Zacks Rank #5 (Strong Sell) List on February 6, 2026.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/energy/marathon-petroleum-buys-venezuelan-crude-us-refineries-2026-02-03/</t>
+          <t>https://www.zacks.com/stock/news/2834881/new-strong-sell-stocks-for-february-6th?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|new_zacks_5_rank_stocks-2834881</t>
         </is>
       </c>
     </row>
@@ -6530,37 +6572,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-02-03 10:09:39</t>
+          <t>2026-02-05 08:51:14</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Marathon Petroleum: Solid Q4 With Remarkable Buyback Capacity</t>
+          <t>Marathon Q4 Earnings &amp; Revenues Beat Estimates, Expenses Down Y/Y</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-solid-q4-with-remarkable-buyback-capacity-20260203.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-q4-earnings-revenues-beat-estimates-expenses-down-yy-20260205.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Marathon Petroleum is rated a 'strong buy' with ~20% upside and a $210 price target, driven by robust capital returns and undervalued refining assets. MPC's Q4 refining EBITDA nearly quadrupled YoY, with strong crack spreads and 114% market capture, despite some cost headwinds from rising energy prices. Shareholder returns remain aggressive, with $4.5B returned in 2025 and a current 11.7% capital return yield, supported by MPLX distributions.</t>
+          <t>MPC, a Findlay, OH-based oil and gas refining and marketing company, expects refining operating costs to average $5.85 per barrel in the first quarter of 2026.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4865296-marathon-petroleum-solid-q4-with-remarkable-buyback-capacity</t>
+          <t>https://www.zacks.com/stock/news/2829571/marathon-q4-earnings-revenues-beat-estimates-expenses-down-y-y?cid=CS-STOCKNEWSAPI-FT-analyst_blog|earnings_article-2829571</t>
         </is>
       </c>
     </row>
@@ -6572,37 +6614,37 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-02-03 08:41:09</t>
+          <t>2026-02-03 18:09:45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) Q4 Earnings and Revenues Surpass Estimates</t>
+          <t>Marathon Petroleum Company Is Ready to Sprint Higher</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-mpc-q4-earnings-and-revenues-surpass-estimates-20260203.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-company-is-ready-to-sprint-higher-20260203.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>marketbeat.com</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Marathon Petroleum (MPC) came out with quarterly earnings of $4.07 per share, beating the Zacks Consensus Estimate of $2.73 per share. This compares to earnings of $0.77 per share a year ago.</t>
+          <t>Marathon Petroleum Company NYSE: MPC was poised to advance ahead of its Q4 earnings release, and the report triggered the move. Affirming the company's strong position in petroleum refining and the strength of its capital return, the report catalyzed a trend-following signal with the potential to take this market to new highs.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2827587/marathon-petroleum-mpc-q4-earnings-and-revenues-surpass-estimates?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_4-2827587</t>
+          <t>https://www.marketbeat.com/originals/marathon-petroleum-company-is-ready-to-sprint-higher/</t>
         </is>
       </c>
     </row>
@@ -6614,37 +6656,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-02-03 06:38:24</t>
+          <t>2026-02-03 18:01:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Marathon Petroleum beats profit estimate on strong refining margins</t>
+          <t>Marathon Petroleum Corp (MPC) Q4 2025 Earnings Call Highlights: Strong Operational Performance and Strategic Investments</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-beats-profit-estimate-on-strong-refining-margins-20260203.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/marathon-petroleum-corp-mpc-q4-2025-earnings-call-highlights-20260203.png</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>gurufocus.com</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Marathon Petroleum beat Wall Street estimate for fourth-quarter profit on Tuesday, helped by strong refining margins.</t>
+          <t>Adjusted Earnings Per Share (EPS): $4.07 for Q4 2025; $10.70 for the full year.Adjusted EBITDA: $3.5 billion for Q4 2025; $12 billion for the full year.Cash Fl</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/energy/marathon-petroleum-beats-profit-estimate-strong-refining-margins-2026-02-03/</t>
+          <t>https://www.gurufocus.com/news/8579170/marathon-petroleum-corp-mpc-q4-2025-earnings-call-highlights-strong-operational-performance-and-strategic-investments</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6712,37 +6754,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-13 09:24:16</t>
+          <t>2026-04-23 11:05:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10% Owner Control Empresarial Has Been Dumping PBF Energy This Year. What Does It Mean for Individual Investors?</t>
+          <t>PBF Energy (PBF) May Report Negative Earnings: Know the Trend Ahead of Next Week's Release</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/10-owner-control-empresarial-has-been-dumping-pbf-energy-20260413.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-pbf-may-report-negative-earnings-know-the-20260423.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Control Empresarial disposed of 200,000 shares over two days for a total consideration of approximately ~$9.30 million, based on a weighted average price of $46.50 per share. This transaction represented 1.03% of Control Empresarial's direct holdings in PBF Energy at the time of sale.</t>
+          <t>PBF Energy (PBF) doesn't possess the right combination of the two key ingredients for a likely earnings beat in its upcoming report. Get prepared with the key expectations.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.fool.com/coverage/filings/2026/04/13/10-owner-control-empresarial-has-been-dumping-pbf-energy-this-year-what-does-it-mean-for-individual-investors/</t>
+          <t>https://www.zacks.com/stock/news/2906705/pbf-energy-pbf-may-report-negative-earnings-know-the-trend-ahead-of-next-week-s-release?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_9-2906705</t>
         </is>
       </c>
     </row>
@@ -6754,37 +6796,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-10 03:22:47</t>
+          <t>2026-04-23 10:46:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Allspring Global Investments Holdings LLC Lowers Stake in PBF Energy Inc. $PBF</t>
+          <t>Why PBF Energy (PBF) is a Top Growth Stock for the Long-Term</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/allspring-global-investments-holdings-llc-lowers-stake-in-pbf-20260410.png</t>
+          <t>https://images.financialmodelingprep.com/news/why-pbf-energy-pbf-is-a-top-growth-stock-20260423.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Allspring Global Investments Holdings LLC lessened its position in shares of PBF Energy Inc. (NYSE: PBF) by 88.0% in the fourth quarter, according to the company in its most recent Form 13F filing with the Securities and Exchange Commission. The firm owned 41,024 shares of the oil and gas company's stock after selling</t>
+          <t>The Zacks Style Scores offers investors a way to easily find top-rated stocks based on their investing style. Here's why you should take advantage.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/04/10/allspring-global-investments-holdings-llc-lowers-stake-in-pbf-energy-inc-pbf.html</t>
+          <t>https://www.zacks.com/stock/news/2906559/why-pbf-energy-pbf-is-a-top-growth-stock-for-the-long-term?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_growth_score-2906559</t>
         </is>
       </c>
     </row>
@@ -6796,37 +6838,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-08 02:15:05</t>
+          <t>2026-04-20 10:42:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE:PBF) Given Average Rating of “Reduce” by Brokerages</t>
+          <t>Here's Why PBF Energy (PBF) is a Strong Value Stock</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-nysepbf-given-average-rating-of-reduce-20260408.png</t>
+          <t>https://images.financialmodelingprep.com/news/heres-why-pbf-energy-pbf-is-a-strong-value-20260420.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Shares of PBF Energy Inc. (NYSE: PBF - Get Free Report) have earned an average recommendation of "Reduce" from the fifteen analysts that are covering the company, Marketbeat Ratings reports. Five investment analysts have rated the stock with a sell recommendation, eight have assigned a hold recommendation and two have given a buy recommendation to the</t>
+          <t>Whether you're a value, growth, or momentum investor, finding strong stocks becomes easier with the Zacks Style Scores, a top feature of the Zacks Premium research service.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/04/08/pbf-energy-inc-nysepbf-given-average-rating-of-reduce-by-brokerages.html</t>
+          <t>https://www.zacks.com/stock/news/2903197/here-s-why-pbf-energy-pbf-is-a-strong-value-stock</t>
         </is>
       </c>
     </row>
@@ -6838,37 +6880,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-07 11:06:19</t>
+          <t>2026-04-13 09:24:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Here's Why PBF Energy (PBF) is a Strong Growth Stock</t>
+          <t>10% Owner Control Empresarial Has Been Dumping PBF Energy This Year. What Does It Mean for Individual Investors?</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/heres-why-pbf-energy-pbf-is-a-strong-growth-20260407.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/10-owner-control-empresarial-has-been-dumping-pbf-energy-20260413.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The Zacks Style Scores offers investors a way to easily find top-rated stocks based on their investing style. Here's why you should take advantage.</t>
+          <t>Control Empresarial disposed of 200,000 shares over two days for a total consideration of approximately ~$9.30 million, based on a weighted average price of $46.50 per share. This transaction represented 1.03% of Control Empresarial's direct holdings in PBF Energy at the time of sale.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2895620/here-s-why-pbf-energy-pbf-is-a-strong-growth-stock</t>
+          <t>https://www.fool.com/coverage/filings/2026/04/13/10-owner-control-empresarial-has-been-dumping-pbf-energy-this-year-what-does-it-mean-for-individual-investors/</t>
         </is>
       </c>
     </row>
@@ -6880,37 +6922,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-06 10:50:21</t>
+          <t>2026-04-10 03:22:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Why PBF Energy (PBF) is a Top Momentum Stock for the Long-Term</t>
+          <t>Allspring Global Investments Holdings LLC Lowers Stake in PBF Energy Inc. $PBF</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-pbf-energy-pbf-is-a-top-momentum-stock-20260406.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/allspring-global-investments-holdings-llc-lowers-stake-in-pbf-20260410.png</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>The Zacks Style Scores offers investors a way to easily find top-rated stocks based on their investing style. Here's why you should take advantage.</t>
+          <t>Allspring Global Investments Holdings LLC lessened its position in shares of PBF Energy Inc. (NYSE: PBF) by 88.0% in the fourth quarter, according to the company in its most recent Form 13F filing with the Securities and Exchange Commission. The firm owned 41,024 shares of the oil and gas company's stock after selling</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2894771/why-pbf-energy-pbf-is-a-top-momentum-stock-for-the-long-term</t>
+          <t>https://www.defenseworld.net/2026/04/10/allspring-global-investments-holdings-llc-lowers-stake-in-pbf-energy-inc-pbf.html</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6964,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-04-05 06:20:53</t>
+          <t>2026-04-08 02:15:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6932,12 +6974,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SG Americas Securities LLC Reduces Holdings in PBF Energy Inc. $PBF</t>
+          <t>PBF Energy Inc. (NYSE:PBF) Given Average Rating of “Reduce” by Brokerages</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/sg-americas-securities-llc-reduces-holdings-in-pbf-energy-20260405.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-nysepbf-given-average-rating-of-reduce-20260408.png</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -6947,12 +6989,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SG Americas Securities LLC decreased its stake in shares of PBF Energy Inc. (NYSE: PBF) by 78.0% during the fourth quarter, according to its most recent filing with the Securities and Exchange Commission. The institutional investor owned 79,929 shares of the oil and gas company's stock after selling 282,609 shares during the period.</t>
+          <t>Shares of PBF Energy Inc. (NYSE: PBF - Get Free Report) have earned an average recommendation of "Reduce" from the fifteen analysts that are covering the company, Marketbeat Ratings reports. Five investment analysts have rated the stock with a sell recommendation, eight have assigned a hold recommendation and two have given a buy recommendation to the</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/04/05/sg-americas-securities-llc-reduces-holdings-in-pbf-energy-inc-pbf.html</t>
+          <t>https://www.defenseworld.net/2026/04/08/pbf-energy-inc-nysepbf-given-average-rating-of-reduce-by-brokerages.html</t>
         </is>
       </c>
     </row>
@@ -6964,37 +7006,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-04-03 05:32:46</t>
+          <t>2026-04-07 11:06:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PBF Energy (NYSE:PBF) SVP James Fedena Sells 77,085 Shares</t>
+          <t>Here's Why PBF Energy (PBF) is a Strong Growth Stock</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-svp-james-fedena-sells-77085-shares-20260403.png</t>
+          <t>https://images.financialmodelingprep.com/news/heres-why-pbf-energy-pbf-is-a-strong-growth-20260407.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) SVP James Fedena sold 77,085 shares of the firm's stock in a transaction dated Tuesday, March 31st. The shares were sold at an average price of $49.60, for a total value of $3,823,416.00. Following the sale, the senior vice president directly owned 139,016 shares in the company,</t>
+          <t>The Zacks Style Scores offers investors a way to easily find top-rated stocks based on their investing style. Here's why you should take advantage.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/04/03/pbf-energy-nysepbf-svp-james-fedena-sells-77085-shares.html</t>
+          <t>https://www.zacks.com/stock/news/2895620/here-s-why-pbf-energy-pbf-is-a-strong-growth-stock</t>
         </is>
       </c>
     </row>
@@ -7006,37 +7048,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04-03 05:32:45</t>
+          <t>2026-04-06 10:50:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PBF Energy (NYSE:PBF) Director Thomas Nimbley Sells 50,000 Shares</t>
+          <t>Why PBF Energy (PBF) is a Top Momentum Stock for the Long-Term</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-director-thomas-nimbley-sells-50000-shares-20260403.png</t>
+          <t>https://images.financialmodelingprep.com/news/why-pbf-energy-pbf-is-a-top-momentum-stock-20260406.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) Director Thomas Nimbley sold 50,000 shares of the business's stock in a transaction that occurred on Tuesday, March 31st. The shares were sold at an average price of $50.62, for a total value of $2,531,000.00. Following the completion of the sale, the director owned 790,716 shares in</t>
+          <t>The Zacks Style Scores offers investors a way to easily find top-rated stocks based on their investing style. Here's why you should take advantage.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/04/03/pbf-energy-nysepbf-director-thomas-nimbley-sells-50000-shares.html</t>
+          <t>https://www.zacks.com/stock/news/2894771/why-pbf-energy-pbf-is-a-top-momentum-stock-for-the-long-term</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7090,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-04-03 05:32:45</t>
+          <t>2026-04-05 06:20:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7058,12 +7100,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PBF Energy (NYSE:PBF) SVP Paul Davis Sells 50,000 Shares of Stock</t>
+          <t>SG Americas Securities LLC Reduces Holdings in PBF Energy Inc. $PBF</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-svp-paul-davis-sells-50000-shares-20260403.png</t>
+          <t>https://images.financialmodelingprep.com/news/sg-americas-securities-llc-reduces-holdings-in-pbf-energy-20260405.png</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -7073,12 +7115,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) SVP Paul Davis sold 50,000 shares of the firm's stock in a transaction that occurred on Friday, March 27th. The stock was sold at an average price of $51.48, for a total transaction of $2,574,000.00. Following the transaction, the senior vice president directly owned 183,426 shares in</t>
+          <t>SG Americas Securities LLC decreased its stake in shares of PBF Energy Inc. (NYSE: PBF) by 78.0% during the fourth quarter, according to its most recent filing with the Securities and Exchange Commission. The institutional investor owned 79,929 shares of the oil and gas company's stock after selling 282,609 shares during the period.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/04/03/pbf-energy-nysepbf-svp-paul-davis-sells-50000-shares-of-stock.html</t>
+          <t>https://www.defenseworld.net/2026/04/05/sg-americas-securities-llc-reduces-holdings-in-pbf-energy-inc-pbf.html</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7132,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-04-03 05:32:44</t>
+          <t>2026-04-03 05:32:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7100,12 +7142,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PBF Energy (NYSE:PBF) Insider Control Empresarial De Capital Sells 85,000 Shares</t>
+          <t>PBF Energy (NYSE:PBF) SVP James Fedena Sells 77,085 Shares</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-insider-control-empresarial-de-capital-sells-20260403.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-svp-james-fedena-sells-77085-shares-20260403.png</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -7115,12 +7157,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 85,000 shares of the stock in a transaction dated Monday, March 30th. The shares were sold at an average price of $51.14, for a total transaction of $4,346,900.00. Following the sale, the insider directly owned 19,653,698 shares of the company's stock,</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) SVP James Fedena sold 77,085 shares of the firm's stock in a transaction dated Tuesday, March 31st. The shares were sold at an average price of $49.60, for a total value of $3,823,416.00. Following the sale, the senior vice president directly owned 139,016 shares in the company,</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/04/03/pbf-energy-nysepbf-insider-control-empresarial-de-capital-sells-85000-shares.html</t>
+          <t>https://www.defenseworld.net/2026/04/03/pbf-energy-nysepbf-svp-james-fedena-sells-77085-shares.html</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7174,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-04-03 04:48:10</t>
+          <t>2026-04-03 05:32:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7142,12 +7184,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PBF Energy (NYSE:PBF) SVP James Fedena Sells 18,941 Shares of Stock</t>
+          <t>PBF Energy (NYSE:PBF) Director Thomas Nimbley Sells 50,000 Shares</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-svp-james-fedena-sells-18941-shares-20260403.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-director-thomas-nimbley-sells-50000-shares-20260403.png</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -7157,12 +7199,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) SVP James Fedena sold 18,941 shares of PBF Energy stock in a transaction on Monday, March 30th. The shares were sold at an average price of $51.66, for a total transaction of $978,492.06. Following the completion of the sale, the senior vice president directly owned 139,016 shares</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) Director Thomas Nimbley sold 50,000 shares of the business's stock in a transaction that occurred on Tuesday, March 31st. The shares were sold at an average price of $50.62, for a total value of $2,531,000.00. Following the completion of the sale, the director owned 790,716 shares in</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/04/03/pbf-energy-nysepbf-svp-james-fedena-sells-18941-shares-of-stock.html</t>
+          <t>https://www.defenseworld.net/2026/04/03/pbf-energy-nysepbf-director-thomas-nimbley-sells-50000-shares.html</t>
         </is>
       </c>
     </row>
@@ -7174,37 +7216,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-04-02 10:41:09</t>
+          <t>2026-04-03 05:32:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Why PBF Energy (PBF) is a Top Value Stock for the Long-Term</t>
+          <t>PBF Energy (NYSE:PBF) SVP Paul Davis Sells 50,000 Shares of Stock</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-pbf-energy-pbf-is-a-top-value-stock-20260402.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-svp-paul-davis-sells-50000-shares-20260403.png</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Wondering how to pick strong, market-beating stocks for your investment portfolio? Look no further than the Zacks Style Scores.</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) SVP Paul Davis sold 50,000 shares of the firm's stock in a transaction that occurred on Friday, March 27th. The stock was sold at an average price of $51.48, for a total transaction of $2,574,000.00. Following the transaction, the senior vice president directly owned 183,426 shares in</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2893659/why-pbf-energy-pbf-is-a-top-value-stock-for-the-long-term</t>
+          <t>https://www.defenseworld.net/2026/04/03/pbf-energy-nysepbf-svp-paul-davis-sells-50000-shares-of-stock.html</t>
         </is>
       </c>
     </row>
@@ -7216,37 +7258,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-31 21:05:00</t>
+          <t>2026-04-03 05:32:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10 No-Brainer Stocks to Buy as Long as the Strait of Hormuz Is Closed</t>
+          <t>PBF Energy (NYSE:PBF) Insider Control Empresarial De Capital Sells 85,000 Shares</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/10-nobrainer-stocks-to-buy-as-long-as-the-20260331.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-insider-control-empresarial-de-capital-sells-20260403.png</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Oil, LNG, refining, shipping, and fertilizer companies could benefit from ongoing disruptions. U.S.-based producers and exporters are among those positioned to outperform due to supply chain shifts.</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 85,000 shares of the stock in a transaction dated Monday, March 30th. The shares were sold at an average price of $51.14, for a total transaction of $4,346,900.00. Following the sale, the insider directly owned 19,653,698 shares of the company's stock,</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.fool.com/investing/2026/03/31/10-no-brainer-stocks-to-buy-as-long-as-the-strait/</t>
+          <t>https://www.defenseworld.net/2026/04/03/pbf-energy-nysepbf-insider-control-empresarial-de-capital-sells-85000-shares.html</t>
         </is>
       </c>
     </row>
@@ -7258,37 +7300,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-31 10:07:12</t>
+          <t>2026-04-03 04:48:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PBF Energy: Middle East Conflict Should Keep The Stock Price Elevated (Buy)</t>
+          <t>PBF Energy (NYSE:PBF) SVP James Fedena Sells 18,941 Shares of Stock</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-middle-east-conflict-should-keep-the-stock-20260331.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-svp-james-fedena-sells-18941-shares-20260403.png</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PBF Energy has restored operations to its Martinez refinery as of March and revenue should increase for 2026. The price of oil and of crack spread contracts are elevated due to the Iran conflict. The company's stock price has increased 164% over the last year and may continue its uptrend.</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) SVP James Fedena sold 18,941 shares of PBF Energy stock in a transaction on Monday, March 30th. The shares were sold at an average price of $51.66, for a total transaction of $978,492.06. Following the completion of the sale, the senior vice president directly owned 139,016 shares</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4887413-pbf-energy-middle-east-conflict-should-keep-the-stock-price-elevated-buy</t>
+          <t>https://www.defenseworld.net/2026/04/03/pbf-energy-nysepbf-svp-james-fedena-sells-18941-shares-of-stock.html</t>
         </is>
       </c>
     </row>
@@ -7300,37 +7342,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-31 08:16:48</t>
+          <t>2026-04-02 10:41:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>U.S. Refiners: Recent Trends And Relative Value</t>
+          <t>Why PBF Energy (PBF) is a Top Value Stock for the Long-Term</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/us-refiners-recent-trends-and-relative-value-20260331.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/why-pbf-energy-pbf-is-a-top-value-stock-20260402.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Refiners are  most profitable when oil prices are elevated, gasoline demand remains robust, and refiner margins are high. Refiner margins are dependent on crack spread - the difference between the value of the gasoline and diesel produced and the input cost of crude oil. The 3-2-1 crack spread has already nearly doubled this year from $0.65 to $1.65 per gallon of fuel.</t>
+          <t>Wondering how to pick strong, market-beating stocks for your investment portfolio? Look no further than the Zacks Style Scores.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4887380-us-refiners-recent-trends-and-relative-value</t>
+          <t>https://www.zacks.com/stock/news/2893659/why-pbf-energy-pbf-is-a-top-value-stock-for-the-long-term</t>
         </is>
       </c>
     </row>
@@ -7342,37 +7384,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-31 07:37:00</t>
+          <t>2026-03-31 21:05:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>First Look: Micron (MU) slides as Google AI 'TurboQuant' jolts memory stocks</t>
+          <t>10 No-Brainer Stocks to Buy as Long as the Strait of Hormuz Is Closed</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/first-look-micron-mu-slides-as-google-ai-turboquant-20260331.png</t>
+          <t>https://images.financialmodelingprep.com/news/10-nobrainer-stocks-to-buy-as-long-as-the-20260331.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>gurufocus.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Stock News U.S. gasoline tops $4: The national average gas price hit $4.02 per gallon, the highest since 2022, amid Iran warârelated supply disruptions, lifti</t>
+          <t>Oil, LNG, refining, shipping, and fertilizer companies could benefit from ongoing disruptions. U.S.-based producers and exporters are among those positioned to outperform due to supply chain shifts.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/8758873/first-look-micron-mu-slides-as-google-ai-turboquant-jolts-memory-stocks</t>
+          <t>https://www.fool.com/investing/2026/03/31/10-no-brainer-stocks-to-buy-as-long-as-the-strait/</t>
         </is>
       </c>
     </row>
@@ -7384,37 +7426,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-28 04:38:58</t>
+          <t>2026-03-31 10:07:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PBF Energy (NYSE:PBF) Insider Sells $34,024,375.00 in Stock</t>
+          <t>PBF Energy: Middle East Conflict Should Keep The Stock Price Elevated (Buy)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-insider-sells-3402437500-in-stock-20260328.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-middle-east-conflict-should-keep-the-stock-20260331.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 687,500 shares of the company's stock in a transaction dated Tuesday, March 24th. The stock was sold at an average price of $49.49, for a total value of $34,024,375.00. Following the completion of the sale, the insider directly owned 21,445,398 shares</t>
+          <t>PBF Energy has restored operations to its Martinez refinery as of March and revenue should increase for 2026. The price of oil and of crack spread contracts are elevated due to the Iran conflict. The company's stock price has increased 164% over the last year and may continue its uptrend.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/28/pbf-energy-nysepbf-insider-sells-34024375-00-in-stock.html</t>
+          <t>https://seekingalpha.com/article/4887413-pbf-energy-middle-east-conflict-should-keep-the-stock-price-elevated-buy</t>
         </is>
       </c>
     </row>
@@ -7426,37 +7468,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-28 04:38:51</t>
+          <t>2026-03-31 08:16:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Insider Selling: PBF Energy (NYSE:PBF) Insider Sells 469,700 Shares of Stock</t>
+          <t>U.S. Refiners: Recent Trends And Relative Value</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/insider-selling-pbf-energy-nysepbf-insider-sells-469700-shares-20260328.png</t>
+          <t>https://images.financialmodelingprep.com/news/us-refiners-recent-trends-and-relative-value-20260331.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 469,700 shares of PBF Energy stock in a transaction that occurred on Wednesday, March 25th. The stock was sold at an average price of $49.44, for a total value of $23,221,968.00. Following the completion of the sale, the insider owned 20,975,698</t>
+          <t>Refiners are  most profitable when oil prices are elevated, gasoline demand remains robust, and refiner margins are high. Refiner margins are dependent on crack spread - the difference between the value of the gasoline and diesel produced and the input cost of crude oil. The 3-2-1 crack spread has already nearly doubled this year from $0.65 to $1.65 per gallon of fuel.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/28/insider-selling-pbf-energy-nysepbf-insider-sells-469700-shares-of-stock.html</t>
+          <t>https://seekingalpha.com/article/4887380-us-refiners-recent-trends-and-relative-value</t>
         </is>
       </c>
     </row>
@@ -7468,37 +7510,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-27 17:20:05</t>
+          <t>2026-03-31 07:37:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PBF Energy SVP Trimmed His Position — A Recovering Margin Environment Is the Real Story</t>
+          <t>First Look: Micron (MU) slides as Google AI 'TurboQuant' jolts memory stocks</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-svp-trimmed-his-position-a-recovering-margin-20260327.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/first-look-micron-mu-slides-as-google-ai-turboquant-20260331.png</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>gurufocus.com</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>50,000 shares of Class A Common Stock were exercised and sold for a total of ~$2.24 million on March 4, 2026, at a weighted average price of $44.80 per share. The transaction represented 21.42% of Davis's direct holdings in Class A shares at the time, reducing direct ownership to 183,426 shares with an estimated post-transaction value of ~$8.22 million.</t>
+          <t>Stock News U.S. gasoline tops $4: The national average gas price hit $4.02 per gallon, the highest since 2022, amid Iran warârelated supply disruptions, lifti</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.fool.com/coverage/filings/2026/03/27/pbf-energy-svp-trimmed-his-position-a-recovering-margin-environment-is-the-real-story/</t>
+          <t>https://www.gurufocus.com/news/8758873/first-look-micron-mu-slides-as-google-ai-turboquant-jolts-memory-stocks</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7552,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-27 04:38:53</t>
+          <t>2026-03-28 04:38:58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7520,12 +7562,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Control Empresarial De Capital Sells 472,000 Shares of PBF Energy (NYSE:PBF) Stock</t>
+          <t>PBF Energy (NYSE:PBF) Insider Sells $34,024,375.00 in Stock</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/control-empresarial-de-capital-sells-472000-shares-of-pbf-20260327.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-insider-sells-3402437500-in-stock-20260328.png</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -7535,12 +7577,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 472,000 shares of the company's stock in a transaction on Monday, March 23rd. The shares were sold at an average price of $47.02, for a total transaction of $22,193,440.00. Following the completion of the sale, the insider directly owned 22,132,898 shares</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 687,500 shares of the company's stock in a transaction dated Tuesday, March 24th. The stock was sold at an average price of $49.49, for a total value of $34,024,375.00. Following the completion of the sale, the insider directly owned 21,445,398 shares</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/27/control-empresarial-de-capital-sells-472000-shares-of-pbf-energy-nysepbf-stock.html</t>
+          <t>https://www.defenseworld.net/2026/03/28/pbf-energy-nysepbf-insider-sells-34024375-00-in-stock.html</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7594,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-27 04:38:51</t>
+          <t>2026-03-28 04:38:51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -7562,12 +7604,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Control Empresarial De Capital Sells 340,000 Shares of PBF Energy (NYSE:PBF) Stock</t>
+          <t>Insider Selling: PBF Energy (NYSE:PBF) Insider Sells 469,700 Shares of Stock</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/control-empresarial-de-capital-sells-340000-shares-of-pbf-20260327.png</t>
+          <t>https://images.financialmodelingprep.com/news/insider-selling-pbf-energy-nysepbf-insider-sells-469700-shares-20260328.png</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -7577,12 +7619,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 340,000 shares of the firm's stock in a transaction that occurred on Friday, March 20th. The shares were sold at an average price of $48.84, for a total value of $16,605,600.00. Following the sale, the insider owned 22,604,898 shares of the</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 469,700 shares of PBF Energy stock in a transaction that occurred on Wednesday, March 25th. The stock was sold at an average price of $49.44, for a total value of $23,221,968.00. Following the completion of the sale, the insider owned 20,975,698</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/27/control-empresarial-de-capital-sells-340000-shares-of-pbf-energy-nysepbf-stock.html</t>
+          <t>https://www.defenseworld.net/2026/03/28/insider-selling-pbf-energy-nysepbf-insider-sells-469700-shares-of-stock.html</t>
         </is>
       </c>
     </row>
@@ -7594,37 +7636,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-03-25 17:00:00</t>
+          <t>2026-03-27 17:20:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PRNewsWire</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PBF Energy to Release First Quarter 2026 Earnings Results</t>
+          <t>PBF Energy SVP Trimmed His Position — A Recovering Margin Environment Is the Real Story</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-to-release-first-quarter-2026-earnings-results-20260325.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-svp-trimmed-his-position-a-recovering-margin-20260327.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PARSIPPANY, N.J., March 25, 2026 /PRNewswire/ -- PBF Energy Inc. (NYSE:PBF) announced today that it will release its earnings results for the first quarter 2026 on Thursday, April 30, 2026.</t>
+          <t>50,000 shares of Class A Common Stock were exercised and sold for a total of ~$2.24 million on March 4, 2026, at a weighted average price of $44.80 per share. The transaction represented 21.42% of Davis's direct holdings in Class A shares at the time, reducing direct ownership to 183,426 shares with an estimated post-transaction value of ~$8.22 million.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/pbf-energy-to-release-first-quarter-2026-earnings-results-302725214.html</t>
+          <t>https://www.fool.com/coverage/filings/2026/03/27/pbf-energy-svp-trimmed-his-position-a-recovering-margin-environment-is-the-real-story/</t>
         </is>
       </c>
     </row>
@@ -7636,37 +7678,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-25 15:05:00</t>
+          <t>2026-03-27 04:38:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5 Ripple Effects From the Strait of Hormuz Blockade Affecting Energy Stocks</t>
+          <t>Control Empresarial De Capital Sells 472,000 Shares of PBF Energy (NYSE:PBF) Stock</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/5-ripple-effects-from-the-strait-of-hormuz-blockade-20260325.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/control-empresarial-de-capital-sells-472000-shares-of-pbf-20260327.png</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>The lack of crude oil and LNG flows through the Strait is severely affecting global energy markets. Refining crack spreads are soaring as gasoline prices rise.</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 472,000 shares of the company's stock in a transaction on Monday, March 23rd. The shares were sold at an average price of $47.02, for a total transaction of $22,193,440.00. Following the completion of the sale, the insider directly owned 22,132,898 shares</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.fool.com/investing/2026/03/25/5-ripple-effects-from-the-strait-of-hormuz-blockad/</t>
+          <t>https://www.defenseworld.net/2026/03/27/control-empresarial-de-capital-sells-472000-shares-of-pbf-energy-nysepbf-stock.html</t>
         </is>
       </c>
     </row>
@@ -7678,37 +7720,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-22 07:55:00</t>
+          <t>2026-03-27 04:38:51</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3 Energy Stocks You'll Want to Own if Oil Soars Above $100 per Barrel</t>
+          <t>Control Empresarial De Capital Sells 340,000 Shares of PBF Energy (NYSE:PBF) Stock</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/3-energy-stocks-youll-want-to-own-if-oil-20260322.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/control-empresarial-de-capital-sells-340000-shares-of-pbf-20260327.png</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Equinor, PBF Energy, and Chevron offer different ways to benefit from high energy prices. Balancing refiners and producers can help manage portfolio risk.</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 340,000 shares of the firm's stock in a transaction that occurred on Friday, March 20th. The shares were sold at an average price of $48.84, for a total value of $16,605,600.00. Following the sale, the insider owned 22,604,898 shares of the</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.fool.com/investing/2026/03/22/3-energy-stocks-youll-want-to-own-if-oil-hits-100/</t>
+          <t>https://www.defenseworld.net/2026/03/27/control-empresarial-de-capital-sells-340000-shares-of-pbf-energy-nysepbf-stock.html</t>
         </is>
       </c>
     </row>
@@ -7720,37 +7762,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-20 04:26:51</t>
+          <t>2026-03-25 17:00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>PRNewsWire</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Control Empresarial De Capital Sells 600,000 Shares of PBF Energy (NYSE:PBF) Stock</t>
+          <t>PBF Energy to Release First Quarter 2026 Earnings Results</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/control-empresarial-de-capital-sells-600000-shares-of-pbf-20260320.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-to-release-first-quarter-2026-earnings-results-20260325.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 600,000 shares of the stock in a transaction dated Tuesday, March 17th. The shares were sold at an average price of $44.43, for a total transaction of $26,658,000.00. Following the completion of the transaction, the insider owned 24,096,898 shares of the</t>
+          <t>PARSIPPANY, N.J., March 25, 2026 /PRNewswire/ -- PBF Energy Inc. (NYSE:PBF) announced today that it will release its earnings results for the first quarter 2026 on Thursday, April 30, 2026.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/20/control-empresarial-de-capital-sells-600000-shares-of-pbf-energy-nysepbf-stock.html</t>
+          <t>https://www.prnewswire.com/news-releases/pbf-energy-to-release-first-quarter-2026-earnings-results-302725214.html</t>
         </is>
       </c>
     </row>
@@ -7762,37 +7804,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-19 10:45:26</t>
+          <t>2026-03-25 15:05:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Why PBF Energy (PBF) is a Top Growth Stock for the Long-Term</t>
+          <t>5 Ripple Effects From the Strait of Hormuz Blockade Affecting Energy Stocks</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-pbf-energy-pbf-is-a-top-growth-stock-20260319.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/5-ripple-effects-from-the-strait-of-hormuz-blockade-20260325.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>The Zacks Style Scores offers investors a way to easily find top-rated stocks based on their investing style. Here's why you should take advantage.</t>
+          <t>The lack of crude oil and LNG flows through the Strait is severely affecting global energy markets. Refining crack spreads are soaring as gasoline prices rise.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2886576/why-pbf-energy-pbf-is-a-top-growth-stock-for-the-long-term?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_growth_score-2886576</t>
+          <t>https://www.fool.com/investing/2026/03/25/5-ripple-effects-from-the-strait-of-hormuz-blockad/</t>
         </is>
       </c>
     </row>
@@ -7804,37 +7846,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-03-18 10:51:20</t>
+          <t>2026-03-22 07:55:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Here's Why PBF Energy (PBF) is a Strong Momentum Stock</t>
+          <t>3 Energy Stocks You'll Want to Own if Oil Soars Above $100 per Barrel</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/heres-why-pbf-energy-pbf-is-a-strong-momentum-20260318.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/3-energy-stocks-youll-want-to-own-if-oil-20260322.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>The Zacks Style Scores offers investors a way to easily find top-rated stocks based on their investing style. Here's why you should take advantage.</t>
+          <t>Equinor, PBF Energy, and Chevron offer different ways to benefit from high energy prices. Balancing refiners and producers can help manage portfolio risk.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2885900/here-s-why-pbf-energy-pbf-is-a-strong-momentum-stock?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_momentum_score-2885900</t>
+          <t>https://www.fool.com/investing/2026/03/22/3-energy-stocks-youll-want-to-own-if-oil-hits-100/</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7888,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-03-16 04:21:06</t>
+          <t>2026-03-20 04:26:51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7856,12 +7898,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Insider Selling: PBF Energy (NYSE:PBF) Insider Sells $16,454,000.00 in Stock</t>
+          <t>Control Empresarial De Capital Sells 600,000 Shares of PBF Energy (NYSE:PBF) Stock</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/insider-selling-pbf-energy-nysepbf-insider-sells-1645400000-in-stock-20260316.png</t>
+          <t>https://images.financialmodelingprep.com/news/control-empresarial-de-capital-sells-600000-shares-of-pbf-20260320.png</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -7871,12 +7913,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 380,000 shares of the firm's stock in a transaction dated Friday, March 13th. The shares were sold at an average price of $43.30, for a total value of $16,454,000.00. Following the sale, the insider owned 24,746,098 shares in the company, valued</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 600,000 shares of the stock in a transaction dated Tuesday, March 17th. The shares were sold at an average price of $44.43, for a total transaction of $26,658,000.00. Following the completion of the transaction, the insider owned 24,096,898 shares of the</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/16/insider-selling-pbf-energy-nysepbf-insider-sells-16454000-00-in-stock.html</t>
+          <t>https://www.defenseworld.net/2026/03/20/control-empresarial-de-capital-sells-600000-shares-of-pbf-energy-nysepbf-stock.html</t>
         </is>
       </c>
     </row>
@@ -7888,37 +7930,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-03-16 04:21:04</t>
+          <t>2026-03-19 10:45:26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Insider Selling: PBF Energy (NYSE:PBF) Insider Sells $11,540,750.00 in Stock</t>
+          <t>Why PBF Energy (PBF) is a Top Growth Stock for the Long-Term</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/insider-selling-pbf-energy-nysepbf-insider-sells-1154075000-in-stock-20260316.png</t>
+          <t>https://images.financialmodelingprep.com/news/why-pbf-energy-pbf-is-a-top-growth-stock-20260319.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 265,000 shares of the stock in a transaction dated Thursday, March 12th. The shares were sold at an average price of $43.55, for a total transaction of $11,540,750.00. Following the completion of the transaction, the insider directly owned 25,126,098 shares of</t>
+          <t>The Zacks Style Scores offers investors a way to easily find top-rated stocks based on their investing style. Here's why you should take advantage.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/16/insider-selling-pbf-energy-nysepbf-insider-sells-11540750-00-in-stock.html</t>
+          <t>https://www.zacks.com/stock/news/2886576/why-pbf-energy-pbf-is-a-top-growth-stock-for-the-long-term?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_growth_score-2886576</t>
         </is>
       </c>
     </row>
@@ -7930,37 +7972,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-03-14 02:44:49</t>
+          <t>2026-03-18 10:51:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE:PBF) Receives Average Rating of “Reduce” from Brokerages</t>
+          <t>Here's Why PBF Energy (PBF) is a Strong Momentum Stock</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-nysepbf-receives-average-rating-of-reduce-20260314.png</t>
+          <t>https://images.financialmodelingprep.com/news/heres-why-pbf-energy-pbf-is-a-strong-momentum-20260318.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) has been given an average recommendation of "Reduce" by the fifteen brokerages that are covering the company, MarketBeat reports. Five research analysts have rated the stock with a sell rating, eight have issued a hold rating and two have assigned a buy rating to the company. The</t>
+          <t>The Zacks Style Scores offers investors a way to easily find top-rated stocks based on their investing style. Here's why you should take advantage.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/14/pbf-energy-inc-nysepbf-receives-average-rating-of-reduce-from-brokerages-2.html</t>
+          <t>https://www.zacks.com/stock/news/2885900/here-s-why-pbf-energy-pbf-is-a-strong-momentum-stock?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|zacks_education_momentum_score-2885900</t>
         </is>
       </c>
     </row>
@@ -7972,37 +8014,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-03-12 16:30:00</t>
+          <t>2026-03-16 04:21:06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PRNewsWire</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PBF Energy to Participate in Piper Sandler Energy Conference</t>
+          <t>Insider Selling: PBF Energy (NYSE:PBF) Insider Sells $16,454,000.00 in Stock</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-to-participate-in-piper-sandler-energy-conference-20260312.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/insider-selling-pbf-energy-nysepbf-insider-sells-1645400000-in-stock-20260316.png</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PARSIPPANY, N.J., March 12, 2026 /PRNewswire/ -- PBF Energy Inc. (NYSE:PBF) today announced that members of its management team will participate in the Piper Sandler Energy Conference on March 16-17, 2026.</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 380,000 shares of the firm's stock in a transaction dated Friday, March 13th. The shares were sold at an average price of $43.30, for a total value of $16,454,000.00. Following the sale, the insider owned 24,746,098 shares in the company, valued</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/pbf-energy-to-participate-in-piper-sandler-energy-conference-302712672.html</t>
+          <t>https://www.defenseworld.net/2026/03/16/insider-selling-pbf-energy-nysepbf-insider-sells-16454000-00-in-stock.html</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8056,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-03-12 03:43:14</t>
+          <t>2026-03-16 04:21:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8024,12 +8066,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors LP Sells 1,318,286 Shares of PBF Energy Inc. $PBF</t>
+          <t>Insider Selling: PBF Energy (NYSE:PBF) Insider Sells $11,540,750.00 in Stock</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/dimensional-fund-advisors-lp-sells-1318286-shares-of-pbf-20260312.png</t>
+          <t>https://images.financialmodelingprep.com/news/insider-selling-pbf-energy-nysepbf-insider-sells-1154075000-in-stock-20260316.png</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -8039,12 +8081,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors LP lowered its stake in PBF Energy Inc. (NYSE: PBF) by 23.6% during the third quarter, according to the company in its most recent filing with the Securities and Exchange Commission. The firm owned 4,276,060 shares of the oil and gas company's stock after selling 1,318,286 shares during the quarter.</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 265,000 shares of the stock in a transaction dated Thursday, March 12th. The shares were sold at an average price of $43.55, for a total transaction of $11,540,750.00. Following the completion of the transaction, the insider directly owned 25,126,098 shares of</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/12/dimensional-fund-advisors-lp-sells-1318286-shares-of-pbf-energy-inc-pbf.html</t>
+          <t>https://www.defenseworld.net/2026/03/16/insider-selling-pbf-energy-nysepbf-insider-sells-11540750-00-in-stock.html</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8098,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-03-11 04:23:48</t>
+          <t>2026-03-14 02:44:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8066,12 +8108,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fieldview Capital Management LLC Takes Position in PBF Energy Inc. $PBF</t>
+          <t>PBF Energy Inc. (NYSE:PBF) Receives Average Rating of “Reduce” from Brokerages</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/fieldview-capital-management-llc-takes-position-in-pbf-energy-20260311.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-nysepbf-receives-average-rating-of-reduce-20260314.png</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -8081,12 +8123,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fieldview Capital Management LLC acquired a new position in PBF Energy Inc. (NYSE: PBF) in the undefined quarter, according to its most recent Form 13F filing with the SEC. The institutional investor acquired 12,632 shares of the oil and gas company's stock, valued at approximately $381,000. Other institutional investors have also recently bought</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) has been given an average recommendation of "Reduce" by the fifteen brokerages that are covering the company, MarketBeat reports. Five research analysts have rated the stock with a sell rating, eight have issued a hold rating and two have assigned a buy rating to the company. The</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/11/fieldview-capital-management-llc-takes-position-in-pbf-energy-inc-pbf.html</t>
+          <t>https://www.defenseworld.net/2026/03/14/pbf-energy-inc-nysepbf-receives-average-rating-of-reduce-from-brokerages-2.html</t>
         </is>
       </c>
     </row>
@@ -8098,37 +8140,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-03-08 04:52:48</t>
+          <t>2026-03-12 16:30:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>PRNewsWire</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Paul Davis Sells 50,000 Shares of PBF Energy (NYSE:PBF) Stock</t>
+          <t>PBF Energy to Participate in Piper Sandler Energy Conference</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/paul-davis-sells-50000-shares-of-pbf-energy-nysepbf-stock-20260308.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-to-participate-in-piper-sandler-energy-conference-20260312.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) SVP Paul Davis sold 50,000 shares of the business's stock in a transaction that occurred on Wednesday, March 4th. The shares were sold at an average price of $44.80, for a total transaction of $2,240,000.00. Following the transaction, the senior vice president owned 183,426 shares of the</t>
+          <t>PARSIPPANY, N.J., March 12, 2026 /PRNewswire/ -- PBF Energy Inc. (NYSE:PBF) today announced that members of its management team will participate in the Piper Sandler Energy Conference on March 16-17, 2026.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/08/paul-davis-sells-50000-shares-of-pbf-energy-nysepbf-stock.html</t>
+          <t>https://www.prnewswire.com/news-releases/pbf-energy-to-participate-in-piper-sandler-energy-conference-302712672.html</t>
         </is>
       </c>
     </row>
@@ -8140,7 +8182,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-03-07 05:02:48</t>
+          <t>2026-03-12 03:43:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8150,12 +8192,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Insider Selling: PBF Energy (NYSE:PBF) Insider Sells $4,599,600.00 in Stock</t>
+          <t>Dimensional Fund Advisors LP Sells 1,318,286 Shares of PBF Energy Inc. $PBF</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/insider-selling-pbf-energy-nysepbf-insider-sells-459960000-in-stock-20260307.png</t>
+          <t>https://images.financialmodelingprep.com/news/dimensional-fund-advisors-lp-sells-1318286-shares-of-pbf-20260312.png</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -8165,12 +8207,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 120,000 shares of the stock in a transaction that occurred on Monday, March 2nd. The stock was sold at an average price of $38.33, for a total transaction of $4,599,600.00. Following the sale, the insider directly owned 27,471,198 shares of the</t>
+          <t>Dimensional Fund Advisors LP lowered its stake in PBF Energy Inc. (NYSE: PBF) by 23.6% during the third quarter, according to the company in its most recent filing with the Securities and Exchange Commission. The firm owned 4,276,060 shares of the oil and gas company's stock after selling 1,318,286 shares during the quarter.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/07/insider-selling-pbf-energy-nysepbf-insider-sells-4599600-00-in-stock.html</t>
+          <t>https://www.defenseworld.net/2026/03/12/dimensional-fund-advisors-lp-sells-1318286-shares-of-pbf-energy-inc-pbf.html</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8224,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-03-07 05:02:46</t>
+          <t>2026-03-11 04:23:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8192,12 +8234,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PBF Energy (NYSE:PBF) Insider Sells $3,992,670.00 in Stock</t>
+          <t>Fieldview Capital Management LLC Takes Position in PBF Energy Inc. $PBF</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-insider-sells-399267000-in-stock-20260307.png</t>
+          <t>https://images.financialmodelingprep.com/news/fieldview-capital-management-llc-takes-position-in-pbf-energy-20260311.png</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8207,12 +8249,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 99,000 shares of PBF Energy stock in a transaction on Tuesday, March 3rd. The shares were sold at an average price of $40.33, for a total transaction of $3,992,670.00. Following the completion of the sale, the insider owned 27,372,198 shares of</t>
+          <t>Fieldview Capital Management LLC acquired a new position in PBF Energy Inc. (NYSE: PBF) in the undefined quarter, according to its most recent Form 13F filing with the SEC. The institutional investor acquired 12,632 shares of the oil and gas company's stock, valued at approximately $381,000. Other institutional investors have also recently bought</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/07/pbf-energy-nysepbf-insider-sells-3992670-00-in-stock.html</t>
+          <t>https://www.defenseworld.net/2026/03/11/fieldview-capital-management-llc-takes-position-in-pbf-energy-inc-pbf.html</t>
         </is>
       </c>
     </row>
@@ -8224,37 +8266,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-03-06 04:06:24</t>
+          <t>2026-03-08 04:52:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>24/7 Wall Street</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4 High Yield Refiners Built for Exactly These Spiking Oil Prices and Geopolitical Swings</t>
+          <t>Paul Davis Sells 50,000 Shares of PBF Energy (NYSE:PBF) Stock</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/4-high-yield-refiners-built-for-exactly-these-spiking-20260306.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/paul-davis-sells-50000-shares-of-pbf-energy-nysepbf-stock-20260308.png</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>247wallst.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>When crude prices surge on geopolitical shock, refiners do not all respond equally.</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) SVP Paul Davis sold 50,000 shares of the business's stock in a transaction that occurred on Wednesday, March 4th. The shares were sold at an average price of $44.80, for a total transaction of $2,240,000.00. Following the transaction, the senior vice president owned 183,426 shares of the</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://247wallst.com/investing/2026/03/06/4-high-yield-refiners-built-for-exactly-these-spiking-oil-prices-and-geopolitical-swings/</t>
+          <t>https://www.defenseworld.net/2026/03/08/paul-davis-sells-50000-shares-of-pbf-energy-nysepbf-stock.html</t>
         </is>
       </c>
     </row>
@@ -8266,7 +8308,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-05 01:14:47</t>
+          <t>2026-03-07 05:02:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8276,12 +8318,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Stock Traders Purchase Large Volume of Call Options on PBF Energy (NYSE:PBF)</t>
+          <t>Insider Selling: PBF Energy (NYSE:PBF) Insider Sells $4,599,600.00 in Stock</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/stock-traders-purchase-large-volume-of-call-options-on-20260305.png</t>
+          <t>https://images.financialmodelingprep.com/news/insider-selling-pbf-energy-nysepbf-insider-sells-459960000-in-stock-20260307.png</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -8291,12 +8333,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) was the target of unusually large options trading on Wednesday. Investors purchased 14,762 call options on the stock. This represents an increase of approximately 392% compared to the average daily volume of 2,998 call options. Insiders Place Their Bets In related news, insider Control Empresarial De Capital</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 120,000 shares of the stock in a transaction that occurred on Monday, March 2nd. The stock was sold at an average price of $38.33, for a total transaction of $4,599,600.00. Following the sale, the insider directly owned 27,471,198 shares of the</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/03/05/stock-traders-purchase-large-volume-of-call-options-on-pbf-energy-nysepbf.html</t>
+          <t>https://www.defenseworld.net/2026/03/07/insider-selling-pbf-energy-nysepbf-insider-sells-4599600-00-in-stock.html</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8350,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-02-28 04:23:02</t>
+          <t>2026-03-07 05:02:46</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -8318,12 +8360,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Control Empresarial De Capital Sells 250,000 Shares of PBF Energy (NYSE:PBF) Stock</t>
+          <t>PBF Energy (NYSE:PBF) Insider Sells $3,992,670.00 in Stock</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/control-empresarial-de-capital-sells-250000-shares-of-pbf-20260228.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-insider-sells-399267000-in-stock-20260307.png</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8333,12 +8375,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 250,000 shares of PBF Energy stock in a transaction on Tuesday, February 24th. The stock was sold at an average price of $34.91, for a total value of $8,727,500.00. Following the transaction, the insider directly owned 27,591,198 shares of the company's</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 99,000 shares of PBF Energy stock in a transaction on Tuesday, March 3rd. The shares were sold at an average price of $40.33, for a total transaction of $3,992,670.00. Following the completion of the sale, the insider owned 27,372,198 shares of</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/02/28/control-empresarial-de-capital-sells-250000-shares-of-pbf-energy-nysepbf-stock.html</t>
+          <t>https://www.defenseworld.net/2026/03/07/pbf-energy-nysepbf-insider-sells-3992670-00-in-stock.html</t>
         </is>
       </c>
     </row>
@@ -8350,37 +8392,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-02-25 04:43:05</t>
+          <t>2026-03-06 04:06:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>24/7 Wall Street</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Counterpoint Mutual Funds LLC Makes New Investment in PBF Energy Inc. $PBF</t>
+          <t>4 High Yield Refiners Built for Exactly These Spiking Oil Prices and Geopolitical Swings</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/counterpoint-mutual-funds-llc-makes-new-investment-in-pbf-20260225.png</t>
+          <t>https://images.financialmodelingprep.com/news/4-high-yield-refiners-built-for-exactly-these-spiking-20260306.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>247wallst.com</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Counterpoint Mutual Funds LLC purchased a new position in PBF Energy Inc. (NYSE: PBF) during the undefined quarter, according to the company in its most recent 13F filing with the Securities and Exchange Commission. The institutional investor purchased 16,649 shares of the oil and gas company's stock, valued at approximately $502,000. Other institutional</t>
+          <t>When crude prices surge on geopolitical shock, refiners do not all respond equally.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/02/25/counterpoint-mutual-funds-llc-makes-new-investment-in-pbf-energy-inc-pbf.html</t>
+          <t>https://247wallst.com/investing/2026/03/06/4-high-yield-refiners-built-for-exactly-these-spiking-oil-prices-and-geopolitical-swings/</t>
         </is>
       </c>
     </row>
@@ -8392,37 +8434,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-02-20 16:15:00</t>
+          <t>2026-03-05 01:14:47</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PRNewsWire</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PBF Energy to Participate in Industry Conferences</t>
+          <t>Stock Traders Purchase Large Volume of Call Options on PBF Energy (NYSE:PBF)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-to-participate-in-industry-conferences-20260220.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/stock-traders-purchase-large-volume-of-call-options-on-20260305.png</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PARSIPPANY, N.J., Feb. 20, 2026 /PRNewswire/ -- PBF Energy Inc. (NYSE:PBF) today announced that members of its management team will participate in the Scotiabank Global Energy Conference on February 25, 2026; the Raymond James Institutional Investor Conference on March 2-3, 2026; and the Wolfe Research Refining Conference on March 5, 2026.</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) was the target of unusually large options trading on Wednesday. Investors purchased 14,762 call options on the stock. This represents an increase of approximately 392% compared to the average daily volume of 2,998 call options. Insiders Place Their Bets In related news, insider Control Empresarial De Capital</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/pbf-energy-to-participate-in-industry-conferences-302693784.html</t>
+          <t>https://www.defenseworld.net/2026/03/05/stock-traders-purchase-large-volume-of-call-options-on-pbf-energy-nysepbf.html</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8476,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-02-20 03:00:49</t>
+          <t>2026-02-28 04:23:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8444,12 +8486,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PBF Energy Sees Unusually Large Options Volume (NYSE:PBF)</t>
+          <t>Control Empresarial De Capital Sells 250,000 Shares of PBF Energy (NYSE:PBF) Stock</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-sees-unusually-large-options-volume-nysepbf-20260220.png</t>
+          <t>https://images.financialmodelingprep.com/news/control-empresarial-de-capital-sells-250000-shares-of-pbf-20260228.png</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8459,12 +8501,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) saw some unusual options trading on Thursday. Stock traders acquired 64,035 put options on the company. This is an increase of 3,175% compared to the typical daily volume of 1,955 put options. PBF Energy Price Performance Shares of NYSE PBF opened at $33.90 on Friday. The stock</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 250,000 shares of PBF Energy stock in a transaction on Tuesday, February 24th. The stock was sold at an average price of $34.91, for a total value of $8,727,500.00. Following the transaction, the insider directly owned 27,591,198 shares of the company's</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/02/20/pbf-energy-sees-unusually-large-options-volume-nysepbf.html</t>
+          <t>https://www.defenseworld.net/2026/02/28/control-empresarial-de-capital-sells-250000-shares-of-pbf-energy-nysepbf-stock.html</t>
         </is>
       </c>
     </row>
@@ -8476,37 +8518,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-02-13 10:35:24</t>
+          <t>2026-02-25 04:43:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PBF Energy Q4 Earnings Beat Estimates on Higher Refining Margins</t>
+          <t>Counterpoint Mutual Funds LLC Makes New Investment in PBF Energy Inc. $PBF</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-q4-earnings-beat-estimates-on-higher-refining-20260213.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/counterpoint-mutual-funds-llc-makes-new-investment-in-pbf-20260225.png</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PBF beats Q4 estimates as higher refining margins and lower costs lift earnings despite a revenue dip.</t>
+          <t>Counterpoint Mutual Funds LLC purchased a new position in PBF Energy Inc. (NYSE: PBF) during the undefined quarter, according to the company in its most recent 13F filing with the Securities and Exchange Commission. The institutional investor purchased 16,649 shares of the oil and gas company's stock, valued at approximately $502,000. Other institutional</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2868880/pbf-energy-q4-earnings-beat-estimates-on-higher-refining-margins?cid=CS-STOCKNEWSAPI-FT-analyst_blog|earnings_article-2868880</t>
+          <t>https://www.defenseworld.net/2026/02/25/counterpoint-mutual-funds-llc-makes-new-investment-in-pbf-energy-inc-pbf.html</t>
         </is>
       </c>
     </row>
@@ -8518,37 +8560,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-02-13 02:08:49</t>
+          <t>2026-02-20 16:15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>PRNewsWire</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PBF Energy Q4 Earnings Call Highlights</t>
+          <t>PBF Energy to Participate in Industry Conferences</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-q4-earnings-call-highlights-20260213.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-to-participate-in-industry-conferences-20260220.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PBF Energy (NYSE: PBF) executives used the company's fourth-quarter 2025 earnings call to highlight progress toward restarting its Martinez, California refinery, point to improving crude oil differentials as a key earnings lever, and outline additional cost-reduction targets under its Refinery Business Improvement (RBI) program. Martinez restart: construction nearly complete, operations targeted by early March Chief Executive</t>
+          <t>PARSIPPANY, N.J., Feb. 20, 2026 /PRNewswire/ -- PBF Energy Inc. (NYSE:PBF) today announced that members of its management team will participate in the Scotiabank Global Energy Conference on February 25, 2026; the Raymond James Institutional Investor Conference on March 2-3, 2026; and the Wolfe Research Refining Conference on March 5, 2026.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/02/13/pbf-energy-q4-earnings-call-highlights.html</t>
+          <t>https://www.prnewswire.com/news-releases/pbf-energy-to-participate-in-industry-conferences-302693784.html</t>
         </is>
       </c>
     </row>
@@ -8560,37 +8602,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-02-12 14:44:29</t>
+          <t>2026-02-20 03:00:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (PBF) Q4 2025 Earnings Call Transcript</t>
+          <t>PBF Energy Sees Unusually Large Options Volume (NYSE:PBF)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-pbf-q4-2025-earnings-call-transcript-20260212.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-sees-unusually-large-options-volume-nysepbf-20260220.png</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (PBF) Q4 2025 Earnings Call Transcript</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) saw some unusual options trading on Thursday. Stock traders acquired 64,035 put options on the company. This is an increase of 3,175% compared to the typical daily volume of 1,955 put options. PBF Energy Price Performance Shares of NYSE PBF opened at $33.90 on Friday. The stock</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4869648-pbf-energy-inc-pbf-q4-2025-earnings-call-transcript</t>
+          <t>https://www.defenseworld.net/2026/02/20/pbf-energy-sees-unusually-large-options-volume-nysepbf.html</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8644,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-02-12 08:45:22</t>
+          <t>2026-02-13 10:35:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8612,12 +8654,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PBF Energy (PBF) Beats Q4 Earnings and Revenue Estimates</t>
+          <t>PBF Energy Q4 Earnings Beat Estimates on Higher Refining Margins</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-pbf-beats-q4-earnings-and-revenue-estimates-20260212.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-q4-earnings-beat-estimates-on-higher-refining-20260213.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8627,12 +8669,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PBF Energy (PBF) came out with quarterly earnings of $0.49 per share, beating the Zacks Consensus Estimate of a loss of $0.15 per share. This compares to a loss of $2.82 per share a year ago.</t>
+          <t>PBF beats Q4 estimates as higher refining margins and lower costs lift earnings despite a revenue dip.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2861287/pbf-energy-pbf-beats-q4-earnings-and-revenue-estimates?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_4-2861287</t>
+          <t>https://www.zacks.com/stock/news/2868880/pbf-energy-q4-earnings-beat-estimates-on-higher-refining-margins?cid=CS-STOCKNEWSAPI-FT-analyst_blog|earnings_article-2868880</t>
         </is>
       </c>
     </row>
@@ -8644,37 +8686,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-02-12 06:30:00</t>
+          <t>2026-02-13 02:08:49</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PRNewsWire</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PBF Energy Reports Fourth Quarter and Full Year 2025 Results, Declares Dividend of $0.275 per Share</t>
+          <t>PBF Energy Q4 Earnings Call Highlights</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-reports-fourth-quarter-and-full-year-2025-20260212.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-q4-earnings-call-highlights-20260213.png</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fourth quarter income from operations of $128.0 million (excluding special items, fourth quarter income from operations of $99.4 million) Full year loss from operations of $54.3 million (excluding special items, full year loss from operations of $479.5 million) Declares quarterly dividend of $0.275 per share Martinez refinery restart on schedule PARSIPPANY, N.J., Feb. 12, 2026 /PRNewswire/ -- PBF Energy Inc. (NYSE:PBF) today reported fourth quarter 2025 income from operations of $128.0 million as compared to loss from operations of $383.2 million for the fourth quarter of 2024.</t>
+          <t>PBF Energy (NYSE: PBF) executives used the company's fourth-quarter 2025 earnings call to highlight progress toward restarting its Martinez, California refinery, point to improving crude oil differentials as a key earnings lever, and outline additional cost-reduction targets under its Refinery Business Improvement (RBI) program. Martinez restart: construction nearly complete, operations targeted by early March Chief Executive</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/pbf-energy-reports-fourth-quarter-and-full-year-2025-results-declares-dividend-of-0-275-per-share-302686115.html</t>
+          <t>https://www.defenseworld.net/2026/02/13/pbf-energy-q4-earnings-call-highlights.html</t>
         </is>
       </c>
     </row>
@@ -8686,37 +8728,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-02-10 07:39:00</t>
+          <t>2026-02-12 14:44:29</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>First Look: Novo sues Hims, BP halts buybacks, Meta faces trial</t>
+          <t>PBF Energy Inc. (PBF) Q4 2025 Earnings Call Transcript</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/first-look-novo-sues-hims-bp-halts-buybacks-meta-20260210.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-pbf-q4-2025-earnings-call-transcript-20260212.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>gurufocus.com</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Stock News Novo sues Hims over compounded weight-loss drugs: Novo Nordisk (NVO) filed suit to stop Hims and Hers Health (HIMS) from selling compounded semaglutide</t>
+          <t>PBF Energy Inc. (PBF) Q4 2025 Earnings Call Transcript</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/8600811/first-look-novo-sues-hims-bp-halts-buybacks-meta-faces-trial</t>
+          <t>https://seekingalpha.com/article/4869648-pbf-energy-inc-pbf-q4-2025-earnings-call-transcript</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8770,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-02-05 11:01:35</t>
+          <t>2026-02-12 08:45:22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -8738,12 +8780,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PBF Energy (PBF) May Report Negative Earnings: Know the Trend Ahead of Next Week's Release</t>
+          <t>PBF Energy (PBF) Beats Q4 Earnings and Revenue Estimates</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-pbf-may-report-negative-earnings-know-the-20260205.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-pbf-beats-q4-earnings-and-revenue-estimates-20260212.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -8753,12 +8795,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>PBF Energy (PBF) doesn't possess the right combination of the two key ingredients for a likely earnings beat in its upcoming report. Get prepared with the key expectations.</t>
+          <t>PBF Energy (PBF) came out with quarterly earnings of $0.49 per share, beating the Zacks Consensus Estimate of a loss of $0.15 per share. This compares to a loss of $2.82 per share a year ago.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2829990/pbf-energy-pbf-may-report-negative-earnings-know-the-trend-ahead-of-next-week-s-release?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_9-2829990</t>
+          <t>https://www.zacks.com/stock/news/2861287/pbf-energy-pbf-beats-q4-earnings-and-revenue-estimates?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_4-2861287</t>
         </is>
       </c>
     </row>
@@ -8770,37 +8812,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-02-04 17:02:00</t>
+          <t>2026-02-12 06:30:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>PRNewsWire</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Weyerhaeuser Co: A Significant Addition to First Eagle Investment's Portfolio</t>
+          <t>PBF Energy Reports Fourth Quarter and Full Year 2025 Results, Declares Dividend of $0.275 per Share</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/weyerhaeuser-co-a-significant-addition-to-first-eagle-investments-portfolio-20260204.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-reports-fourth-quarter-and-full-year-2025-20260212.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>gurufocus.com</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>First Eagle Investment (Trades, Portfolio)'s Strategic Moves in Q4 2025 First Eagle Investment (Trades, Portfolio) recently submitted its 13F filing for the fo</t>
+          <t>Fourth quarter income from operations of $128.0 million (excluding special items, fourth quarter income from operations of $99.4 million) Full year loss from operations of $54.3 million (excluding special items, full year loss from operations of $479.5 million) Declares quarterly dividend of $0.275 per share Martinez refinery restart on schedule PARSIPPANY, N.J., Feb. 12, 2026 /PRNewswire/ -- PBF Energy Inc. (NYSE:PBF) today reported fourth quarter 2025 income from operations of $128.0 million as compared to loss from operations of $383.2 million for the fourth quarter of 2024.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/8583025/weyerhaeuser-co-a-significant-addition-to-first-eagle-investments-portfolio</t>
+          <t>https://www.prnewswire.com/news-releases/pbf-energy-reports-fourth-quarter-and-full-year-2025-results-declares-dividend-of-0-275-per-share-302686115.html</t>
         </is>
       </c>
     </row>
@@ -8812,37 +8854,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-01-31 03:56:06</t>
+          <t>2026-02-10 07:39:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PBF Insider Sells Nearly 50k Shares as the Recovery from a Refinery Explosion Continues</t>
+          <t>First Look: Novo sues Hims, BP halts buybacks, Meta faces trial</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-insider-sells-nearly-50k-shares-as-the-recovery-20260131.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/first-look-novo-sues-hims-bp-halts-buybacks-meta-20260210.png</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>fool.com</t>
+          <t>gurufocus.com</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Control Empresarial de Capitales S.A. de C.V. sold 49,000 insider shares over two days in late January, which was worth over $1 million This sale represented 0.16% of the insider's direct holdings, reducing direct ownership to 30,358,498 shares.</t>
+          <t>Stock News Novo sues Hims over compounded weight-loss drugs: Novo Nordisk (NVO) filed suit to stop Hims and Hers Health (HIMS) from selling compounded semaglutide</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.fool.com/coverage/filings/2026/01/31/pbf-insider-sells-nearly-50k-shares-as-the-recovery-from-a-refinery-explosion-continues/</t>
+          <t>https://www.gurufocus.com/news/8600811/first-look-novo-sues-hims-bp-halts-buybacks-meta-faces-trial</t>
         </is>
       </c>
     </row>
@@ -8854,37 +8896,37 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-01-25 05:30:45</t>
+          <t>2026-02-05 11:01:35</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Control Empresarial De Capital Sells 40,000 Shares of PBF Energy (NYSE:PBF) Stock</t>
+          <t>PBF Energy (PBF) May Report Negative Earnings: Know the Trend Ahead of Next Week's Release</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/control-empresarial-de-capital-sells-40000-shares-of-pbf-20260125.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-pbf-may-report-negative-earnings-know-the-20260205.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 40,000 shares of PBF Energy stock in a transaction dated Thursday, January 22nd. The shares were sold at an average price of $33.79, for a total transaction of $1,351,600.00. Following the completion of the transaction, the insider directly owned 30,358,498 shares</t>
+          <t>PBF Energy (PBF) doesn't possess the right combination of the two key ingredients for a likely earnings beat in its upcoming report. Get prepared with the key expectations.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/01/25/control-empresarial-de-capital-sells-40000-shares-of-pbf-energy-nysepbf-stock.html</t>
+          <t>https://www.zacks.com/stock/news/2829990/pbf-energy-pbf-may-report-negative-earnings-know-the-trend-ahead-of-next-week-s-release?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_9-2829990</t>
         </is>
       </c>
     </row>
@@ -8896,37 +8938,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-01-23 02:48:53</t>
+          <t>2026-02-04 17:02:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE:PBF) Receives Consensus Rating of “Reduce” from Analysts</t>
+          <t>Weyerhaeuser Co: A Significant Addition to First Eagle Investment's Portfolio</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-nysepbf-receives-consensus-rating-of-reduce-20260123.png</t>
+          <t>https://images.financialmodelingprep.com/news/weyerhaeuser-co-a-significant-addition-to-first-eagle-investments-portfolio-20260204.png</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>gurufocus.com</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Shares of PBF Energy Inc. (NYSE: PBF - Get Free Report) have been assigned an average rating of "Reduce" from the seventeen ratings firms that are currently covering the stock, Marketbeat reports. Eight investment analysts have rated the stock with a sell rating, seven have given a hold rating and two have issued a buy rating</t>
+          <t>First Eagle Investment (Trades, Portfolio)'s Strategic Moves in Q4 2025 First Eagle Investment (Trades, Portfolio) recently submitted its 13F filing for the fo</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/01/23/pbf-energy-inc-nysepbf-receives-consensus-rating-of-reduce-from-analysts-2.html</t>
+          <t>https://www.gurufocus.com/news/8583025/weyerhaeuser-co-a-significant-addition-to-first-eagle-investments-portfolio</t>
         </is>
       </c>
     </row>
@@ -8938,37 +8980,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-01-20 09:27:00</t>
+          <t>2026-01-31 03:56:06</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GlobeNewsWire</t>
+          <t>The Motley Fool</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Performance Shipping Inc. Secures Three-Year Time Charter Contract for M/T P. Monterey at USD31,000 per Day</t>
+          <t>PBF Insider Sells Nearly 50k Shares as the Recovery from a Refinery Explosion Continues</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/performance-shipping-inc-secures-threeyear-time-charter-contract-for-20260120.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-insider-sells-nearly-50k-shares-as-the-recovery-20260131.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>globenewswire.com</t>
+          <t>fool.com</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ATHENS, Greece, Jan. 20, 2026 (GLOBE NEWSWIRE) -- Performance Shipping Inc. (NASDAQ: PSHG) (“we” or the “Company”), a global shipping company specializing in the ownership of tanker vessels, announced today that, through a separate wholly-owned subsidiary, it has entered into a time charter contract with PBF Holding Company LLC, a subsidiary of PBF Energy Inc. (NYSE: PBF) (“PBF” or the “Charterer”) for its M/T P. Monterey (the “vessel”), a 105,525 dwt Aframax tanker built in 2011.</t>
+          <t>Control Empresarial de Capitales S.A. de C.V. sold 49,000 insider shares over two days in late January, which was worth over $1 million This sale represented 0.16% of the insider's direct holdings, reducing direct ownership to 30,358,498 shares.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/01/20/3221859/14069/en/Performance-Shipping-Inc-Secures-Three-Year-Time-Charter-Contract-for-M-T-P-Monterey-at-USD31-000-per-Day.html</t>
+          <t>https://www.fool.com/coverage/filings/2026/01/31/pbf-insider-sells-nearly-50k-shares-as-the-recovery-from-a-refinery-explosion-continues/</t>
         </is>
       </c>
     </row>
@@ -8980,7 +9022,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-01-14 04:48:48</t>
+          <t>2026-01-25 05:30:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8990,12 +9032,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PBF Energy (NYSE:PBF) Insider Control Empresarial De Capital Sells 50,000 Shares</t>
+          <t>Control Empresarial De Capital Sells 40,000 Shares of PBF Energy (NYSE:PBF) Stock</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-insider-control-empresarial-de-capital-sells-50000-20260114.png</t>
+          <t>https://images.financialmodelingprep.com/news/control-empresarial-de-capital-sells-40000-shares-of-pbf-20260125.png</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -9005,12 +9047,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 50,000 shares of the business's stock in a transaction dated Friday, January 9th. The stock was sold at an average price of $32.31, for a total transaction of $1,615,500.00. Following the completion of the sale, the insider directly owned 30,773,498 shares</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 40,000 shares of PBF Energy stock in a transaction dated Thursday, January 22nd. The shares were sold at an average price of $33.79, for a total transaction of $1,351,600.00. Following the completion of the transaction, the insider directly owned 30,358,498 shares</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2026/01/14/pbf-energy-nysepbf-insider-control-empresarial-de-capital-sells-50000-shares.html</t>
+          <t>https://www.defenseworld.net/2026/01/25/control-empresarial-de-capital-sells-40000-shares-of-pbf-energy-nysepbf-stock.html</t>
         </is>
       </c>
     </row>
@@ -9022,37 +9064,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-01-09 11:55:11</t>
+          <t>2026-01-23 02:48:53</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Forbes</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Why PBF Energy Stock Is Surging On Venezuela Catalyst</t>
+          <t>PBF Energy Inc. (NYSE:PBF) Receives Consensus Rating of “Reduce” from Analysts</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/why-pbf-energy-stock-is-surging-on-venezuela-catalyst-20260109.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-nysepbf-receives-consensus-rating-of-reduce-20260123.png</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>forbes.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>PBF Energy soared 14% on a robust gap-and-go following a Piper Sandler upgrade to ‘Overweight' accompanied by a $40 price target. The catalyst mentioned was PBF‘s strategic advantage in increasing Venezuelan crude imports.</t>
+          <t>Shares of PBF Energy Inc. (NYSE: PBF - Get Free Report) have been assigned an average rating of "Reduce" from the seventeen ratings firms that are currently covering the stock, Marketbeat reports. Eight investment analysts have rated the stock with a sell rating, seven have given a hold rating and two have issued a buy rating</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.forbes.com/sites/greatspeculations/2026/01/09/why-pbf-energy-stock-is-surging-on-venezuela-catalyst/</t>
+          <t>https://www.defenseworld.net/2026/01/23/pbf-energy-inc-nysepbf-receives-consensus-rating-of-reduce-from-analysts-2.html</t>
         </is>
       </c>
     </row>
@@ -9064,37 +9106,37 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-01-09 10:47:18</t>
+          <t>2026-01-20 09:27:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>GlobeNewsWire</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PBF Energy (PBF) Moves 13.9% Higher: Will This Strength Last?</t>
+          <t>Performance Shipping Inc. Secures Three-Year Time Charter Contract for M/T P. Monterey at USD31,000 per Day</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-pbf-moves-139-higher-will-this-strength-20260109.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/performance-shipping-inc-secures-threeyear-time-charter-contract-for-20260120.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>globenewswire.com</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PBF Energy (PBF) witnessed a jump in share price last session on above-average trading volume. The latest trend in earnings estimate revisions for the stock doesn't suggest further strength down the road.</t>
+          <t>ATHENS, Greece, Jan. 20, 2026 (GLOBE NEWSWIRE) -- Performance Shipping Inc. (NASDAQ: PSHG) (“we” or the “Company”), a global shipping company specializing in the ownership of tanker vessels, announced today that, through a separate wholly-owned subsidiary, it has entered into a time charter contract with PBF Holding Company LLC, a subsidiary of PBF Energy Inc. (NYSE: PBF) (“PBF” or the “Charterer”) for its M/T P. Monterey (the “vessel”), a 105,525 dwt Aframax tanker built in 2011.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2815013/pbf-energy-pbf-moves-13-9-higher-will-this-strength-last?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|daily_price_change_5%-2815013</t>
+          <t>https://www.globenewswire.com/news-release/2026/01/20/3221859/14069/en/Performance-Shipping-Inc-Secures-Three-Year-Time-Charter-Contract-for-M-T-P-Monterey-at-USD31-000-per-Day.html</t>
         </is>
       </c>
     </row>
@@ -9106,37 +9148,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-01-09 08:09:49</t>
+          <t>2026-01-14 04:48:48</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Scott Bessent Contradicts Trump, Says Oil Giants 'Not Interested' In Venezuela</t>
+          <t>PBF Energy (NYSE:PBF) Insider Control Empresarial De Capital Sells 50,000 Shares</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/scott-bessent-contradicts-trump-says-oil-giants-not-interested-20260109.jpeg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-insider-control-empresarial-de-capital-sells-50000-20260114.png</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>feeds.benzinga.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Contrary to President Donald Trump's assurances, major oil companies are not keen on investing in Venezuela, according to Treasury Secretary Scott Bessent.</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) insider Control Empresarial De Capital sold 50,000 shares of the business's stock in a transaction dated Friday, January 9th. The stock was sold at an average price of $32.31, for a total transaction of $1,615,500.00. Following the completion of the sale, the insider directly owned 30,773,498 shares</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.benzinga.com/markets/commodities/26/01/49810352/scott-bessent-contradicts-trump-says-oil-giants-not-interested-in-venezuela</t>
+          <t>https://www.defenseworld.net/2026/01/14/pbf-energy-nysepbf-insider-control-empresarial-de-capital-sells-50000-shares.html</t>
         </is>
       </c>
     </row>
@@ -9148,37 +9190,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-01-06 13:47:13</t>
+          <t>2026-01-09 11:55:11</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Forbes</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Venezuelan oil would boost US refiners, hurt Canadian producers</t>
+          <t>Why PBF Energy Stock Is Surging On Venezuela Catalyst</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/venezuelan-oil-would-boost-us-refiners-hurt-canadian-producers-20260106.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/why-pbf-energy-stock-is-surging-on-venezuela-catalyst-20260109.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>forbes.com</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>A full-scale resumption of Venezuelan oil exports would benefit refiners in the United States and lower their fuel production costs, with the refineries capable of absorbing most of the roughly 1 million barrels per day of crude that would trade freely if U.S. sanctions on the South American country are removed.</t>
+          <t>PBF Energy soared 14% on a robust gap-and-go following a Piper Sandler upgrade to ‘Overweight' accompanied by a $40 price target. The catalyst mentioned was PBF‘s strategic advantage in increasing Venezuelan crude imports.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/energy/venezuelan-oil-would-boost-us-refiners-hurt-canadian-producers-2026-01-06/</t>
+          <t>https://www.forbes.com/sites/greatspeculations/2026/01/09/why-pbf-energy-stock-is-surging-on-venezuela-catalyst/</t>
         </is>
       </c>
     </row>
@@ -9190,37 +9232,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-01-02 17:30:00</t>
+          <t>2026-01-09 10:47:18</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PRNewsWire</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PBF Energy Provides Update on Martinez Refinery Operations and Issues 2026 Annual Guidance Information</t>
+          <t>PBF Energy (PBF) Moves 13.9% Higher: Will This Strength Last?</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-provides-update-on-martinez-refinery-operations-and-20260102.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-pbf-moves-139-higher-will-this-strength-20260109.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>PARSIPPANY, N.J., Jan. 2, 2026 /PRNewswire/ -- PBF Energy Inc. (NYSE: PBF) announced today that rebuild activities at its 157,000 barrel per day Martinez, California refinery following the February 1, 2025 fire are now expected to progress into February.</t>
+          <t>PBF Energy (PBF) witnessed a jump in share price last session on above-average trading volume. The latest trend in earnings estimate revisions for the stock doesn't suggest further strength down the road.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/pbf-energy-provides-update-on-martinez-refinery-operations-and-issues-2026-annual-guidance-information-302651926.html</t>
+          <t>https://www.zacks.com/stock/news/2815013/pbf-energy-pbf-moves-13-9-higher-will-this-strength-last?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|daily_price_change_5%-2815013</t>
         </is>
       </c>
     </row>
@@ -9232,37 +9274,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2025-12-29 01:12:56</t>
+          <t>2026-01-09 08:09:49</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE:PBF) Receives Consensus Rating of “Reduce” from Analysts</t>
+          <t>Scott Bessent Contradicts Trump, Says Oil Giants 'Not Interested' In Venezuela</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-nysepbf-receives-consensus-rating-of-reduce-20251229.png</t>
+          <t>https://images.financialmodelingprep.com/news/scott-bessent-contradicts-trump-says-oil-giants-not-interested-20260109.jpeg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>feeds.benzinga.com</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Shares of PBF Energy Inc. (NYSE: PBF - Get Free Report) have received an average rating of "Reduce" from the sixteen research firms that are covering the stock, MarketBeat reports. Nine research analysts have rated the stock with a sell rating, six have issued a hold rating and one has assigned a buy rating to the</t>
+          <t>Contrary to President Donald Trump's assurances, major oil companies are not keen on investing in Venezuela, according to Treasury Secretary Scott Bessent.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2025/12/29/pbf-energy-inc-nysepbf-receives-consensus-rating-of-reduce-from-analysts.html</t>
+          <t>https://www.benzinga.com/markets/commodities/26/01/49810352/scott-bessent-contradicts-trump-says-oil-giants-not-interested-in-venezuela</t>
         </is>
       </c>
     </row>
@@ -9274,37 +9316,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2025-12-23 05:01:12</t>
+          <t>2026-01-06 13:47:13</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PBF Energy (NYSE:PBF) CAO Steven John Andriola Sells 2,579 Shares</t>
+          <t>Venezuelan oil would boost US refiners, hurt Canadian producers</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-cao-steven-john-andriola-sells-2579-20251223.png</t>
+          <t>https://images.financialmodelingprep.com/news/venezuelan-oil-would-boost-us-refiners-hurt-canadian-producers-20260106.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) CAO Steven John Andriola sold 2,579 shares of the business's stock in a transaction dated Friday, December 19th. The shares were sold at an average price of $26.19, for a total transaction of $67,544.01. Following the sale, the chief accounting officer directly owned 17,414 shares of the</t>
+          <t>A full-scale resumption of Venezuelan oil exports would benefit refiners in the United States and lower their fuel production costs, with the refineries capable of absorbing most of the roughly 1 million barrels per day of crude that would trade freely if U.S. sanctions on the South American country are removed.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2025/12/23/pbf-energy-nysepbf-cao-steven-john-andriola-sells-2579-shares.html</t>
+          <t>https://www.reuters.com/business/energy/venezuelan-oil-would-boost-us-refiners-hurt-canadian-producers-2026-01-06/</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9358,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2025-12-18 17:30:00</t>
+          <t>2026-01-02 17:30:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9326,12 +9368,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PBF Energy to Participate in the Goldman Sachs Energy, CleanTech &amp; Utilities Conference</t>
+          <t>PBF Energy Provides Update on Martinez Refinery Operations and Issues 2026 Annual Guidance Information</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-to-participate-in-the-goldman-sachs-energy-20251218.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-provides-update-on-martinez-refinery-operations-and-20260102.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -9341,12 +9383,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>PARSIPPANY, N.J. , Dec. 18, 2025 /PRNewswire/ -- PBF Energy Inc. (NYSE:PBF) today announced that members of its management team will participate in the Goldman Sachs Energy, CleanTech &amp; Utilities Conference on January 5-7, 2026.</t>
+          <t>PARSIPPANY, N.J., Jan. 2, 2026 /PRNewswire/ -- PBF Energy Inc. (NYSE: PBF) announced today that rebuild activities at its 157,000 barrel per day Martinez, California refinery following the February 1, 2025 fire are now expected to progress into February.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/pbf-energy-to-participate-in-the-goldman-sachs-energy-cleantech--utilities-conference-302640099.html</t>
+          <t>https://www.prnewswire.com/news-releases/pbf-energy-provides-update-on-martinez-refinery-operations-and-issues-2026-annual-guidance-information-302651926.html</t>
         </is>
       </c>
     </row>
@@ -9358,37 +9400,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2025-12-18 17:15:00</t>
+          <t>2025-12-29 01:12:56</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PRNewsWire</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PBF Energy to Release Fourth Quarter 2025 Earnings Results</t>
+          <t>PBF Energy Inc. (NYSE:PBF) Receives Consensus Rating of “Reduce” from Analysts</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-to-release-fourth-quarter-2025-earnings-results-20251218.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-nysepbf-receives-consensus-rating-of-reduce-20251229.png</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>PARSIPPANY, N.J. , Dec. 18, 2025 /PRNewswire/ -- PBF Energy Inc. (NYSE: PBF) announced today that it will release its earnings results for the fourth quarter 2025 on Thursday, February 12, 2026.</t>
+          <t>Shares of PBF Energy Inc. (NYSE: PBF - Get Free Report) have received an average rating of "Reduce" from the sixteen research firms that are covering the stock, MarketBeat reports. Nine research analysts have rated the stock with a sell rating, six have issued a hold rating and one has assigned a buy rating to the</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/pbf-energy-to-release-fourth-quarter-2025-earnings-results-302640020.html</t>
+          <t>https://www.defenseworld.net/2025/12/29/pbf-energy-inc-nysepbf-receives-consensus-rating-of-reduce-from-analysts.html</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9442,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2025-12-16 05:46:55</t>
+          <t>2025-12-23 05:01:12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9410,12 +9452,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Nomura Holdings Inc. Purchases Shares of 269,645 PBF Energy Inc. $PBF</t>
+          <t>PBF Energy (NYSE:PBF) CAO Steven John Andriola Sells 2,579 Shares</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/nomura-holdings-inc-purchases-shares-of-269645-pbf-energy-20251216.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-nysepbf-cao-steven-john-andriola-sells-2579-20251223.png</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -9425,12 +9467,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nomura Holdings Inc. acquired a new position in PBF Energy Inc. (NYSE: PBF) during the undefined quarter, according to the company in its most recent disclosure with the SEC. The fund acquired 269,645 shares of the oil and gas company's stock, valued at approximately $5,843,000. Nomura Holdings Inc. owned about 0.23% of PBF</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) CAO Steven John Andriola sold 2,579 shares of the business's stock in a transaction dated Friday, December 19th. The shares were sold at an average price of $26.19, for a total transaction of $67,544.01. Following the sale, the chief accounting officer directly owned 17,414 shares of the</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2025/12/16/nomura-holdings-inc-purchases-shares-of-269645-pbf-energy-inc-pbf.html</t>
+          <t>https://www.defenseworld.net/2025/12/23/pbf-energy-nysepbf-cao-steven-john-andriola-sells-2579-shares.html</t>
         </is>
       </c>
     </row>
@@ -9442,37 +9484,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2025-12-04 18:51:00</t>
+          <t>2025-12-18 17:30:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Newsfile Corp</t>
+          <t>PRNewsWire</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Update Regarding Singapore Subsidiary</t>
+          <t>PBF Energy to Participate in the Goldman Sachs Energy, CleanTech &amp; Utilities Conference</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/update-regarding-singapore-subsidiary-20251204.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-to-participate-in-the-goldman-sachs-energy-20251218.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>newsfilecorp.com</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Vancouver, British Columbia--(Newsfile Corp. - December 4, 2025) - Planet Based Foods Global Inc. (CSE: PBF) (OTC Pink: PBFFF) (FSE: AZ00) (the "Company" or "PBFG") advises that, further to its October 22, 2025 news release announcing the establishment of a wholly owned subsidiary in Singapore, PBFG Trade Pte. Ltd., the Company has determined that it will not proceed with the subsidiary at this time.</t>
+          <t>PARSIPPANY, N.J. , Dec. 18, 2025 /PRNewswire/ -- PBF Energy Inc. (NYSE:PBF) today announced that members of its management team will participate in the Goldman Sachs Energy, CleanTech &amp; Utilities Conference on January 5-7, 2026.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.newsfilecorp.com/release/277007/Update-Regarding-Singapore-Subsidiary</t>
+          <t>https://www.prnewswire.com/news-releases/pbf-energy-to-participate-in-the-goldman-sachs-energy-cleantech--utilities-conference-302640099.html</t>
         </is>
       </c>
     </row>
@@ -9484,37 +9526,37 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2025-12-04 04:38:52</t>
+          <t>2025-12-18 17:15:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>PRNewsWire</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. $PBF Position Trimmed by Edgestream Partners L.P.</t>
+          <t>PBF Energy to Release Fourth Quarter 2025 Earnings Results</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-pbf-position-trimmed-by-edgestream-partners-20251204.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-to-release-fourth-quarter-2025-earnings-results-20251218.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Edgestream Partners L.P. trimmed its stake in PBF Energy Inc. (NYSE: PBF) by 15.7% in the second quarter, according to its most recent disclosure with the Securities and Exchange Commission (SEC). The institutional investor owned 147,513 shares of the oil and gas company's stock after selling 27,541 shares during the quarter. Edgestream Partners</t>
+          <t>PARSIPPANY, N.J. , Dec. 18, 2025 /PRNewswire/ -- PBF Energy Inc. (NYSE: PBF) announced today that it will release its earnings results for the fourth quarter 2025 on Thursday, February 12, 2026.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2025/12/04/pbf-energy-inc-pbf-position-trimmed-by-edgestream-partners-l-p.html</t>
+          <t>https://www.prnewswire.com/news-releases/pbf-energy-to-release-fourth-quarter-2025-earnings-results-302640020.html</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9568,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2025-12-04 01:40:50</t>
+          <t>2025-12-16 05:46:55</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9536,12 +9578,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE:PBF) Receives Average Rating of “Strong Sell” from Analysts</t>
+          <t>Nomura Holdings Inc. Purchases Shares of 269,645 PBF Energy Inc. $PBF</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-nysepbf-receives-average-rating-of-strong-sell-20251204.png</t>
+          <t>https://images.financialmodelingprep.com/news/nomura-holdings-inc-purchases-shares-of-269645-pbf-energy-20251216.png</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -9551,12 +9593,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) has received an average recommendation of "Strong Sell" from the fifteen research firms that are presently covering the company, MarketBeat.com reports. Nine analysts have rated the stock with a sell rating, five have assigned a hold rating and one has given a buy rating to the company.</t>
+          <t>Nomura Holdings Inc. acquired a new position in PBF Energy Inc. (NYSE: PBF) during the undefined quarter, according to the company in its most recent disclosure with the SEC. The fund acquired 269,645 shares of the oil and gas company's stock, valued at approximately $5,843,000. Nomura Holdings Inc. owned about 0.23% of PBF</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2025/12/04/pbf-energy-inc-nysepbf-receives-average-rating-of-strong-sell-from-analysts.html</t>
+          <t>https://www.defenseworld.net/2025/12/16/nomura-holdings-inc-purchases-shares-of-269645-pbf-energy-inc-pbf.html</t>
         </is>
       </c>
     </row>
@@ -9568,37 +9610,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2025-12-02 04:14:57</t>
+          <t>2025-12-04 18:51:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Newsfile Corp</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cetera Investment Advisers Acquires 22,607 Shares of PBF Energy Inc. $PBF</t>
+          <t>Update Regarding Singapore Subsidiary</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/cetera-investment-advisers-acquires-22607-shares-of-pbf-energy-20251202.png</t>
+          <t>https://images.financialmodelingprep.com/news/update-regarding-singapore-subsidiary-20251204.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>newsfilecorp.com</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cetera Investment Advisers raised its holdings in PBF Energy Inc. (NYSE: PBF) by 49.5% in the undefined quarter, according to the company in its most recent 13F filing with the SEC. The fund owned 68,266 shares of the oil and gas company's stock after purchasing an additional 22,607 shares during the quarter. Cetera</t>
+          <t>Vancouver, British Columbia--(Newsfile Corp. - December 4, 2025) - Planet Based Foods Global Inc. (CSE: PBF) (OTC Pink: PBFFF) (FSE: AZ00) (the "Company" or "PBFG") advises that, further to its October 22, 2025 news release announcing the establishment of a wholly owned subsidiary in Singapore, PBFG Trade Pte. Ltd., the Company has determined that it will not proceed with the subsidiary at this time.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2025/12/02/cetera-investment-advisers-acquires-22607-shares-of-pbf-energy-inc-pbf.html</t>
+          <t>https://www.newsfilecorp.com/release/277007/Update-Regarding-Singapore-Subsidiary</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9652,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2025-11-29 03:26:50</t>
+          <t>2025-12-04 04:38:52</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9620,12 +9662,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ameritas Investment Partners Inc. Sells 2,474 Shares of PBF Energy Inc. $PBF</t>
+          <t>PBF Energy Inc. $PBF Position Trimmed by Edgestream Partners L.P.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/ameritas-investment-partners-inc-sells-2474-shares-of-pbf-energy-20251129.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-pbf-position-trimmed-by-edgestream-partners-20251204.png</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -9635,12 +9677,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ameritas Investment Partners Inc. cut its position in shares of PBF Energy Inc. (NYSE: PBF) by 8.2% during the second quarter, according to the company in its most recent disclosure with the Securities and Exchange Commission. The institutional investor owned 27,648 shares of the oil and gas company's stock after selling 2,474 shares</t>
+          <t>Edgestream Partners L.P. trimmed its stake in PBF Energy Inc. (NYSE: PBF) by 15.7% in the second quarter, according to its most recent disclosure with the Securities and Exchange Commission (SEC). The institutional investor owned 147,513 shares of the oil and gas company's stock after selling 27,541 shares during the quarter. Edgestream Partners</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2025/11/29/ameritas-investment-partners-inc-sells-2474-shares-of-pbf-energy-inc-pbf.html</t>
+          <t>https://www.defenseworld.net/2025/12/04/pbf-energy-inc-pbf-position-trimmed-by-edgestream-partners-l-p.html</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9694,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2025-11-26 05:14:43</t>
+          <t>2025-12-04 01:40:50</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -9662,12 +9704,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Creative Planning Acquires 36,571 Shares of PBF Energy Inc. $PBF</t>
+          <t>PBF Energy Inc. (NYSE:PBF) Receives Average Rating of “Strong Sell” from Analysts</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/creative-planning-acquires-36571-shares-of-pbf-energy-inc-20251126.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-nysepbf-receives-average-rating-of-strong-sell-20251204.png</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -9677,12 +9719,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Creative Planning grew its holdings in shares of PBF Energy Inc. (NYSE: PBF) by 64.8% in the undefined quarter, according to its most recent disclosure with the SEC. The fund owned 92,976 shares of the oil and gas company's stock after acquiring an additional 36,571 shares during the period. Creative Planning owned about</t>
+          <t>PBF Energy Inc. (NYSE: PBF - Get Free Report) has received an average recommendation of "Strong Sell" from the fifteen research firms that are presently covering the company, MarketBeat.com reports. Nine analysts have rated the stock with a sell rating, five have assigned a hold rating and one has given a buy rating to the company.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2025/11/26/creative-planning-acquires-36571-shares-of-pbf-energy-inc-pbf.html</t>
+          <t>https://www.defenseworld.net/2025/12/04/pbf-energy-inc-nysepbf-receives-average-rating-of-strong-sell-from-analysts.html</t>
         </is>
       </c>
     </row>
@@ -9694,37 +9736,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2025-11-12 13:01:24</t>
+          <t>2025-12-02 04:14:57</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>PBF Energy Q3 Loss Narrower Than Expected, Revenues Decline Y/Y</t>
+          <t>Cetera Investment Advisers Acquires 22,607 Shares of PBF Energy Inc. $PBF</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-q3-loss-narrower-than-expected-revenues-decline-20251112.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/cetera-investment-advisers-acquires-22607-shares-of-pbf-energy-20251202.png</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>PBF posts narrower Q3 loss as cost cuts lift results, though revenues and throughput volumes fall year over year.</t>
+          <t>Cetera Investment Advisers raised its holdings in PBF Energy Inc. (NYSE: PBF) by 49.5% in the undefined quarter, according to the company in its most recent 13F filing with the SEC. The fund owned 68,266 shares of the oil and gas company's stock after purchasing an additional 22,607 shares during the quarter. Cetera</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2790125/pbf-energy-q3-loss-narrower-than-expected-revenues-decline-y-y?cid=CS-STOCKNEWSAPI-FT-analyst_blog|earnings_article-2790125</t>
+          <t>https://www.defenseworld.net/2025/12/02/cetera-investment-advisers-acquires-22607-shares-of-pbf-energy-inc-pbf.html</t>
         </is>
       </c>
     </row>
@@ -9736,37 +9778,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2025-11-06 16:30:00</t>
+          <t>2025-11-29 03:26:50</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PRNewsWire</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PBF Energy to Participate in Industry Conferences</t>
+          <t>Ameritas Investment Partners Inc. Sells 2,474 Shares of PBF Energy Inc. $PBF</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-to-participate-in-industry-conferences-20251106.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/ameritas-investment-partners-inc-sells-2474-shares-of-pbf-energy-20251129.png</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>PARSIPPANY, N.J. , Nov. 6, 2025 /PRNewswire/ -- PBF Energy Inc. (NYSE:PBF) today announced that members of its management team will participate in the TD Cowen Annual Energy Conference on November 18, 2025, and the Mizuho Power, Energy &amp; Infrastructure Conference on December 9, 2025.</t>
+          <t>Ameritas Investment Partners Inc. cut its position in shares of PBF Energy Inc. (NYSE: PBF) by 8.2% during the second quarter, according to the company in its most recent disclosure with the Securities and Exchange Commission. The institutional investor owned 27,648 shares of the oil and gas company's stock after selling 2,474 shares</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/pbf-energy-to-participate-in-industry-conferences-302607729.html</t>
+          <t>https://www.defenseworld.net/2025/11/29/ameritas-investment-partners-inc-sells-2474-shares-of-pbf-energy-inc-pbf.html</t>
         </is>
       </c>
     </row>
@@ -9778,37 +9820,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2025-10-30 16:36:30</t>
+          <t>2025-11-26 05:14:43</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Defense World</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. (PBF) Q3 2025 Earnings Call Transcript</t>
+          <t>Creative Planning Acquires 36,571 Shares of PBF Energy Inc. $PBF</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-pbf-q3-2025-earnings-call-transcript-20251030.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/creative-planning-acquires-36571-shares-of-pbf-energy-inc-20251126.png</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>seekingalpha.com</t>
+          <t>defenseworld.net</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>PBF Energy Inc. ( PBF ) Q3 2025 Earnings Call October 30, 2025 8:30 AM EDT Company Participants Colin Murray - Vice President of Investor Relations Matthew Lucey - President, CEO &amp; Director Michael A. Bukowski - Senior VP &amp; Head of Refining Joseph Marino - CFO, SVP &amp; Treasurer Thomas D.</t>
+          <t>Creative Planning grew its holdings in shares of PBF Energy Inc. (NYSE: PBF) by 64.8% in the undefined quarter, according to its most recent disclosure with the SEC. The fund owned 92,976 shares of the oil and gas company's stock after acquiring an additional 36,571 shares during the period. Creative Planning owned about</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://seekingalpha.com/article/4835865-pbf-energy-inc-pbf-q3-2025-earnings-call-transcript</t>
+          <t>https://www.defenseworld.net/2025/11/26/creative-planning-acquires-36571-shares-of-pbf-energy-inc-pbf.html</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9862,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2025-10-30 10:31:36</t>
+          <t>2025-11-12 13:01:24</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -9830,12 +9872,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PBF Energy (PBF) Q3 Earnings: Taking a Look at Key Metrics Versus Estimates</t>
+          <t>PBF Energy Q3 Loss Narrower Than Expected, Revenues Decline Y/Y</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-pbf-q3-earnings-taking-a-look-at-20251030.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-q3-loss-narrower-than-expected-revenues-decline-20251112.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -9845,12 +9887,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>The headline numbers for PBF Energy (PBF) give insight into how the company performed in the quarter ended September 2025, but it may be worthwhile to compare some of its key metrics to Wall Street estimates and the year-ago actuals.</t>
+          <t>PBF posts narrower Q3 loss as cost cuts lift results, though revenues and throughput volumes fall year over year.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2781372/pbf-energy-pbf-q3-earnings-taking-a-look-at-key-metrics-versus-estimates?cid=CS-STOCKNEWSAPI-FT-fundamental_analysis|nfm-2781372</t>
+          <t>https://www.zacks.com/stock/news/2790125/pbf-energy-q3-loss-narrower-than-expected-revenues-decline-y-y?cid=CS-STOCKNEWSAPI-FT-analyst_blog|earnings_article-2790125</t>
         </is>
       </c>
     </row>
@@ -9862,37 +9904,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2025-10-30 08:46:08</t>
+          <t>2025-11-06 16:30:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Zacks Investment Research</t>
+          <t>PRNewsWire</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PBF Energy (PBF) Reports Q3 Loss, Beats Revenue Estimates</t>
+          <t>PBF Energy to Participate in Industry Conferences</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-pbf-reports-q3-loss-beats-revenue-estimates-20251030.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-to-participate-in-industry-conferences-20251106.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>zacks.com</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>PBF Energy (PBF) came out with a quarterly loss of $0.52 per share versus the Zacks Consensus Estimate of a loss of $0.69. This compares to a loss of $1.5 per share a year ago.</t>
+          <t>PARSIPPANY, N.J. , Nov. 6, 2025 /PRNewswire/ -- PBF Energy Inc. (NYSE:PBF) today announced that members of its management team will participate in the TD Cowen Annual Energy Conference on November 18, 2025, and the Mizuho Power, Energy &amp; Infrastructure Conference on December 9, 2025.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2781070/pbf-energy-pbf-reports-q3-loss-beats-revenue-estimates?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_4-2781070</t>
+          <t>https://www.prnewswire.com/news-releases/pbf-energy-to-participate-in-industry-conferences-302607729.html</t>
         </is>
       </c>
     </row>
@@ -9904,37 +9946,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2025-10-30 06:30:00</t>
+          <t>2025-10-30 16:36:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PRNewsWire</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PBF Energy Announces Third Quarter 2025 Results and Declares Dividend of $0.275 per Share</t>
+          <t>PBF Energy Inc. (PBF) Q3 2025 Earnings Call Transcript</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/pbf-energy-announces-third-quarter-2025-results-and-declares-20251030.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-inc-pbf-q3-2025-earnings-call-transcript-20251030.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>seekingalpha.com</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Third quarter income from operations of $285.9 million (excluding special items, third quarter loss from operations of $27.1 million) Declared quarterly dividend of $0.275 per share PBF closed sale of terminal assets for $175.4 million PBF to receive a second unallocated installment of $250 million related to the Martinez Refinery Fire PARSIPPANY, N.J. , Oct. 30, 2025 /PRNewswire/ -- PBF Energy Inc. (NYSE: PBF) today reported third quarter 2025 income from operations of $285.9 million as compared to loss from operations of $386.3 million for the third quarter of 2024.</t>
+          <t>PBF Energy Inc. ( PBF ) Q3 2025 Earnings Call October 30, 2025 8:30 AM EDT Company Participants Colin Murray - Vice President of Investor Relations Matthew Lucey - President, CEO &amp; Director Michael A. Bukowski - Senior VP &amp; Head of Refining Joseph Marino - CFO, SVP &amp; Treasurer Thomas D.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/pbf-energy-announces-third-quarter-2025-results-and-declares-dividend-of-0-275-per-share-302599304.html</t>
+          <t>https://seekingalpha.com/article/4835865-pbf-energy-inc-pbf-q3-2025-earnings-call-transcript</t>
         </is>
       </c>
     </row>
@@ -9946,37 +9988,37 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2025-10-26 02:36:25</t>
+          <t>2025-10-30 10:31:36</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Defense World</t>
+          <t>Zacks Investment Research</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Amerilithium (OTCMKTS:PTTN) and PBF Energy (NYSE:PBF) Head-To-Head Comparison</t>
+          <t>PBF Energy (PBF) Q3 Earnings: Taking a Look at Key Metrics Versus Estimates</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/amerilithium-otcmktspttn-and-pbf-energy-nysepbf-headtohead-comparison-20251026.png</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-pbf-q3-earnings-taking-a-look-at-20251030.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>defenseworld.net</t>
+          <t>zacks.com</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>PBF Energy (NYSE: PBF - Get Free Report) and Amerilithium (OTCMKTS:PTTN - Get Free Report) are both energy companies, but which is the superior stock? We will contrast the two companies based on the strength of their valuation, risk, profitability, institutional ownership, analyst recommendations, dividends and earnings. Volatility and Risk PBF Energy has a beta of</t>
+          <t>The headline numbers for PBF Energy (PBF) give insight into how the company performed in the quarter ended September 2025, but it may be worthwhile to compare some of its key metrics to Wall Street estimates and the year-ago actuals.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.defenseworld.net/2025/10/26/amerilithium-otcmktspttn-and-pbf-energy-nysepbf-head-to-head-comparison.html</t>
+          <t>https://www.zacks.com/stock/news/2781372/pbf-energy-pbf-q3-earnings-taking-a-look-at-key-metrics-versus-estimates?cid=CS-STOCKNEWSAPI-FT-fundamental_analysis|nfm-2781372</t>
         </is>
       </c>
     </row>
@@ -9988,7 +10030,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2025-10-23 11:06:06</t>
+          <t>2025-10-30 08:46:08</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9998,12 +10040,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Will PBF Energy (PBF) Report Negative Earnings Next Week? What You Should Know</t>
+          <t>PBF Energy (PBF) Reports Q3 Loss, Beats Revenue Estimates</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://images.financialmodelingprep.com/news/will-pbf-energy-pbf-report-negative-earnings-next-week-20251023.jpg</t>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-pbf-reports-q3-loss-beats-revenue-estimates-20251030.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -10013,12 +10055,54 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>PBF Energy (PBF) doesn't possess the right combination of the two key ingredients for a likely earnings beat in its upcoming report. Get prepared with the key expectations.</t>
+          <t>PBF Energy (PBF) came out with a quarterly loss of $0.52 per share versus the Zacks Consensus Estimate of a loss of $0.69. This compares to a loss of $1.5 per share a year ago.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.zacks.com/stock/news/2775298/will-pbf-energy-pbf-report-negative-earnings-next-week-what-you-should-know?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_9-2775298</t>
+          <t>https://www.zacks.com/stock/news/2781070/pbf-energy-pbf-reports-q3-loss-beats-revenue-estimates?cid=CS-STOCKNEWSAPI-FT-tale_of_the_tape|yseop_template_4-2781070</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PBF</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-10-30 06:30:00</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PRNewsWire</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PBF Energy Announces Third Quarter 2025 Results and Declares Dividend of $0.275 per Share</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://images.financialmodelingprep.com/news/pbf-energy-announces-third-quarter-2025-results-and-declares-20251030.jpg</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>prnewswire.com</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Third quarter income from operations of $285.9 million (excluding special items, third quarter loss from operations of $27.1 million) Declared quarterly dividend of $0.275 per share PBF closed sale of terminal assets for $175.4 million PBF to receive a second unallocated installment of $250 million related to the Martinez Refinery Fire PARSIPPANY, N.J. , Oct. 30, 2025 /PRNewswire/ -- PBF Energy Inc. (NYSE: PBF) today reported third quarter 2025 income from operations of $285.9 million as compared to loss from operations of $386.3 million for the third quarter of 2024.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/pbf-energy-announces-third-quarter-2025-results-and-declares-dividend-of-0-275-per-share-302599304.html</t>
         </is>
       </c>
     </row>
